--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1099"/>
+  <dimension ref="A1:U1118"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -65785,23 +65785,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1099" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1118" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1099" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1118" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1099" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1118" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1099" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1118" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1099" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1118" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68293,11 +68293,11 @@
         <v>4253528.2101453487</v>
       </c>
       <c r="N1077">
-        <f t="shared" ref="N1077:N1099" si="141">IF(A1077&lt;&gt;$K$56,MAX(N1076,VLOOKUP(A1077,A:C,3)),)</f>
+        <f t="shared" ref="N1077:N1098" si="141">IF(A1077&lt;&gt;$K$56,MAX(N1076,VLOOKUP(A1077,A:C,3)),)</f>
         <v>1.0570000410079956</v>
       </c>
       <c r="O1077">
-        <f t="shared" ref="O1077:O1099" si="142">IF(A1077&lt;&gt;$K$56,MIN(O1076,VLOOKUP(A1077,A:D,4)),)</f>
+        <f t="shared" ref="O1077:O1098" si="142">IF(A1077&lt;&gt;$K$56,MIN(O1076,VLOOKUP(A1077,A:D,4)),)</f>
         <v>1.0429999828338623</v>
       </c>
       <c r="P1077">
@@ -68931,7 +68931,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1099" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1118" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69041,7 +69041,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1099" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1118" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -69679,12 +69679,12 @@
         <v>4200498.0933511853</v>
       </c>
       <c r="N1099">
-        <f t="shared" si="141"/>
-        <v>0</v>
+        <f>VLOOKUP(L57,A:C,3)</f>
+        <v>1.0850000381469727</v>
       </c>
       <c r="O1099">
-        <f t="shared" si="142"/>
-        <v>0</v>
+        <f>VLOOKUP(L57,A:D,4)</f>
+        <v>1.0740000009536743</v>
       </c>
       <c r="P1099">
         <f t="shared" si="143"/>
@@ -69709,6 +69709,1203 @@
       <c r="U1099">
         <f t="shared" si="136"/>
         <v>38.003913332402767</v>
+      </c>
+    </row>
+    <row r="1100" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1100" s="1">
+        <v>46027</v>
+      </c>
+      <c r="B1100">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C1100">
+        <v>1.0850000381469727</v>
+      </c>
+      <c r="D1100">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="E1100">
+        <v>1.0829999446868896</v>
+      </c>
+      <c r="F1100">
+        <v>2676530</v>
+      </c>
+      <c r="G1100">
+        <v>26765.30078125</v>
+      </c>
+      <c r="H1100">
+        <f t="shared" si="144"/>
+        <v>1098</v>
+      </c>
+      <c r="I1100">
+        <f>SUM($F$3:F1100)/H1100</f>
+        <v>4199110.1442679875</v>
+      </c>
+      <c r="N1100">
+        <f t="shared" ref="N1100:N1118" si="145">IF(A1100&lt;&gt;$K$57,MAX(N1099,VLOOKUP(A1100,A:C,3)),)</f>
+        <v>1.0850000381469727</v>
+      </c>
+      <c r="O1100">
+        <f t="shared" ref="O1100:O1118" si="146">IF(A1100&lt;&gt;$K$57,MIN(O1099,VLOOKUP(A1100,A:D,4)),)</f>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1100">
+        <f t="shared" si="143"/>
+        <v>1.0806666612625122</v>
+      </c>
+      <c r="Q1100">
+        <f t="shared" si="132"/>
+        <v>1.0653333351725622</v>
+      </c>
+      <c r="R1100">
+        <f t="shared" si="133"/>
+        <v>1.5333326089949972E-2</v>
+      </c>
+      <c r="S1100">
+        <f t="shared" si="134"/>
+        <v>1.014285590372932E-2</v>
+      </c>
+      <c r="T1100">
+        <f t="shared" si="135"/>
+        <v>1.521428385559398E-4</v>
+      </c>
+      <c r="U1100">
+        <f t="shared" si="136"/>
+        <v>100.78243731670764</v>
+      </c>
+    </row>
+    <row r="1101" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1101" s="1">
+        <v>46028</v>
+      </c>
+      <c r="B1101">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="C1101">
+        <v>1.0950000286102295</v>
+      </c>
+      <c r="D1101">
+        <v>1.0809999704360962</v>
+      </c>
+      <c r="E1101">
+        <v>1.093999981880188</v>
+      </c>
+      <c r="F1101">
+        <v>3956634</v>
+      </c>
+      <c r="G1101">
+        <v>39566.33984375</v>
+      </c>
+      <c r="H1101">
+        <f t="shared" si="144"/>
+        <v>1099</v>
+      </c>
+      <c r="I1101">
+        <f>SUM($F$3:F1101)/H1101</f>
+        <v>4198889.5108337123</v>
+      </c>
+      <c r="N1101">
+        <f t="shared" si="145"/>
+        <v>1.0950000286102295</v>
+      </c>
+      <c r="O1101">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1101">
+        <f t="shared" si="143"/>
+        <v>1.0899999936421711</v>
+      </c>
+      <c r="Q1101">
+        <f t="shared" si="132"/>
+        <v>1.0678571434248061</v>
+      </c>
+      <c r="R1101">
+        <f t="shared" si="133"/>
+        <v>2.2142850217365062E-2</v>
+      </c>
+      <c r="S1101">
+        <f t="shared" si="134"/>
+        <v>1.0421767932217163E-2</v>
+      </c>
+      <c r="T1101">
+        <f t="shared" si="135"/>
+        <v>1.5632651898325745E-4</v>
+      </c>
+      <c r="U1101">
+        <f t="shared" si="136"/>
+        <v>141.64487485156988</v>
+      </c>
+    </row>
+    <row r="1102" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1102" s="1">
+        <v>46029</v>
+      </c>
+      <c r="B1102">
+        <v>1.090999960899353</v>
+      </c>
+      <c r="C1102">
+        <v>1.0959999561309814</v>
+      </c>
+      <c r="D1102">
+        <v>1.0829999446868896</v>
+      </c>
+      <c r="E1102">
+        <v>1.0900000333786011</v>
+      </c>
+      <c r="F1102">
+        <v>4585126</v>
+      </c>
+      <c r="G1102">
+        <v>45851.26171875</v>
+      </c>
+      <c r="H1102">
+        <f t="shared" si="144"/>
+        <v>1100</v>
+      </c>
+      <c r="I1102">
+        <f>SUM($F$3:F1102)/H1102</f>
+        <v>4199240.6349147726</v>
+      </c>
+      <c r="N1102">
+        <f t="shared" si="145"/>
+        <v>1.0959999561309814</v>
+      </c>
+      <c r="O1102">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1102">
+        <f t="shared" si="143"/>
+        <v>1.0896666447321575</v>
+      </c>
+      <c r="Q1102">
+        <f t="shared" si="132"/>
+        <v>1.0712142842156545</v>
+      </c>
+      <c r="R1102">
+        <f t="shared" si="133"/>
+        <v>1.8452360516503008E-2</v>
+      </c>
+      <c r="S1102">
+        <f t="shared" si="134"/>
+        <v>9.5476195925758046E-3</v>
+      </c>
+      <c r="T1102">
+        <f t="shared" si="135"/>
+        <v>1.4321429388863707E-4</v>
+      </c>
+      <c r="U1102">
+        <f t="shared" si="136"/>
+        <v>128.84440522991019</v>
+      </c>
+    </row>
+    <row r="1103" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1103" s="1">
+        <v>46030</v>
+      </c>
+      <c r="B1103">
+        <v>1.0809999704360962</v>
+      </c>
+      <c r="C1103">
+        <v>1.0870000123977661</v>
+      </c>
+      <c r="D1103">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="E1103">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="F1103">
+        <v>2499423</v>
+      </c>
+      <c r="G1103">
+        <v>24994.23046875</v>
+      </c>
+      <c r="H1103">
+        <f t="shared" si="144"/>
+        <v>1101</v>
+      </c>
+      <c r="I1103">
+        <f>SUM($F$3:F1103)/H1103</f>
+        <v>4197696.7496877834</v>
+      </c>
+      <c r="N1103">
+        <f t="shared" si="145"/>
+        <v>1.0959999561309814</v>
+      </c>
+      <c r="O1103">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1103">
+        <f t="shared" si="143"/>
+        <v>1.0803333123524983</v>
+      </c>
+      <c r="Q1103">
+        <f t="shared" si="132"/>
+        <v>1.0729523783638364</v>
+      </c>
+      <c r="R1103">
+        <f t="shared" si="133"/>
+        <v>7.3809339886619085E-3</v>
+      </c>
+      <c r="S1103">
+        <f t="shared" si="134"/>
+        <v>8.9523792266845703E-3</v>
+      </c>
+      <c r="T1103">
+        <f t="shared" si="135"/>
+        <v>1.3428568840026856E-4</v>
+      </c>
+      <c r="U1103">
+        <f t="shared" si="136"/>
+        <v>54.96441263838468</v>
+      </c>
+    </row>
+    <row r="1104" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1104" s="1">
+        <v>46031</v>
+      </c>
+      <c r="B1104">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="C1104">
+        <v>1.0880000591278076</v>
+      </c>
+      <c r="D1104">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="E1104">
+        <v>1.0859999656677246</v>
+      </c>
+      <c r="F1104">
+        <v>3370827</v>
+      </c>
+      <c r="G1104">
+        <v>33708.26953125</v>
+      </c>
+      <c r="H1104">
+        <f t="shared" si="144"/>
+        <v>1102</v>
+      </c>
+      <c r="I1104">
+        <f>SUM($F$3:F1104)/H1104</f>
+        <v>4196946.414161751</v>
+      </c>
+      <c r="N1104">
+        <f t="shared" si="145"/>
+        <v>1.0959999561309814</v>
+      </c>
+      <c r="O1104">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1104">
+        <f t="shared" si="143"/>
+        <v>1.0826666752497356</v>
+      </c>
+      <c r="Q1104">
+        <f t="shared" si="132"/>
+        <v>1.0752619022414798</v>
+      </c>
+      <c r="R1104">
+        <f t="shared" si="133"/>
+        <v>7.4047730082558161E-3</v>
+      </c>
+      <c r="S1104">
+        <f t="shared" si="134"/>
+        <v>7.9183651476490338E-3</v>
+      </c>
+      <c r="T1104">
+        <f t="shared" si="135"/>
+        <v>1.187754772147355E-4</v>
+      </c>
+      <c r="U1104">
+        <f t="shared" si="136"/>
+        <v>62.342607934705619</v>
+      </c>
+    </row>
+    <row r="1105" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1105" s="1">
+        <v>46034</v>
+      </c>
+      <c r="B1105">
+        <v>1.0839999914169312</v>
+      </c>
+      <c r="C1105">
+        <v>1.0970000028610229</v>
+      </c>
+      <c r="D1105">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="E1105">
+        <v>1.093999981880188</v>
+      </c>
+      <c r="F1105">
+        <v>3083408</v>
+      </c>
+      <c r="G1105">
+        <v>30834.080078125</v>
+      </c>
+      <c r="H1105">
+        <f t="shared" si="144"/>
+        <v>1103</v>
+      </c>
+      <c r="I1105">
+        <f>SUM($F$3:F1105)/H1105</f>
+        <v>4195936.8598424755</v>
+      </c>
+      <c r="N1105">
+        <f t="shared" si="145"/>
+        <v>1.0970000028610229</v>
+      </c>
+      <c r="O1105">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1105">
+        <f t="shared" si="143"/>
+        <v>1.0893333355585735</v>
+      </c>
+      <c r="Q1105">
+        <f t="shared" si="132"/>
+        <v>1.0779047608375547</v>
+      </c>
+      <c r="R1105">
+        <f t="shared" si="133"/>
+        <v>1.1428574721018769E-2</v>
+      </c>
+      <c r="S1105">
+        <f t="shared" si="134"/>
+        <v>7.2857113111586902E-3</v>
+      </c>
+      <c r="T1105">
+        <f t="shared" si="135"/>
+        <v>1.0928566966738035E-4</v>
+      </c>
+      <c r="U1105">
+        <f t="shared" si="136"/>
+        <v>104.57523622083799</v>
+      </c>
+    </row>
+    <row r="1106" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1106" s="1">
+        <v>46035</v>
+      </c>
+      <c r="B1106">
+        <v>1.0989999771118164</v>
+      </c>
+      <c r="C1106">
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="D1106">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="E1106">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="F1106">
+        <v>3338104</v>
+      </c>
+      <c r="G1106">
+        <v>33381.0390625</v>
+      </c>
+      <c r="H1106">
+        <f t="shared" si="144"/>
+        <v>1104</v>
+      </c>
+      <c r="I1106">
+        <f>SUM($F$3:F1106)/H1106</f>
+        <v>4195159.8373245019</v>
+      </c>
+      <c r="N1106">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1106">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1106">
+        <f t="shared" si="143"/>
+        <v>1.0883333285649617</v>
+      </c>
+      <c r="Q1106">
+        <f t="shared" si="132"/>
+        <v>1.0795714259147644</v>
+      </c>
+      <c r="R1106">
+        <f t="shared" si="133"/>
+        <v>8.761902650197273E-3</v>
+      </c>
+      <c r="S1106">
+        <f t="shared" si="134"/>
+        <v>6.8707466125488281E-3</v>
+      </c>
+      <c r="T1106">
+        <f t="shared" si="135"/>
+        <v>1.0306119918823242E-4</v>
+      </c>
+      <c r="U1106">
+        <f t="shared" si="136"/>
+        <v>85.01650203190836</v>
+      </c>
+    </row>
+    <row r="1107" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1107" s="1">
+        <v>46036</v>
+      </c>
+      <c r="B1107">
+        <v>1.093999981880188</v>
+      </c>
+      <c r="C1107">
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="D1107">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="E1107">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="F1107">
+        <v>2456403</v>
+      </c>
+      <c r="G1107">
+        <v>24564.029296875</v>
+      </c>
+      <c r="H1107">
+        <f t="shared" si="144"/>
+        <v>1105</v>
+      </c>
+      <c r="I1107">
+        <f>SUM($F$3:F1107)/H1107</f>
+        <v>4193586.3017251133</v>
+      </c>
+      <c r="N1107">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1107">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1107">
+        <f t="shared" si="143"/>
+        <v>1.0853333473205566</v>
+      </c>
+      <c r="Q1107">
+        <f t="shared" si="132"/>
+        <v>1.0807619038082303</v>
+      </c>
+      <c r="R1107">
+        <f t="shared" si="133"/>
+        <v>4.5714435123263009E-3</v>
+      </c>
+      <c r="S1107">
+        <f t="shared" si="134"/>
+        <v>6.2380972362700016E-3</v>
+      </c>
+      <c r="T1107">
+        <f t="shared" si="135"/>
+        <v>9.3571458544050023E-5</v>
+      </c>
+      <c r="U1107">
+        <f t="shared" si="136"/>
+        <v>48.855105856602975</v>
+      </c>
+    </row>
+    <row r="1108" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1108" s="1">
+        <v>46037</v>
+      </c>
+      <c r="B1108">
+        <v>1.090999960899353</v>
+      </c>
+      <c r="C1108">
+        <v>1.090999960899353</v>
+      </c>
+      <c r="D1108">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="E1108">
+        <v>1.0900000333786011</v>
+      </c>
+      <c r="F1108">
+        <v>3495507</v>
+      </c>
+      <c r="G1108">
+        <v>34955.0703125</v>
+      </c>
+      <c r="H1108">
+        <f t="shared" si="144"/>
+        <v>1106</v>
+      </c>
+      <c r="I1108">
+        <f>SUM($F$3:F1108)/H1108</f>
+        <v>4192955.126949593</v>
+      </c>
+      <c r="N1108">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1108">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1108">
+        <f t="shared" si="143"/>
+        <v>1.0849999984105427</v>
+      </c>
+      <c r="Q1108">
+        <f t="shared" si="132"/>
+        <v>1.0818333341961817</v>
+      </c>
+      <c r="R1108">
+        <f t="shared" si="133"/>
+        <v>3.1666642143610702E-3</v>
+      </c>
+      <c r="S1108">
+        <f t="shared" si="134"/>
+        <v>5.6190474503705146E-3</v>
+      </c>
+      <c r="T1108">
+        <f t="shared" si="135"/>
+        <v>8.4285711755557714E-5</v>
+      </c>
+      <c r="U1108">
+        <f t="shared" si="136"/>
+        <v>37.570593501599795</v>
+      </c>
+    </row>
+    <row r="1109" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1109" s="1">
+        <v>46038</v>
+      </c>
+      <c r="B1109">
+        <v>1.090999960899353</v>
+      </c>
+      <c r="C1109">
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="D1109">
+        <v>1.0859999656677246</v>
+      </c>
+      <c r="E1109">
+        <v>1.0900000333786011</v>
+      </c>
+      <c r="F1109">
+        <v>5616817</v>
+      </c>
+      <c r="G1109">
+        <v>56168.171875</v>
+      </c>
+      <c r="H1109">
+        <f t="shared" si="144"/>
+        <v>1107</v>
+      </c>
+      <c r="I1109">
+        <f>SUM($F$3:F1109)/H1109</f>
+        <v>4194241.3617039295</v>
+      </c>
+      <c r="N1109">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1109">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1109">
+        <f t="shared" si="143"/>
+        <v>1.0926666657129924</v>
+      </c>
+      <c r="Q1109">
+        <f t="shared" si="132"/>
+        <v>1.0824761901582991</v>
+      </c>
+      <c r="R1109">
+        <f t="shared" si="133"/>
+        <v>1.0190475554693323E-2</v>
+      </c>
+      <c r="S1109">
+        <f t="shared" si="134"/>
+        <v>6.170066846471256E-3</v>
+      </c>
+      <c r="T1109">
+        <f t="shared" si="135"/>
+        <v>9.2551002697068834E-5</v>
+      </c>
+      <c r="U1109">
+        <f t="shared" si="136"/>
+        <v>110.10659266489031</v>
+      </c>
+    </row>
+    <row r="1110" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1110" s="1">
+        <v>46041</v>
+      </c>
+      <c r="B1110">
+        <v>1.0850000381469727</v>
+      </c>
+      <c r="C1110">
+        <v>1.0970000028610229</v>
+      </c>
+      <c r="D1110">
+        <v>1.0850000381469727</v>
+      </c>
+      <c r="E1110">
+        <v>1.0870000123977661</v>
+      </c>
+      <c r="F1110">
+        <v>2259601</v>
+      </c>
+      <c r="G1110">
+        <v>22596.009765625</v>
+      </c>
+      <c r="H1110">
+        <f t="shared" si="144"/>
+        <v>1108</v>
+      </c>
+      <c r="I1110">
+        <f>SUM($F$3:F1110)/H1110</f>
+        <v>4192495.2963955323</v>
+      </c>
+      <c r="N1110">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1110">
+        <f t="shared" si="146"/>
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="P1110">
+        <f t="shared" si="143"/>
+        <v>1.0896666844685872</v>
+      </c>
+      <c r="Q1110">
+        <f t="shared" si="132"/>
+        <v>1.0835238099098206</v>
+      </c>
+      <c r="R1110">
+        <f t="shared" si="133"/>
+        <v>6.1428745587666089E-3</v>
+      </c>
+      <c r="S1110">
+        <f t="shared" si="134"/>
+        <v>5.9727884474254688E-3</v>
+      </c>
+      <c r="T1110">
+        <f t="shared" si="135"/>
+        <v>8.9591826711382026E-5</v>
+      </c>
+      <c r="U1110">
+        <f t="shared" si="136"/>
+        <v>68.565122335944054</v>
+      </c>
+    </row>
+    <row r="1111" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1111" s="1">
+        <v>46042</v>
+      </c>
+      <c r="B1111">
+        <v>1.0870000123977661</v>
+      </c>
+      <c r="C1111">
+        <v>1.0870000123977661</v>
+      </c>
+      <c r="D1111">
+        <v>1.0709999799728394</v>
+      </c>
+      <c r="E1111">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="F1111">
+        <v>876701</v>
+      </c>
+      <c r="G1111">
+        <v>8767.009765625</v>
+      </c>
+      <c r="H1111">
+        <f t="shared" si="144"/>
+        <v>1109</v>
+      </c>
+      <c r="I1111">
+        <f>SUM($F$3:F1111)/H1111</f>
+        <v>4189505.4007270061</v>
+      </c>
+      <c r="N1111">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1111">
+        <f t="shared" si="146"/>
+        <v>1.0709999799728394</v>
+      </c>
+      <c r="P1111">
+        <f t="shared" si="143"/>
+        <v>1.0786666472752888</v>
+      </c>
+      <c r="Q1111">
+        <f t="shared" si="132"/>
+        <v>1.0839761892954509</v>
+      </c>
+      <c r="R1111">
+        <f t="shared" si="133"/>
+        <v>-5.3095420201620946E-3</v>
+      </c>
+      <c r="S1111">
+        <f t="shared" si="134"/>
+        <v>5.455783435276561E-3</v>
+      </c>
+      <c r="T1111">
+        <f t="shared" si="135"/>
+        <v>8.1836751529148409E-5</v>
+      </c>
+      <c r="U1111">
+        <f t="shared" si="136"/>
+        <v>-64.879677173781218</v>
+      </c>
+    </row>
+    <row r="1112" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1112" s="1">
+        <v>46043</v>
+      </c>
+      <c r="B1112">
+        <v>1.0829999446868896</v>
+      </c>
+      <c r="C1112">
+        <v>1.0900000333786011</v>
+      </c>
+      <c r="D1112">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="E1112">
+        <v>1.0789999961853027</v>
+      </c>
+      <c r="F1112">
+        <v>1945701</v>
+      </c>
+      <c r="G1112">
+        <v>19457.009765625</v>
+      </c>
+      <c r="H1112">
+        <f t="shared" si="144"/>
+        <v>1110</v>
+      </c>
+      <c r="I1112">
+        <f>SUM($F$3:F1112)/H1112</f>
+        <v>4187483.9553209459</v>
+      </c>
+      <c r="N1112">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1112">
+        <f t="shared" si="146"/>
+        <v>1.0709999799728394</v>
+      </c>
+      <c r="P1112">
+        <f t="shared" si="143"/>
+        <v>1.0823333263397217</v>
+      </c>
+      <c r="Q1112">
+        <f t="shared" si="132"/>
+        <v>1.0845714268230258</v>
+      </c>
+      <c r="R1112">
+        <f t="shared" si="133"/>
+        <v>-2.2381004833040841E-3</v>
+      </c>
+      <c r="S1112">
+        <f t="shared" si="134"/>
+        <v>4.7755119751910569E-3</v>
+      </c>
+      <c r="T1112">
+        <f t="shared" si="135"/>
+        <v>7.1632679627865847E-5</v>
+      </c>
+      <c r="U1112">
+        <f t="shared" si="136"/>
+        <v>-31.244126213497672</v>
+      </c>
+    </row>
+    <row r="1113" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1113" s="1">
+        <v>46044</v>
+      </c>
+      <c r="B1113">
+        <v>1.0829999446868896</v>
+      </c>
+      <c r="C1113">
+        <v>1.0889999866485596</v>
+      </c>
+      <c r="D1113">
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="E1113">
+        <v>1.0839999914169312</v>
+      </c>
+      <c r="F1113">
+        <v>3030802</v>
+      </c>
+      <c r="G1113">
+        <v>30308.01953125</v>
+      </c>
+      <c r="H1113">
+        <f t="shared" si="144"/>
+        <v>1111</v>
+      </c>
+      <c r="I1113">
+        <f>SUM($F$3:F1113)/H1113</f>
+        <v>4186442.83744937</v>
+      </c>
+      <c r="N1113">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1113">
+        <f t="shared" si="146"/>
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="P1113">
+        <f t="shared" si="143"/>
+        <v>1.0806666612625122</v>
+      </c>
+      <c r="Q1113">
+        <f t="shared" si="132"/>
+        <v>1.0853809487252009</v>
+      </c>
+      <c r="R1113">
+        <f t="shared" si="133"/>
+        <v>-4.7142874626886488E-3</v>
+      </c>
+      <c r="S1113">
+        <f t="shared" si="134"/>
+        <v>3.9115657611769206E-3</v>
+      </c>
+      <c r="T1113">
+        <f t="shared" si="135"/>
+        <v>5.8673486417653808E-5</v>
+      </c>
+      <c r="U1113">
+        <f t="shared" si="136"/>
+        <v>-80.347832564969309</v>
+      </c>
+    </row>
+    <row r="1114" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1114" s="1">
+        <v>46045</v>
+      </c>
+      <c r="B1114">
+        <v>1.0839999914169312</v>
+      </c>
+      <c r="C1114">
+        <v>1.0850000381469727</v>
+      </c>
+      <c r="D1114">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="E1114">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="F1114">
+        <v>3432404</v>
+      </c>
+      <c r="G1114">
+        <v>34324.0390625</v>
+      </c>
+      <c r="H1114">
+        <f t="shared" si="144"/>
+        <v>1112</v>
+      </c>
+      <c r="I1114">
+        <f>SUM($F$3:F1114)/H1114</f>
+        <v>4185764.7449696492</v>
+      </c>
+      <c r="N1114">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1114">
+        <f t="shared" si="146"/>
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="P1114">
+        <f t="shared" si="143"/>
+        <v>1.0793333450953166</v>
+      </c>
+      <c r="Q1114">
+        <f t="shared" si="132"/>
+        <v>1.0852857118561154</v>
+      </c>
+      <c r="R1114">
+        <f t="shared" si="133"/>
+        <v>-5.9523667607987996E-3</v>
+      </c>
+      <c r="S1114">
+        <f t="shared" si="134"/>
+        <v>4.000002429598859E-3</v>
+      </c>
+      <c r="T1114">
+        <f t="shared" si="135"/>
+        <v>6.0000036443982883E-5</v>
+      </c>
+      <c r="U1114">
+        <f t="shared" si="136"/>
+        <v>-99.206052422252057</v>
+      </c>
+    </row>
+    <row r="1115" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1115" s="1">
+        <v>46048</v>
+      </c>
+      <c r="B1115">
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="C1115">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="D1115">
+        <v>1.0709999799728394</v>
+      </c>
+      <c r="E1115">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="F1115">
+        <v>1126201</v>
+      </c>
+      <c r="G1115">
+        <v>11262.009765625</v>
+      </c>
+      <c r="H1115">
+        <f t="shared" si="144"/>
+        <v>1113</v>
+      </c>
+      <c r="I1115">
+        <f>SUM($F$3:F1115)/H1115</f>
+        <v>4183015.8107872866</v>
+      </c>
+      <c r="N1115">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1115">
+        <f t="shared" si="146"/>
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="P1115">
+        <f t="shared" si="143"/>
+        <v>1.0756666660308838</v>
+      </c>
+      <c r="Q1115">
+        <f t="shared" si="132"/>
+        <v>1.0842619027410234</v>
+      </c>
+      <c r="R1115">
+        <f t="shared" si="133"/>
+        <v>-8.5952367101396199E-3</v>
+      </c>
+      <c r="S1115">
+        <f t="shared" si="134"/>
+        <v>4.3095265116010395E-3</v>
+      </c>
+      <c r="T1115">
+        <f t="shared" si="135"/>
+        <v>6.4642897674015588E-5</v>
+      </c>
+      <c r="U1115">
+        <f t="shared" si="136"/>
+        <v>-132.96490441199134</v>
+      </c>
+    </row>
+    <row r="1116" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1116" s="1">
+        <v>46049</v>
+      </c>
+      <c r="B1116">
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="C1116">
+        <v>1.0789999961853027</v>
+      </c>
+      <c r="D1116">
+        <v>1.062999963760376</v>
+      </c>
+      <c r="E1116">
+        <v>1.0709999799728394</v>
+      </c>
+      <c r="F1116">
+        <v>1934201</v>
+      </c>
+      <c r="G1116">
+        <v>19342.009765625</v>
+      </c>
+      <c r="H1116">
+        <f t="shared" si="144"/>
+        <v>1114</v>
+      </c>
+      <c r="I1116">
+        <f>SUM($F$3:F1116)/H1116</f>
+        <v>4180997.1260379264</v>
+      </c>
+      <c r="N1116">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1116">
+        <f t="shared" si="146"/>
+        <v>1.062999963760376</v>
+      </c>
+      <c r="P1116">
+        <f t="shared" si="143"/>
+        <v>1.0709999799728394</v>
+      </c>
+      <c r="Q1116">
+        <f t="shared" si="132"/>
+        <v>1.0829285695439295</v>
+      </c>
+      <c r="R1116">
+        <f t="shared" si="133"/>
+        <v>-1.1928589571090109E-2</v>
+      </c>
+      <c r="S1116">
+        <f t="shared" si="134"/>
+        <v>4.6802775389483331E-3</v>
+      </c>
+      <c r="T1116">
+        <f t="shared" si="135"/>
+        <v>7.0204163084224992E-5</v>
+      </c>
+      <c r="U1116">
+        <f t="shared" si="136"/>
+        <v>-169.91285198826742</v>
+      </c>
+    </row>
+    <row r="1117" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1117" s="1">
+        <v>46050</v>
+      </c>
+      <c r="B1117">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="C1117">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="D1117">
+        <v>1.065000057220459</v>
+      </c>
+      <c r="E1117">
+        <v>1.0670000314712524</v>
+      </c>
+      <c r="F1117">
+        <v>2403309</v>
+      </c>
+      <c r="G1117">
+        <v>24033.08984375</v>
+      </c>
+      <c r="H1117">
+        <f t="shared" si="144"/>
+        <v>1115</v>
+      </c>
+      <c r="I1117">
+        <f>SUM($F$3:F1117)/H1117</f>
+        <v>4179402.786911435</v>
+      </c>
+      <c r="N1117">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1117">
+        <f t="shared" si="146"/>
+        <v>1.062999963760376</v>
+      </c>
+      <c r="P1117">
+        <f t="shared" si="143"/>
+        <v>1.0693333546320598</v>
+      </c>
+      <c r="Q1117">
+        <f t="shared" si="132"/>
+        <v>1.0821428582781836</v>
+      </c>
+      <c r="R1117">
+        <f t="shared" si="133"/>
+        <v>-1.2809503646123765E-2</v>
+      </c>
+      <c r="S1117">
+        <f t="shared" si="134"/>
+        <v>5.455785057171687E-3</v>
+      </c>
+      <c r="T1117">
+        <f t="shared" si="135"/>
+        <v>8.1836775857575296E-5</v>
+      </c>
+      <c r="U1117">
+        <f t="shared" si="136"/>
+        <v>-156.52502816602643</v>
+      </c>
+    </row>
+    <row r="1118" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1118" s="1">
+        <v>46051</v>
+      </c>
+      <c r="B1118">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="C1118">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="D1118">
+        <v>1.062999963760376</v>
+      </c>
+      <c r="E1118">
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="F1118">
+        <v>2159414</v>
+      </c>
+      <c r="G1118">
+        <v>21594.140625</v>
+      </c>
+      <c r="H1118">
+        <f t="shared" si="144"/>
+        <v>1116</v>
+      </c>
+      <c r="I1118">
+        <f>SUM($F$3:F1118)/H1118</f>
+        <v>4177592.7611167114</v>
+      </c>
+      <c r="N1118">
+        <f t="shared" si="145"/>
+        <v>1.1050000190734863</v>
+      </c>
+      <c r="O1118">
+        <f t="shared" si="146"/>
+        <v>1.062999963760376</v>
+      </c>
+      <c r="P1118">
+        <f t="shared" si="143"/>
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="Q1118">
+        <f t="shared" si="132"/>
+        <v>1.0811666675976344</v>
+      </c>
+      <c r="R1118">
+        <f t="shared" si="133"/>
+        <v>-1.2166661875588458E-2</v>
+      </c>
+      <c r="S1118">
+        <f t="shared" si="134"/>
+        <v>6.357144741784948E-3</v>
+      </c>
+      <c r="T1118">
+        <f t="shared" si="135"/>
+        <v>9.5357171126774211E-5</v>
+      </c>
+      <c r="U1118">
+        <f t="shared" si="136"/>
+        <v>-127.59042379113032</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1118"/>
+  <dimension ref="A1:U1119"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4065,7 +4065,7 @@
         <v>0.82840236686436464</v>
       </c>
     </row>
-    <row r="58" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>44452</v>
       </c>
@@ -4095,6 +4095,12 @@
         <f>SUM($F$3:F58)/H58</f>
         <v>18731862.589285713</v>
       </c>
+      <c r="K58" s="2">
+        <v>46080</v>
+      </c>
+      <c r="L58" s="2">
+        <v>46055</v>
+      </c>
       <c r="N58">
         <f t="shared" si="11"/>
         <v>0.98799999999999999</v>
@@ -65785,23 +65791,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1118" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1119" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1118" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1119" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1118" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1119" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1118" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1119" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1118" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1119" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68931,7 +68937,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1118" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1119" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69041,7 +69047,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1118" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1119" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -69742,11 +69748,11 @@
         <v>4199110.1442679875</v>
       </c>
       <c r="N1100">
-        <f t="shared" ref="N1100:N1118" si="145">IF(A1100&lt;&gt;$K$57,MAX(N1099,VLOOKUP(A1100,A:C,3)),)</f>
+        <f t="shared" ref="N1100:N1119" si="145">IF(A1100&lt;&gt;$K$57,MAX(N1099,VLOOKUP(A1100,A:C,3)),)</f>
         <v>1.0850000381469727</v>
       </c>
       <c r="O1100">
-        <f t="shared" ref="O1100:O1118" si="146">IF(A1100&lt;&gt;$K$57,MIN(O1099,VLOOKUP(A1100,A:D,4)),)</f>
+        <f t="shared" ref="O1100:O1119" si="146">IF(A1100&lt;&gt;$K$57,MIN(O1099,VLOOKUP(A1100,A:D,4)),)</f>
         <v>1.0740000009536743</v>
       </c>
       <c r="P1100">
@@ -70906,6 +70912,69 @@
       <c r="U1118">
         <f t="shared" si="136"/>
         <v>-127.59042379113032</v>
+      </c>
+    </row>
+    <row r="1119" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1119" s="1">
+        <v>46052</v>
+      </c>
+      <c r="B1119">
+        <v>1.0670000314712524</v>
+      </c>
+      <c r="C1119">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="D1119">
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="E1119">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="F1119">
+        <v>3570901.25</v>
+      </c>
+      <c r="G1119">
+        <v>35709.01171875</v>
+      </c>
+      <c r="H1119">
+        <f t="shared" si="144"/>
+        <v>1117</v>
+      </c>
+      <c r="I1119">
+        <f>SUM($F$3:F1119)/H1119</f>
+        <v>4177049.6174183078</v>
+      </c>
+      <c r="N1119">
+        <f t="shared" si="145"/>
+        <v>0</v>
+      </c>
+      <c r="O1119">
+        <f t="shared" si="146"/>
+        <v>0</v>
+      </c>
+      <c r="P1119">
+        <f t="shared" si="143"/>
+        <v>1.0663333336512248</v>
+      </c>
+      <c r="Q1119">
+        <f t="shared" si="132"/>
+        <v>1.0795238103185381</v>
+      </c>
+      <c r="R1119">
+        <f t="shared" si="133"/>
+        <v>-1.3190476667313211E-2</v>
+      </c>
+      <c r="S1119">
+        <f t="shared" si="134"/>
+        <v>6.7619056928725262E-3</v>
+      </c>
+      <c r="T1119">
+        <f t="shared" si="135"/>
+        <v>1.0142858539308789E-4</v>
+      </c>
+      <c r="U1119">
+        <f t="shared" si="136"/>
+        <v>-130.04693515337254</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1119"/>
+  <dimension ref="A1:U1132"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -65791,23 +65791,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1119" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1132" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1119" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1132" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1119" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1132" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1119" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1132" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1119" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1132" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68937,7 +68937,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1119" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1132" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69047,7 +69047,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1119" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1132" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -69748,11 +69748,11 @@
         <v>4199110.1442679875</v>
       </c>
       <c r="N1100">
-        <f t="shared" ref="N1100:N1119" si="145">IF(A1100&lt;&gt;$K$57,MAX(N1099,VLOOKUP(A1100,A:C,3)),)</f>
+        <f t="shared" ref="N1100:N1118" si="145">IF(A1100&lt;&gt;$K$57,MAX(N1099,VLOOKUP(A1100,A:C,3)),)</f>
         <v>1.0850000381469727</v>
       </c>
       <c r="O1100">
-        <f t="shared" ref="O1100:O1119" si="146">IF(A1100&lt;&gt;$K$57,MIN(O1099,VLOOKUP(A1100,A:D,4)),)</f>
+        <f t="shared" ref="O1100:O1118" si="146">IF(A1100&lt;&gt;$K$57,MIN(O1099,VLOOKUP(A1100,A:D,4)),)</f>
         <v>1.0740000009536743</v>
       </c>
       <c r="P1100">
@@ -70945,12 +70945,12 @@
         <v>4177049.6174183078</v>
       </c>
       <c r="N1119">
-        <f t="shared" si="145"/>
-        <v>0</v>
+        <f>VLOOKUP(L58,A:C,3)</f>
+        <v>1.0800000429153442</v>
       </c>
       <c r="O1119">
-        <f t="shared" si="146"/>
-        <v>0</v>
+        <f>VLOOKUP(L58,A:D,4)</f>
+        <v>1.0529999732971191</v>
       </c>
       <c r="P1119">
         <f t="shared" si="143"/>
@@ -70975,6 +70975,825 @@
       <c r="U1119">
         <f t="shared" si="136"/>
         <v>-130.04693515337254</v>
+      </c>
+    </row>
+    <row r="1120" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1120" s="1">
+        <v>46055</v>
+      </c>
+      <c r="B1120">
+        <v>1.0609999895095825</v>
+      </c>
+      <c r="C1120">
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="D1120">
+        <v>1.0529999732971191</v>
+      </c>
+      <c r="E1120">
+        <v>1.0549999475479126</v>
+      </c>
+      <c r="F1120">
+        <v>5174600</v>
+      </c>
+      <c r="G1120">
+        <v>51746</v>
+      </c>
+      <c r="H1120">
+        <f t="shared" si="144"/>
+        <v>1118</v>
+      </c>
+      <c r="I1120">
+        <f>SUM($F$3:F1120)/H1120</f>
+        <v>4177941.8807300986</v>
+      </c>
+      <c r="N1120">
+        <f t="shared" ref="N1120:N1132" si="147">IF(A1120&lt;&gt;$K$58,MAX(N1119,VLOOKUP(A1120,A:C,3)),)</f>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1120">
+        <f t="shared" ref="O1120:O1132" si="148">IF(A1120&lt;&gt;$K$58,MIN(O1119,VLOOKUP(A1120,A:D,4)),)</f>
+        <v>1.0529999732971191</v>
+      </c>
+      <c r="P1120">
+        <f t="shared" si="143"/>
+        <v>1.062666654586792</v>
+      </c>
+      <c r="Q1120">
+        <f t="shared" si="132"/>
+        <v>1.0776904764629545</v>
+      </c>
+      <c r="R1120">
+        <f t="shared" si="133"/>
+        <v>-1.5023821876162469E-2</v>
+      </c>
+      <c r="S1120">
+        <f t="shared" si="134"/>
+        <v>7.448980597411693E-3</v>
+      </c>
+      <c r="T1120">
+        <f t="shared" si="135"/>
+        <v>1.117347089611754E-4</v>
+      </c>
+      <c r="U1120">
+        <f t="shared" si="136"/>
+        <v>-134.45975754394112</v>
+      </c>
+    </row>
+    <row r="1121" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1121" s="1">
+        <v>46056</v>
+      </c>
+      <c r="B1121">
+        <v>1.0659999847412109</v>
+      </c>
+      <c r="C1121">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="D1121">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="E1121">
+        <v>1.0670000314712524</v>
+      </c>
+      <c r="F1121">
+        <v>2039405.125</v>
+      </c>
+      <c r="G1121">
+        <v>20394.05078125</v>
+      </c>
+      <c r="H1121">
+        <f t="shared" si="144"/>
+        <v>1119</v>
+      </c>
+      <c r="I1121">
+        <f>SUM($F$3:F1121)/H1121</f>
+        <v>4176030.7665605452</v>
+      </c>
+      <c r="N1121">
+        <f t="shared" si="147"/>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1121">
+        <f t="shared" si="148"/>
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="P1121">
+        <f t="shared" si="143"/>
+        <v>1.0609999895095825</v>
+      </c>
+      <c r="Q1121">
+        <f t="shared" si="132"/>
+        <v>1.0759523794764563</v>
+      </c>
+      <c r="R1121">
+        <f t="shared" si="133"/>
+        <v>-1.4952389966873758E-2</v>
+      </c>
+      <c r="S1121">
+        <f t="shared" si="134"/>
+        <v>8.0952388899666761E-3</v>
+      </c>
+      <c r="T1121">
+        <f t="shared" si="135"/>
+        <v>1.2142858334950014E-4</v>
+      </c>
+      <c r="U1121">
+        <f t="shared" si="136"/>
+        <v>-123.13731705028007</v>
+      </c>
+    </row>
+    <row r="1122" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1122" s="1">
+        <v>46057</v>
+      </c>
+      <c r="B1122">
+        <v>1.0709999799728394</v>
+      </c>
+      <c r="C1122">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="D1122">
+        <v>1.0549999475479126</v>
+      </c>
+      <c r="E1122">
+        <v>1.0700000524520874</v>
+      </c>
+      <c r="F1122">
+        <v>722400</v>
+      </c>
+      <c r="G1122">
+        <v>7224</v>
+      </c>
+      <c r="H1122">
+        <f t="shared" si="144"/>
+        <v>1120</v>
+      </c>
+      <c r="I1122">
+        <f>SUM($F$3:F1122)/H1122</f>
+        <v>4172947.1676618303</v>
+      </c>
+      <c r="N1122">
+        <f t="shared" si="147"/>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1122">
+        <f t="shared" si="148"/>
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="P1122">
+        <f t="shared" si="143"/>
+        <v>1.065666675567627</v>
+      </c>
+      <c r="Q1122">
+        <f t="shared" si="132"/>
+        <v>1.0745714278448195</v>
+      </c>
+      <c r="R1122">
+        <f t="shared" si="133"/>
+        <v>-8.9047522771925625E-3</v>
+      </c>
+      <c r="S1122">
+        <f t="shared" si="134"/>
+        <v>8.1428573245093828E-3</v>
+      </c>
+      <c r="T1122">
+        <f t="shared" si="135"/>
+        <v>1.2214285986764074E-4</v>
+      </c>
+      <c r="U1122">
+        <f t="shared" si="136"/>
+        <v>-72.90440298223028</v>
+      </c>
+    </row>
+    <row r="1123" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1123" s="1">
+        <v>46058</v>
+      </c>
+      <c r="B1123">
+        <v>1.0670000314712524</v>
+      </c>
+      <c r="C1123">
+        <v>1.0670000314712524</v>
+      </c>
+      <c r="D1123">
+        <v>1.0570000410079956</v>
+      </c>
+      <c r="E1123">
+        <v>1.062999963760376</v>
+      </c>
+      <c r="F1123">
+        <v>2331400</v>
+      </c>
+      <c r="G1123">
+        <v>23314</v>
+      </c>
+      <c r="H1123">
+        <f t="shared" si="144"/>
+        <v>1121</v>
+      </c>
+      <c r="I1123">
+        <f>SUM($F$3:F1123)/H1123</f>
+        <v>4171304.3958797948</v>
+      </c>
+      <c r="N1123">
+        <f t="shared" si="147"/>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1123">
+        <f t="shared" si="148"/>
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="P1123">
+        <f t="shared" si="143"/>
+        <v>1.062333345413208</v>
+      </c>
+      <c r="Q1123">
+        <f t="shared" si="132"/>
+        <v>1.0724047621091206</v>
+      </c>
+      <c r="R1123">
+        <f t="shared" si="133"/>
+        <v>-1.0071416695912605E-2</v>
+      </c>
+      <c r="S1123">
+        <f t="shared" si="134"/>
+        <v>7.4149654025122969E-3</v>
+      </c>
+      <c r="T1123">
+        <f t="shared" si="135"/>
+        <v>1.1122448103768445E-4</v>
+      </c>
+      <c r="U1123">
+        <f t="shared" si="136"/>
+        <v>-90.550359075177568</v>
+      </c>
+    </row>
+    <row r="1124" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1124" s="1">
+        <v>46059</v>
+      </c>
+      <c r="B1124">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="C1124">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="D1124">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="E1124">
+        <v>1.0570000410079956</v>
+      </c>
+      <c r="F1124">
+        <v>1194705</v>
+      </c>
+      <c r="G1124">
+        <v>11947.0498046875</v>
+      </c>
+      <c r="H1124">
+        <f t="shared" si="144"/>
+        <v>1122</v>
+      </c>
+      <c r="I1124">
+        <f>SUM($F$3:F1124)/H1124</f>
+        <v>4168651.4552417556</v>
+      </c>
+      <c r="N1124">
+        <f t="shared" si="147"/>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1124">
+        <f t="shared" si="148"/>
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="P1124">
+        <f t="shared" si="143"/>
+        <v>1.0573333501815796</v>
+      </c>
+      <c r="Q1124">
+        <f t="shared" si="132"/>
+        <v>1.0700952382314772</v>
+      </c>
+      <c r="R1124">
+        <f t="shared" si="133"/>
+        <v>-1.2761888049897641E-2</v>
+      </c>
+      <c r="S1124">
+        <f t="shared" si="134"/>
+        <v>6.7278852268140964E-3</v>
+      </c>
+      <c r="T1124">
+        <f t="shared" si="135"/>
+        <v>1.0091827840221144E-4</v>
+      </c>
+      <c r="U1124">
+        <f t="shared" si="136"/>
+        <v>-126.45764723645927</v>
+      </c>
+    </row>
+    <row r="1125" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1125" s="1">
+        <v>46062</v>
+      </c>
+      <c r="B1125">
+        <v>1.0700000524520874</v>
+      </c>
+      <c r="C1125">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="D1125">
+        <v>1.0590000152587891</v>
+      </c>
+      <c r="E1125">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="F1125">
+        <v>1489601</v>
+      </c>
+      <c r="G1125">
+        <v>14896.009765625</v>
+      </c>
+      <c r="H1125">
+        <f t="shared" si="144"/>
+        <v>1123</v>
+      </c>
+      <c r="I1125">
+        <f>SUM($F$3:F1125)/H1125</f>
+        <v>4166265.8359583705</v>
+      </c>
+      <c r="N1125">
+        <f t="shared" si="147"/>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1125">
+        <f t="shared" si="148"/>
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="P1125">
+        <f t="shared" si="143"/>
+        <v>1.0706666707992554</v>
+      </c>
+      <c r="Q1125">
+        <f t="shared" si="132"/>
+        <v>1.069523811340332</v>
+      </c>
+      <c r="R1125">
+        <f t="shared" si="133"/>
+        <v>1.1428594589233398E-3</v>
+      </c>
+      <c r="S1125">
+        <f t="shared" si="134"/>
+        <v>6.0748259226481071E-3</v>
+      </c>
+      <c r="T1125">
+        <f t="shared" si="135"/>
+        <v>9.1122388839721597E-5</v>
+      </c>
+      <c r="U1125">
+        <f t="shared" si="136"/>
+        <v>12.542026975758459</v>
+      </c>
+    </row>
+    <row r="1126" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1126" s="1">
+        <v>46063</v>
+      </c>
+      <c r="B1126">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C1126">
+        <v>1.0789999961853027</v>
+      </c>
+      <c r="D1126">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="E1126">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="F1126">
+        <v>630800</v>
+      </c>
+      <c r="G1126">
+        <v>6308</v>
+      </c>
+      <c r="H1126">
+        <f t="shared" si="144"/>
+        <v>1124</v>
+      </c>
+      <c r="I1126">
+        <f>SUM($F$3:F1126)/H1126</f>
+        <v>4163120.4037199733</v>
+      </c>
+      <c r="N1126">
+        <f t="shared" si="147"/>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1126">
+        <f t="shared" si="148"/>
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="P1126">
+        <f t="shared" si="143"/>
+        <v>1.0763333241144817</v>
+      </c>
+      <c r="Q1126">
+        <f t="shared" si="132"/>
+        <v>1.0690952397528148</v>
+      </c>
+      <c r="R1126">
+        <f t="shared" si="133"/>
+        <v>7.2380843616668411E-3</v>
+      </c>
+      <c r="S1126">
+        <f t="shared" si="134"/>
+        <v>5.6190462339492176E-3</v>
+      </c>
+      <c r="T1126">
+        <f t="shared" si="135"/>
+        <v>8.428569350923826E-5</v>
+      </c>
+      <c r="U1126">
+        <f t="shared" si="136"/>
+        <v>85.875598340701799</v>
+      </c>
+    </row>
+    <row r="1127" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1127" s="1">
+        <v>46064</v>
+      </c>
+      <c r="B1127">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="C1127">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="D1127">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="E1127">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="F1127">
+        <v>340200</v>
+      </c>
+      <c r="G1127">
+        <v>3402</v>
+      </c>
+      <c r="H1127">
+        <f t="shared" si="144"/>
+        <v>1125</v>
+      </c>
+      <c r="I1127">
+        <f>SUM($F$3:F1127)/H1127</f>
+        <v>4159722.2522499999</v>
+      </c>
+      <c r="N1127">
+        <f t="shared" si="147"/>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1127">
+        <f t="shared" si="148"/>
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="P1127">
+        <f t="shared" si="143"/>
+        <v>1.0706666310628254</v>
+      </c>
+      <c r="Q1127">
+        <f t="shared" si="132"/>
+        <v>1.0683809518814087</v>
+      </c>
+      <c r="R1127">
+        <f t="shared" si="133"/>
+        <v>2.2856791814167554E-3</v>
+      </c>
+      <c r="S1127">
+        <f t="shared" si="134"/>
+        <v>4.993194625491193E-3</v>
+      </c>
+      <c r="T1127">
+        <f t="shared" si="135"/>
+        <v>7.4897919382367896E-5</v>
+      </c>
+      <c r="U1127">
+        <f t="shared" si="136"/>
+        <v>30.517258693768721</v>
+      </c>
+    </row>
+    <row r="1128" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1128" s="1">
+        <v>46065</v>
+      </c>
+      <c r="B1128">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="C1128">
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="D1128">
+        <v>1.0670000314712524</v>
+      </c>
+      <c r="E1128">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="F1128">
+        <v>1218201</v>
+      </c>
+      <c r="G1128">
+        <v>12182.009765625</v>
+      </c>
+      <c r="H1128">
+        <f t="shared" si="144"/>
+        <v>1126</v>
+      </c>
+      <c r="I1128">
+        <f>SUM($F$3:F1128)/H1128</f>
+        <v>4157109.8887932948</v>
+      </c>
+      <c r="N1128">
+        <f t="shared" si="147"/>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1128">
+        <f t="shared" si="148"/>
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="P1128">
+        <f t="shared" si="143"/>
+        <v>1.0730000336964924</v>
+      </c>
+      <c r="Q1128">
+        <f t="shared" si="132"/>
+        <v>1.0679285724957785</v>
+      </c>
+      <c r="R1128">
+        <f t="shared" si="133"/>
+        <v>5.0714612007138893E-3</v>
+      </c>
+      <c r="S1128">
+        <f t="shared" si="134"/>
+        <v>4.6054408663794844E-3</v>
+      </c>
+      <c r="T1128">
+        <f t="shared" si="135"/>
+        <v>6.9081612995692263E-5</v>
+      </c>
+      <c r="U1128">
+        <f t="shared" si="136"/>
+        <v>73.412605479118326</v>
+      </c>
+    </row>
+    <row r="1129" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1129" s="1">
+        <v>46066</v>
+      </c>
+      <c r="B1129">
+        <v>1.065000057220459</v>
+      </c>
+      <c r="C1129">
+        <v>1.0709999799728394</v>
+      </c>
+      <c r="D1129">
+        <v>1.0609999895095825</v>
+      </c>
+      <c r="E1129">
+        <v>1.062000036239624</v>
+      </c>
+      <c r="F1129">
+        <v>1467404</v>
+      </c>
+      <c r="G1129">
+        <v>14674.0400390625</v>
+      </c>
+      <c r="H1129">
+        <f t="shared" si="144"/>
+        <v>1127</v>
+      </c>
+      <c r="I1129">
+        <f>SUM($F$3:F1129)/H1129</f>
+        <v>4154723.2819709405</v>
+      </c>
+      <c r="N1129">
+        <f t="shared" si="147"/>
+        <v>1.0800000429153442</v>
+      </c>
+      <c r="O1129">
+        <f t="shared" si="148"/>
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="P1129">
+        <f t="shared" si="143"/>
+        <v>1.0646666685740154</v>
+      </c>
+      <c r="Q1129">
+        <f t="shared" si="132"/>
+        <v>1.0671428583917164</v>
+      </c>
+      <c r="R1129">
+        <f t="shared" si="133"/>
+        <v>-2.4761898177010355E-3</v>
+      </c>
+      <c r="S1129">
+        <f t="shared" si="134"/>
+        <v>4.2857130368550512E-3</v>
+      </c>
+      <c r="T1129">
+        <f t="shared" si="135"/>
+        <v>6.428569555282577E-5</v>
+      </c>
+      <c r="U1129">
+        <f t="shared" si="136"/>
+        <v>-38.518519499664819</v>
+      </c>
+    </row>
+    <row r="1130" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1130" s="1">
+        <v>46077</v>
+      </c>
+      <c r="B1130">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="C1130">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="D1130">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="E1130">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="F1130">
+        <v>1768400</v>
+      </c>
+      <c r="G1130">
+        <v>17684</v>
+      </c>
+      <c r="H1130">
+        <f t="shared" si="144"/>
+        <v>1128</v>
+      </c>
+      <c r="I1130">
+        <f>SUM($F$3:F1130)/H1130</f>
+        <v>4152607.7471464984</v>
+      </c>
+      <c r="N1130">
+        <f t="shared" si="147"/>
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="O1130">
+        <f t="shared" si="148"/>
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="P1130">
+        <f t="shared" si="143"/>
+        <v>1.0756666660308838</v>
+      </c>
+      <c r="Q1130">
+        <f t="shared" si="132"/>
+        <v>1.0674761931101482</v>
+      </c>
+      <c r="R1130">
+        <f t="shared" si="133"/>
+        <v>8.1904729207356031E-3</v>
+      </c>
+      <c r="S1130">
+        <f t="shared" si="134"/>
+        <v>4.6190477552867969E-3</v>
+      </c>
+      <c r="T1130">
+        <f t="shared" si="135"/>
+        <v>6.9285716329301944E-5</v>
+      </c>
+      <c r="U1130">
+        <f t="shared" si="136"/>
+        <v>118.21300774040972</v>
+      </c>
+    </row>
+    <row r="1131" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1131" s="1">
+        <v>46078</v>
+      </c>
+      <c r="B1131">
+        <v>1.0789999961853027</v>
+      </c>
+      <c r="C1131">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="D1131">
+        <v>1.0789999961853027</v>
+      </c>
+      <c r="E1131">
+        <v>1.0859999656677246</v>
+      </c>
+      <c r="F1131">
+        <v>1020800</v>
+      </c>
+      <c r="G1131">
+        <v>10208</v>
+      </c>
+      <c r="H1131">
+        <f t="shared" si="144"/>
+        <v>1129</v>
+      </c>
+      <c r="I1131">
+        <f>SUM($F$3:F1131)/H1131</f>
+        <v>4149833.781028565</v>
+      </c>
+      <c r="N1131">
+        <f t="shared" si="147"/>
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="O1131">
+        <f t="shared" si="148"/>
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="P1131">
+        <f t="shared" si="143"/>
+        <v>1.0856666564941406</v>
+      </c>
+      <c r="Q1131">
+        <f t="shared" si="132"/>
+        <v>1.0686428575288682</v>
+      </c>
+      <c r="R1131">
+        <f t="shared" si="133"/>
+        <v>1.7023798965272396E-2</v>
+      </c>
+      <c r="S1131">
+        <f t="shared" si="134"/>
+        <v>5.7857121740068551E-3</v>
+      </c>
+      <c r="T1131">
+        <f t="shared" si="135"/>
+        <v>8.6785682610102818E-5</v>
+      </c>
+      <c r="U1131">
+        <f t="shared" si="136"/>
+        <v>196.15907201829899</v>
+      </c>
+    </row>
+    <row r="1132" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1132" s="1">
+        <v>46079</v>
+      </c>
+      <c r="B1132">
+        <v>1.0859999656677246</v>
+      </c>
+      <c r="C1132">
+        <v>1.0889999866485596</v>
+      </c>
+      <c r="D1132">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="E1132">
+        <v>1.0859999656677246</v>
+      </c>
+      <c r="F1132">
+        <v>1815410</v>
+      </c>
+      <c r="G1132">
+        <v>18154.099609375</v>
+      </c>
+      <c r="H1132">
+        <f t="shared" si="144"/>
+        <v>1130</v>
+      </c>
+      <c r="I1132">
+        <f>SUM($F$3:F1132)/H1132</f>
+        <v>4147767.9192754426</v>
+      </c>
+      <c r="N1132">
+        <f t="shared" si="147"/>
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="O1132">
+        <f t="shared" si="148"/>
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="P1132">
+        <f t="shared" si="143"/>
+        <v>1.0843333005905151</v>
+      </c>
+      <c r="Q1132">
+        <f t="shared" si="132"/>
+        <v>1.069738092876616</v>
+      </c>
+      <c r="R1132">
+        <f t="shared" si="133"/>
+        <v>1.4595207713899105E-2</v>
+      </c>
+      <c r="S1132">
+        <f t="shared" si="134"/>
+        <v>6.8809475217546578E-3</v>
+      </c>
+      <c r="T1132">
+        <f t="shared" si="135"/>
+        <v>1.0321421282631986E-4</v>
+      </c>
+      <c r="U1132">
+        <f t="shared" si="136"/>
+        <v>141.40695660256293</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1132"/>
+  <dimension ref="A1:U1133"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4134,7 +4134,7 @@
         <v>-7.3380171740824558</v>
       </c>
     </row>
-    <row r="59" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>44453</v>
       </c>
@@ -4164,6 +4164,12 @@
         <f>SUM($F$3:F59)/H59</f>
         <v>18474303.877192982</v>
       </c>
+      <c r="K59" s="2">
+        <v>46112</v>
+      </c>
+      <c r="L59" s="2">
+        <v>46083</v>
+      </c>
       <c r="N59">
         <f t="shared" si="11"/>
         <v>0.98799999999999999</v>
@@ -65791,23 +65797,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1132" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1133" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1132" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1133" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1132" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1133" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1132" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1133" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1132" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1133" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68937,7 +68943,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1132" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1133" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69047,7 +69053,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1132" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1133" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -71008,11 +71014,11 @@
         <v>4177941.8807300986</v>
       </c>
       <c r="N1120">
-        <f t="shared" ref="N1120:N1132" si="147">IF(A1120&lt;&gt;$K$58,MAX(N1119,VLOOKUP(A1120,A:C,3)),)</f>
+        <f t="shared" ref="N1120:N1133" si="147">IF(A1120&lt;&gt;$K$58,MAX(N1119,VLOOKUP(A1120,A:C,3)),)</f>
         <v>1.0800000429153442</v>
       </c>
       <c r="O1120">
-        <f t="shared" ref="O1120:O1132" si="148">IF(A1120&lt;&gt;$K$58,MIN(O1119,VLOOKUP(A1120,A:D,4)),)</f>
+        <f t="shared" ref="O1120:O1133" si="148">IF(A1120&lt;&gt;$K$58,MIN(O1119,VLOOKUP(A1120,A:D,4)),)</f>
         <v>1.0529999732971191</v>
       </c>
       <c r="P1120">
@@ -71794,6 +71800,69 @@
       <c r="U1132">
         <f t="shared" si="136"/>
         <v>141.40695660256293</v>
+      </c>
+    </row>
+    <row r="1133" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1133" s="1">
+        <v>46080</v>
+      </c>
+      <c r="B1133">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="C1133">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="D1133">
+        <v>1.0700000524520874</v>
+      </c>
+      <c r="E1133">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="F1133">
+        <v>1968100</v>
+      </c>
+      <c r="G1133">
+        <v>19681</v>
+      </c>
+      <c r="H1133">
+        <f t="shared" si="144"/>
+        <v>1131</v>
+      </c>
+      <c r="I1133">
+        <f>SUM($F$3:F1133)/H1133</f>
+        <v>4145840.7151027853</v>
+      </c>
+      <c r="N1133">
+        <f t="shared" si="147"/>
+        <v>0</v>
+      </c>
+      <c r="O1133">
+        <f t="shared" si="148"/>
+        <v>0</v>
+      </c>
+      <c r="P1133">
+        <f t="shared" si="143"/>
+        <v>1.0743333498636882</v>
+      </c>
+      <c r="Q1133">
+        <f t="shared" si="132"/>
+        <v>1.0703095226060777</v>
+      </c>
+      <c r="R1133">
+        <f t="shared" si="133"/>
+        <v>4.0238272576105238E-3</v>
+      </c>
+      <c r="S1133">
+        <f t="shared" si="134"/>
+        <v>6.8843502576659199E-3</v>
+      </c>
+      <c r="T1133">
+        <f t="shared" si="135"/>
+        <v>1.032652538649888E-4</v>
+      </c>
+      <c r="U1133">
+        <f t="shared" si="136"/>
+        <v>38.965935849742465</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1133"/>
+  <dimension ref="A1:U1154"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -65797,23 +65797,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1133" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1154" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1133" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1154" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1133" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1154" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1133" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1154" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1133" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1154" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68943,7 +68943,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1133" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1154" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69053,7 +69053,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1133" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1154" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -71014,11 +71014,11 @@
         <v>4177941.8807300986</v>
       </c>
       <c r="N1120">
-        <f t="shared" ref="N1120:N1133" si="147">IF(A1120&lt;&gt;$K$58,MAX(N1119,VLOOKUP(A1120,A:C,3)),)</f>
+        <f t="shared" ref="N1120:N1132" si="147">IF(A1120&lt;&gt;$K$58,MAX(N1119,VLOOKUP(A1120,A:C,3)),)</f>
         <v>1.0800000429153442</v>
       </c>
       <c r="O1120">
-        <f t="shared" ref="O1120:O1133" si="148">IF(A1120&lt;&gt;$K$58,MIN(O1119,VLOOKUP(A1120,A:D,4)),)</f>
+        <f t="shared" ref="O1120:O1132" si="148">IF(A1120&lt;&gt;$K$58,MIN(O1119,VLOOKUP(A1120,A:D,4)),)</f>
         <v>1.0529999732971191</v>
       </c>
       <c r="P1120">
@@ -71833,12 +71833,12 @@
         <v>4145840.7151027853</v>
       </c>
       <c r="N1133">
-        <f t="shared" si="147"/>
-        <v>0</v>
+        <f>VLOOKUP(L59,A:C,3)</f>
+        <v>1.0789999961853027</v>
       </c>
       <c r="O1133">
-        <f t="shared" si="148"/>
-        <v>0</v>
+        <f>VLOOKUP(L59,A:D,4)</f>
+        <v>1.0570000410079956</v>
       </c>
       <c r="P1133">
         <f t="shared" si="143"/>
@@ -71863,6 +71863,1329 @@
       <c r="U1133">
         <f t="shared" si="136"/>
         <v>38.965935849742465</v>
+      </c>
+    </row>
+    <row r="1134" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1134" s="1">
+        <v>46083</v>
+      </c>
+      <c r="B1134">
+        <v>1.0570000410079956</v>
+      </c>
+      <c r="C1134">
+        <v>1.0789999961853027</v>
+      </c>
+      <c r="D1134">
+        <v>1.0570000410079956</v>
+      </c>
+      <c r="E1134">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="F1134">
+        <v>6311015</v>
+      </c>
+      <c r="G1134">
+        <v>63110.1484375</v>
+      </c>
+      <c r="H1134">
+        <f t="shared" si="144"/>
+        <v>1132</v>
+      </c>
+      <c r="I1134">
+        <f>SUM($F$3:F1134)/H1134</f>
+        <v>4147753.41323432</v>
+      </c>
+      <c r="N1134">
+        <f t="shared" ref="N1134:N1154" si="149">IF(A1134&lt;&gt;$K$59,MAX(N1133,VLOOKUP(A1134,A:C,3)),)</f>
+        <v>1.0789999961853027</v>
+      </c>
+      <c r="O1134">
+        <f t="shared" ref="O1134:O1154" si="150">IF(A1134&lt;&gt;$K$59,MIN(O1133,VLOOKUP(A1134,A:D,4)),)</f>
+        <v>1.0570000410079956</v>
+      </c>
+      <c r="P1134">
+        <f t="shared" si="143"/>
+        <v>1.0706666707992554</v>
+      </c>
+      <c r="Q1134">
+        <f t="shared" si="132"/>
+        <v>1.0708809523355394</v>
+      </c>
+      <c r="R1134">
+        <f t="shared" si="133"/>
+        <v>-2.1428153628400004E-4</v>
+      </c>
+      <c r="S1134">
+        <f t="shared" si="134"/>
+        <v>6.2925166824237145E-3</v>
+      </c>
+      <c r="T1134">
+        <f t="shared" si="135"/>
+        <v>9.4387750236355709E-5</v>
+      </c>
+      <c r="U1134">
+        <f t="shared" si="136"/>
+        <v>-2.2702261230659606</v>
+      </c>
+    </row>
+    <row r="1135" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1135" s="1">
+        <v>46084</v>
+      </c>
+      <c r="B1135">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="C1135">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="D1135">
+        <v>1.0540000200271606</v>
+      </c>
+      <c r="E1135">
+        <v>1.0540000200271606</v>
+      </c>
+      <c r="F1135">
+        <v>2741414</v>
+      </c>
+      <c r="G1135">
+        <v>27414.140625</v>
+      </c>
+      <c r="H1135">
+        <f t="shared" si="144"/>
+        <v>1133</v>
+      </c>
+      <c r="I1135">
+        <f>SUM($F$3:F1135)/H1135</f>
+        <v>4146512.1604424096</v>
+      </c>
+      <c r="N1135">
+        <f t="shared" si="149"/>
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="O1135">
+        <f t="shared" si="150"/>
+        <v>1.0540000200271606</v>
+      </c>
+      <c r="P1135">
+        <f t="shared" si="143"/>
+        <v>1.0633333524068196</v>
+      </c>
+      <c r="Q1135">
+        <f t="shared" si="132"/>
+        <v>1.0710476211139135</v>
+      </c>
+      <c r="R1135">
+        <f t="shared" si="133"/>
+        <v>-7.7142687070939076E-3</v>
+      </c>
+      <c r="S1135">
+        <f t="shared" si="134"/>
+        <v>6.1496577295316558E-3</v>
+      </c>
+      <c r="T1135">
+        <f t="shared" si="135"/>
+        <v>9.224486594297483E-5</v>
+      </c>
+      <c r="U1135">
+        <f t="shared" si="136"/>
+        <v>-83.628163239597725</v>
+      </c>
+    </row>
+    <row r="1136" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1136" s="1">
+        <v>46085</v>
+      </c>
+      <c r="B1136">
+        <v>1.0540000200271606</v>
+      </c>
+      <c r="C1136">
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="D1136">
+        <v>1.0360000133514404</v>
+      </c>
+      <c r="E1136">
+        <v>1.0429999828338623</v>
+      </c>
+      <c r="F1136">
+        <v>4072510.25</v>
+      </c>
+      <c r="G1136">
+        <v>40725.1015625</v>
+      </c>
+      <c r="H1136">
+        <f t="shared" si="144"/>
+        <v>1134</v>
+      </c>
+      <c r="I1136">
+        <f>SUM($F$3:F1136)/H1136</f>
+        <v>4146446.9030257938</v>
+      </c>
+      <c r="N1136">
+        <f t="shared" si="149"/>
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="O1136">
+        <f t="shared" si="150"/>
+        <v>1.0360000133514404</v>
+      </c>
+      <c r="P1136">
+        <f t="shared" si="143"/>
+        <v>1.0590000152587891</v>
+      </c>
+      <c r="Q1136">
+        <f t="shared" si="132"/>
+        <v>1.0705714310918535</v>
+      </c>
+      <c r="R1136">
+        <f t="shared" si="133"/>
+        <v>-1.1571415833064425E-2</v>
+      </c>
+      <c r="S1136">
+        <f t="shared" si="134"/>
+        <v>6.5986319464080368E-3</v>
+      </c>
+      <c r="T1136">
+        <f t="shared" si="135"/>
+        <v>9.8979479196120544E-5</v>
+      </c>
+      <c r="U1136">
+        <f t="shared" si="136"/>
+        <v>-116.90722084055946</v>
+      </c>
+    </row>
+    <row r="1137" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1137" s="1">
+        <v>46086</v>
+      </c>
+      <c r="B1137">
+        <v>1.0570000410079956</v>
+      </c>
+      <c r="C1137">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="D1137">
+        <v>1.0529999732971191</v>
+      </c>
+      <c r="E1137">
+        <v>1.0559999942779541</v>
+      </c>
+      <c r="F1137">
+        <v>2136511</v>
+      </c>
+      <c r="G1137">
+        <v>21365.109375</v>
+      </c>
+      <c r="H1137">
+        <f t="shared" si="144"/>
+        <v>1135</v>
+      </c>
+      <c r="I1137">
+        <f>SUM($F$3:F1137)/H1137</f>
+        <v>4144676.0343887666</v>
+      </c>
+      <c r="N1137">
+        <f t="shared" si="149"/>
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="O1137">
+        <f t="shared" si="150"/>
+        <v>1.0360000133514404</v>
+      </c>
+      <c r="P1137">
+        <f t="shared" si="143"/>
+        <v>1.0589999755223591</v>
+      </c>
+      <c r="Q1137">
+        <f t="shared" si="132"/>
+        <v>1.0703333332425073</v>
+      </c>
+      <c r="R1137">
+        <f t="shared" si="133"/>
+        <v>-1.1333357720148207E-2</v>
+      </c>
+      <c r="S1137">
+        <f t="shared" si="134"/>
+        <v>6.9047577527104253E-3</v>
+      </c>
+      <c r="T1137">
+        <f t="shared" si="135"/>
+        <v>1.0357136629065638E-4</v>
+      </c>
+      <c r="U1137">
+        <f t="shared" si="136"/>
+        <v>-109.42558861628765</v>
+      </c>
+    </row>
+    <row r="1138" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1138" s="1">
+        <v>46087</v>
+      </c>
+      <c r="B1138">
+        <v>1.0509999990463257</v>
+      </c>
+      <c r="C1138">
+        <v>1.0670000314712524</v>
+      </c>
+      <c r="D1138">
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="E1138">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="F1138">
+        <v>2197001</v>
+      </c>
+      <c r="G1138">
+        <v>21970.009765625</v>
+      </c>
+      <c r="H1138">
+        <f t="shared" si="144"/>
+        <v>1136</v>
+      </c>
+      <c r="I1138">
+        <f>SUM($F$3:F1138)/H1138</f>
+        <v>4142961.5317176497</v>
+      </c>
+      <c r="N1138">
+        <f t="shared" si="149"/>
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="O1138">
+        <f t="shared" si="150"/>
+        <v>1.0360000133514404</v>
+      </c>
+      <c r="P1138">
+        <f t="shared" si="143"/>
+        <v>1.0603333314259846</v>
+      </c>
+      <c r="Q1138">
+        <f t="shared" si="132"/>
+        <v>1.0705476176171076</v>
+      </c>
+      <c r="R1138">
+        <f t="shared" si="133"/>
+        <v>-1.0214286191122968E-2</v>
+      </c>
+      <c r="S1138">
+        <f t="shared" si="134"/>
+        <v>6.6292492710814232E-3</v>
+      </c>
+      <c r="T1138">
+        <f t="shared" si="135"/>
+        <v>9.9438739066221341E-5</v>
+      </c>
+      <c r="U1138">
+        <f t="shared" si="136"/>
+        <v>-102.71938569455061</v>
+      </c>
+    </row>
+    <row r="1139" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1139" s="1">
+        <v>46090</v>
+      </c>
+      <c r="B1139">
+        <v>1.0549999475479126</v>
+      </c>
+      <c r="C1139">
+        <v>1.0559999942779541</v>
+      </c>
+      <c r="D1139">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="E1139">
+        <v>1.0509999990463257</v>
+      </c>
+      <c r="F1139">
+        <v>1665600</v>
+      </c>
+      <c r="G1139">
+        <v>16656</v>
+      </c>
+      <c r="H1139">
+        <f t="shared" si="144"/>
+        <v>1137</v>
+      </c>
+      <c r="I1139">
+        <f>SUM($F$3:F1139)/H1139</f>
+        <v>4140782.6737302109</v>
+      </c>
+      <c r="N1139">
+        <f t="shared" si="149"/>
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="O1139">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1139">
+        <f t="shared" si="143"/>
+        <v>1.0460000038146973</v>
+      </c>
+      <c r="Q1139">
+        <f t="shared" si="132"/>
+        <v>1.0687857128324965</v>
+      </c>
+      <c r="R1139">
+        <f t="shared" si="133"/>
+        <v>-2.2785709017799194E-2</v>
+      </c>
+      <c r="S1139">
+        <f t="shared" si="134"/>
+        <v>8.6258471417589109E-3</v>
+      </c>
+      <c r="T1139">
+        <f t="shared" si="135"/>
+        <v>1.2938770712638367E-4</v>
+      </c>
+      <c r="U1139">
+        <f t="shared" si="136"/>
+        <v>-176.1041255298118</v>
+      </c>
+    </row>
+    <row r="1140" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1140" s="1">
+        <v>46091</v>
+      </c>
+      <c r="B1140">
+        <v>1.0590000152587891</v>
+      </c>
+      <c r="C1140">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="D1140">
+        <v>1.0559999942779541</v>
+      </c>
+      <c r="E1140">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="F1140">
+        <v>2434414</v>
+      </c>
+      <c r="G1140">
+        <v>24344.140625</v>
+      </c>
+      <c r="H1140">
+        <f t="shared" si="144"/>
+        <v>1138</v>
+      </c>
+      <c r="I1140">
+        <f>SUM($F$3:F1140)/H1140</f>
+        <v>4139283.2284984621</v>
+      </c>
+      <c r="N1140">
+        <f t="shared" si="149"/>
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="O1140">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1140">
+        <f t="shared" si="143"/>
+        <v>1.0699999729792278</v>
+      </c>
+      <c r="Q1140">
+        <f t="shared" si="132"/>
+        <v>1.0683333306085496</v>
+      </c>
+      <c r="R1140">
+        <f t="shared" si="133"/>
+        <v>1.6666423706781508E-3</v>
+      </c>
+      <c r="S1140">
+        <f t="shared" si="134"/>
+        <v>8.2380909498046082E-3</v>
+      </c>
+      <c r="T1140">
+        <f t="shared" si="135"/>
+        <v>1.2357136424706911E-4</v>
+      </c>
+      <c r="U1140">
+        <f t="shared" si="136"/>
+        <v>13.487286321010901</v>
+      </c>
+    </row>
+    <row r="1141" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1141" s="1">
+        <v>46092</v>
+      </c>
+      <c r="B1141">
+        <v>1.0789999961853027</v>
+      </c>
+      <c r="C1141">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="D1141">
+        <v>1.0789999961853027</v>
+      </c>
+      <c r="E1141">
+        <v>1.0880000591278076</v>
+      </c>
+      <c r="F1141">
+        <v>1632302</v>
+      </c>
+      <c r="G1141">
+        <v>16323.01953125</v>
+      </c>
+      <c r="H1141">
+        <f t="shared" si="144"/>
+        <v>1139</v>
+      </c>
+      <c r="I1141">
+        <f>SUM($F$3:F1141)/H1141</f>
+        <v>4137082.1914233975</v>
+      </c>
+      <c r="N1141">
+        <f t="shared" si="149"/>
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="O1141">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1141">
+        <f t="shared" si="143"/>
+        <v>1.0866667032241821</v>
+      </c>
+      <c r="Q1141">
+        <f t="shared" si="132"/>
+        <v>1.0694761929057894</v>
+      </c>
+      <c r="R1141">
+        <f t="shared" si="133"/>
+        <v>1.7190510318392693E-2</v>
+      </c>
+      <c r="S1141">
+        <f t="shared" si="134"/>
+        <v>9.2176872045815397E-3</v>
+      </c>
+      <c r="T1141">
+        <f t="shared" si="135"/>
+        <v>1.3826530806872308E-4</v>
+      </c>
+      <c r="U1141">
+        <f t="shared" si="136"/>
+        <v>124.32988837553062</v>
+      </c>
+    </row>
+    <row r="1142" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1142" s="1">
+        <v>46093</v>
+      </c>
+      <c r="B1142">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="C1142">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="D1142">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="E1142">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="F1142">
+        <v>1582402</v>
+      </c>
+      <c r="G1142">
+        <v>15824.01953125</v>
+      </c>
+      <c r="H1142">
+        <f t="shared" si="144"/>
+        <v>1140</v>
+      </c>
+      <c r="I1142">
+        <f>SUM($F$3:F1142)/H1142</f>
+        <v>4134841.2438870613</v>
+      </c>
+      <c r="N1142">
+        <f t="shared" si="149"/>
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="O1142">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1142">
+        <f t="shared" si="143"/>
+        <v>1.0826666752497356</v>
+      </c>
+      <c r="Q1142">
+        <f t="shared" si="132"/>
+        <v>1.0701666673024497</v>
+      </c>
+      <c r="R1142">
+        <f t="shared" si="133"/>
+        <v>1.2500007947285896E-2</v>
+      </c>
+      <c r="S1142">
+        <f t="shared" si="134"/>
+        <v>9.8333358764648594E-3</v>
+      </c>
+      <c r="T1142">
+        <f t="shared" si="135"/>
+        <v>1.4750003814697289E-4</v>
+      </c>
+      <c r="U1142">
+        <f t="shared" si="136"/>
+        <v>84.745794674510947</v>
+      </c>
+    </row>
+    <row r="1143" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1143" s="1">
+        <v>46094</v>
+      </c>
+      <c r="B1143">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="C1143">
+        <v>1.0900000333786011</v>
+      </c>
+      <c r="D1143">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="E1143">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="F1143">
+        <v>785000</v>
+      </c>
+      <c r="G1143">
+        <v>7850</v>
+      </c>
+      <c r="H1143">
+        <f t="shared" si="144"/>
+        <v>1141</v>
+      </c>
+      <c r="I1143">
+        <f>SUM($F$3:F1143)/H1143</f>
+        <v>4131905.3619905785</v>
+      </c>
+      <c r="N1143">
+        <f t="shared" si="149"/>
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="O1143">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1143">
+        <f t="shared" si="143"/>
+        <v>1.0833333333333333</v>
+      </c>
+      <c r="Q1143">
+        <f t="shared" si="132"/>
+        <v>1.0715000004995436</v>
+      </c>
+      <c r="R1143">
+        <f t="shared" si="133"/>
+        <v>1.1833332833789623E-2</v>
+      </c>
+      <c r="S1143">
+        <f t="shared" si="134"/>
+        <v>1.0309525898524709E-2</v>
+      </c>
+      <c r="T1143">
+        <f t="shared" si="135"/>
+        <v>1.5464288847787065E-4</v>
+      </c>
+      <c r="U1143">
+        <f t="shared" si="136"/>
+        <v>76.520381572431432</v>
+      </c>
+    </row>
+    <row r="1144" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1144" s="1">
+        <v>46097</v>
+      </c>
+      <c r="B1144">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="C1144">
+        <v>1.090999960899353</v>
+      </c>
+      <c r="D1144">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="E1144">
+        <v>1.0900000333786011</v>
+      </c>
+      <c r="F1144">
+        <v>1282200</v>
+      </c>
+      <c r="G1144">
+        <v>12822</v>
+      </c>
+      <c r="H1144">
+        <f t="shared" si="144"/>
+        <v>1142</v>
+      </c>
+      <c r="I1144">
+        <f>SUM($F$3:F1144)/H1144</f>
+        <v>4129409.9982760507</v>
+      </c>
+      <c r="N1144">
+        <f t="shared" si="149"/>
+        <v>1.0980000495910645</v>
+      </c>
+      <c r="O1144">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1144">
+        <f t="shared" si="143"/>
+        <v>1.0853333473205566</v>
+      </c>
+      <c r="Q1144">
+        <f t="shared" si="132"/>
+        <v>1.0721904777345201</v>
+      </c>
+      <c r="R1144">
+        <f t="shared" si="133"/>
+        <v>1.3142869586036499E-2</v>
+      </c>
+      <c r="S1144">
+        <f t="shared" si="134"/>
+        <v>1.1000003133501341E-2</v>
+      </c>
+      <c r="T1144">
+        <f t="shared" si="135"/>
+        <v>1.6500004700252012E-4</v>
+      </c>
+      <c r="U1144">
+        <f t="shared" si="136"/>
+        <v>79.653732376426305</v>
+      </c>
+    </row>
+    <row r="1145" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1145" s="1">
+        <v>46098</v>
+      </c>
+      <c r="B1145">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="C1145">
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="D1145">
+        <v>1.0759999752044678</v>
+      </c>
+      <c r="E1145">
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="F1145">
+        <v>2947526</v>
+      </c>
+      <c r="G1145">
+        <v>29475.259765625</v>
+      </c>
+      <c r="H1145">
+        <f t="shared" si="144"/>
+        <v>1143</v>
+      </c>
+      <c r="I1145">
+        <f>SUM($F$3:F1145)/H1145</f>
+        <v>4128375.9790299651</v>
+      </c>
+      <c r="N1145">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1145">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1145">
+        <f t="shared" si="143"/>
+        <v>1.0849999984105427</v>
+      </c>
+      <c r="Q1145">
+        <f t="shared" si="132"/>
+        <v>1.0721428592999775</v>
+      </c>
+      <c r="R1145">
+        <f t="shared" si="133"/>
+        <v>1.2857139110565186E-2</v>
+      </c>
+      <c r="S1145">
+        <f t="shared" si="134"/>
+        <v>1.0952384698958635E-2</v>
+      </c>
+      <c r="T1145">
+        <f t="shared" si="135"/>
+        <v>1.6428577048437952E-4</v>
+      </c>
+      <c r="U1145">
+        <f t="shared" si="136"/>
+        <v>78.260819988592118</v>
+      </c>
+    </row>
+    <row r="1146" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1146" s="1">
+        <v>46099</v>
+      </c>
+      <c r="B1146">
+        <v>1.0729999542236328</v>
+      </c>
+      <c r="C1146">
+        <v>1.0880000591278076</v>
+      </c>
+      <c r="D1146">
+        <v>1.0700000524520874</v>
+      </c>
+      <c r="E1146">
+        <v>1.0870000123977661</v>
+      </c>
+      <c r="F1146">
+        <v>2248502</v>
+      </c>
+      <c r="G1146">
+        <v>22485.01953125</v>
+      </c>
+      <c r="H1146">
+        <f t="shared" si="144"/>
+        <v>1144</v>
+      </c>
+      <c r="I1146">
+        <f>SUM($F$3:F1146)/H1146</f>
+        <v>4126732.7325447989</v>
+      </c>
+      <c r="N1146">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1146">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1146">
+        <f t="shared" si="143"/>
+        <v>1.0816667079925537</v>
+      </c>
+      <c r="Q1146">
+        <f t="shared" si="132"/>
+        <v>1.0719523884001232</v>
+      </c>
+      <c r="R1146">
+        <f t="shared" si="133"/>
+        <v>9.7143195924305203E-3</v>
+      </c>
+      <c r="S1146">
+        <f t="shared" si="134"/>
+        <v>1.0761913799104248E-2</v>
+      </c>
+      <c r="T1146">
+        <f t="shared" si="135"/>
+        <v>1.6142870698656372E-4</v>
+      </c>
+      <c r="U1146">
+        <f t="shared" si="136"/>
+        <v>60.1771504819095</v>
+      </c>
+    </row>
+    <row r="1147" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1147" s="1">
+        <v>46100</v>
+      </c>
+      <c r="B1147">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="C1147">
+        <v>1.0920000076293945</v>
+      </c>
+      <c r="D1147">
+        <v>1.0670000314712524</v>
+      </c>
+      <c r="E1147">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="F1147">
+        <v>2220003</v>
+      </c>
+      <c r="G1147">
+        <v>22200.029296875</v>
+      </c>
+      <c r="H1147">
+        <f t="shared" si="144"/>
+        <v>1145</v>
+      </c>
+      <c r="I1147">
+        <f>SUM($F$3:F1147)/H1147</f>
+        <v>4125067.4664028385</v>
+      </c>
+      <c r="N1147">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1147">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1147">
+        <f t="shared" si="143"/>
+        <v>1.0770000219345093</v>
+      </c>
+      <c r="Q1147">
+        <f t="shared" si="132"/>
+        <v>1.0721428649766105</v>
+      </c>
+      <c r="R1147">
+        <f t="shared" si="133"/>
+        <v>4.8571569578987894E-3</v>
+      </c>
+      <c r="S1147">
+        <f t="shared" si="134"/>
+        <v>1.0952390375591465E-2</v>
+      </c>
+      <c r="T1147">
+        <f t="shared" si="135"/>
+        <v>1.6428585563387199E-4</v>
+      </c>
+      <c r="U1147">
+        <f t="shared" si="136"/>
+        <v>29.56527778461626</v>
+      </c>
+    </row>
+    <row r="1148" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1148" s="1">
+        <v>46101</v>
+      </c>
+      <c r="B1148">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="C1148">
+        <v>1.093000054359436</v>
+      </c>
+      <c r="D1148">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="E1148">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="F1148">
+        <v>2063001</v>
+      </c>
+      <c r="G1148">
+        <v>20630.009765625</v>
+      </c>
+      <c r="H1148">
+        <f t="shared" si="144"/>
+        <v>1146</v>
+      </c>
+      <c r="I1148">
+        <f>SUM($F$3:F1148)/H1148</f>
+        <v>4123268.1064845114</v>
+      </c>
+      <c r="N1148">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1148">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1148">
+        <f t="shared" si="143"/>
+        <v>1.0816666682561238</v>
+      </c>
+      <c r="Q1148">
+        <f t="shared" si="132"/>
+        <v>1.0729285790806726</v>
+      </c>
+      <c r="R1148">
+        <f t="shared" si="133"/>
+        <v>8.738089175451158E-3</v>
+      </c>
+      <c r="S1148">
+        <f t="shared" si="134"/>
+        <v>1.1414974725165315E-2</v>
+      </c>
+      <c r="T1148">
+        <f t="shared" si="135"/>
+        <v>1.712246208774797E-4</v>
+      </c>
+      <c r="U1148">
+        <f t="shared" si="136"/>
+        <v>51.032901288791429</v>
+      </c>
+    </row>
+    <row r="1149" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1149" s="1">
+        <v>46104</v>
+      </c>
+      <c r="B1149">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="C1149">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="D1149">
+        <v>1.0410000085830688</v>
+      </c>
+      <c r="E1149">
+        <v>1.0410000085830688</v>
+      </c>
+      <c r="F1149">
+        <v>5032603</v>
+      </c>
+      <c r="G1149">
+        <v>50326.03125</v>
+      </c>
+      <c r="H1149">
+        <f t="shared" si="144"/>
+        <v>1147</v>
+      </c>
+      <c r="I1149">
+        <f>SUM($F$3:F1149)/H1149</f>
+        <v>4124060.9006375326</v>
+      </c>
+      <c r="N1149">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1149">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1149">
+        <f t="shared" si="143"/>
+        <v>1.053333322207133</v>
+      </c>
+      <c r="Q1149">
+        <f t="shared" si="132"/>
+        <v>1.0722142912092665</v>
+      </c>
+      <c r="R1149">
+        <f t="shared" si="133"/>
+        <v>-1.888096900213343E-2</v>
+      </c>
+      <c r="S1149">
+        <f t="shared" si="134"/>
+        <v>1.2231303721058089E-2</v>
+      </c>
+      <c r="T1149">
+        <f t="shared" si="135"/>
+        <v>1.8346955581587132E-4</v>
+      </c>
+      <c r="U1149">
+        <f t="shared" si="136"/>
+        <v>-102.91063777950293</v>
+      </c>
+    </row>
+    <row r="1150" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1150" s="1">
+        <v>46105</v>
+      </c>
+      <c r="B1150">
+        <v>1.0499999523162842</v>
+      </c>
+      <c r="C1150">
+        <v>1.0549999475479126</v>
+      </c>
+      <c r="D1150">
+        <v>1.0329999923706055</v>
+      </c>
+      <c r="E1150">
+        <v>1.0549999475479126</v>
+      </c>
+      <c r="F1150">
+        <v>2242601</v>
+      </c>
+      <c r="G1150">
+        <v>22426.009765625</v>
+      </c>
+      <c r="H1150">
+        <f t="shared" si="144"/>
+        <v>1148</v>
+      </c>
+      <c r="I1150">
+        <f>SUM($F$3:F1150)/H1150</f>
+        <v>4122421.9982850607</v>
+      </c>
+      <c r="N1150">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1150">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1150">
+        <f t="shared" si="143"/>
+        <v>1.0476666291554768</v>
+      </c>
+      <c r="Q1150">
+        <f t="shared" si="132"/>
+        <v>1.0714047636304582</v>
+      </c>
+      <c r="R1150">
+        <f t="shared" si="133"/>
+        <v>-2.3738134474981409E-2</v>
+      </c>
+      <c r="S1150">
+        <f t="shared" si="134"/>
+        <v>1.3156478096838715E-2</v>
+      </c>
+      <c r="T1150">
+        <f t="shared" si="135"/>
+        <v>1.9734717145258071E-4</v>
+      </c>
+      <c r="U1150">
+        <f t="shared" si="136"/>
+        <v>-120.28616523994768</v>
+      </c>
+    </row>
+    <row r="1151" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1151" s="1">
+        <v>46106</v>
+      </c>
+      <c r="B1151">
+        <v>1.0579999685287476</v>
+      </c>
+      <c r="C1151">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="D1151">
+        <v>1.0579999685287476</v>
+      </c>
+      <c r="E1151">
+        <v>1.0740000009536743</v>
+      </c>
+      <c r="F1151">
+        <v>1546200</v>
+      </c>
+      <c r="G1151">
+        <v>15462</v>
+      </c>
+      <c r="H1151">
+        <f t="shared" si="144"/>
+        <v>1149</v>
+      </c>
+      <c r="I1151">
+        <f>SUM($F$3:F1151)/H1151</f>
+        <v>4120179.8555537425</v>
+      </c>
+      <c r="N1151">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1151">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1151">
+        <f t="shared" si="143"/>
+        <v>1.068666656812032</v>
+      </c>
+      <c r="Q1151">
+        <f t="shared" si="132"/>
+        <v>1.072095240865435</v>
+      </c>
+      <c r="R1151">
+        <f t="shared" si="133"/>
+        <v>-3.428584053402961E-3</v>
+      </c>
+      <c r="S1151">
+        <f t="shared" si="134"/>
+        <v>1.2367361256865408E-2</v>
+      </c>
+      <c r="T1151">
+        <f t="shared" si="135"/>
+        <v>1.8551041885298111E-4</v>
+      </c>
+      <c r="U1151">
+        <f t="shared" si="136"/>
+        <v>-18.481894842360035</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1152" s="1">
+        <v>46107</v>
+      </c>
+      <c r="B1152">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="C1152">
+        <v>1.0750000476837158</v>
+      </c>
+      <c r="D1152">
+        <v>1.0570000410079956</v>
+      </c>
+      <c r="E1152">
+        <v>1.0590000152587891</v>
+      </c>
+      <c r="F1152">
+        <v>1461400</v>
+      </c>
+      <c r="G1152">
+        <v>14614</v>
+      </c>
+      <c r="H1152">
+        <f t="shared" si="144"/>
+        <v>1150</v>
+      </c>
+      <c r="I1152">
+        <f>SUM($F$3:F1152)/H1152</f>
+        <v>4117867.8730706521</v>
+      </c>
+      <c r="N1152">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1152">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1152">
+        <f t="shared" si="143"/>
+        <v>1.0636667013168335</v>
+      </c>
+      <c r="Q1152">
+        <f t="shared" si="132"/>
+        <v>1.0723333387147813</v>
+      </c>
+      <c r="R1152">
+        <f t="shared" si="133"/>
+        <v>-8.6666373979478184E-3</v>
+      </c>
+      <c r="S1152">
+        <f t="shared" si="134"/>
+        <v>1.2095249429041008E-2</v>
+      </c>
+      <c r="T1152">
+        <f t="shared" si="135"/>
+        <v>1.814287414356151E-4</v>
+      </c>
+      <c r="U1152">
+        <f t="shared" si="136"/>
+        <v>-47.76882278612625</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1153" s="1">
+        <v>46108</v>
+      </c>
+      <c r="B1153">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="C1153">
+        <v>1.0720000267028809</v>
+      </c>
+      <c r="D1153">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="E1153">
+        <v>1.0679999589920044</v>
+      </c>
+      <c r="F1153">
+        <v>1443500</v>
+      </c>
+      <c r="G1153">
+        <v>14435</v>
+      </c>
+      <c r="H1153">
+        <f t="shared" si="144"/>
+        <v>1151</v>
+      </c>
+      <c r="I1153">
+        <f>SUM($F$3:F1153)/H1153</f>
+        <v>4115544.35623914</v>
+      </c>
+      <c r="N1153">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1153">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1153">
+        <f t="shared" si="143"/>
+        <v>1.062333345413208</v>
+      </c>
+      <c r="Q1153">
+        <f t="shared" si="132"/>
+        <v>1.0735000059718178</v>
+      </c>
+      <c r="R1153">
+        <f t="shared" si="133"/>
+        <v>-1.116666055860982E-2</v>
+      </c>
+      <c r="S1153">
+        <f t="shared" si="134"/>
+        <v>1.076191542099931E-2</v>
+      </c>
+      <c r="T1153">
+        <f t="shared" si="135"/>
+        <v>1.6142873131498966E-4</v>
+      </c>
+      <c r="U1153">
+        <f t="shared" si="136"/>
+        <v>-69.173934947309633</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1154" s="1">
+        <v>46111</v>
+      </c>
+      <c r="B1154">
+        <v>1.0590000152587891</v>
+      </c>
+      <c r="C1154">
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="D1154">
+        <v>1.0520000457763672</v>
+      </c>
+      <c r="E1154">
+        <v>1.062000036239624</v>
+      </c>
+      <c r="F1154">
+        <v>2004800</v>
+      </c>
+      <c r="G1154">
+        <v>20048</v>
+      </c>
+      <c r="H1154">
+        <f t="shared" si="144"/>
+        <v>1152</v>
+      </c>
+      <c r="I1154">
+        <f>SUM($F$3:F1154)/H1154</f>
+        <v>4113712.1128743491</v>
+      </c>
+      <c r="N1154">
+        <f t="shared" si="149"/>
+        <v>1.1019999980926514</v>
+      </c>
+      <c r="O1154">
+        <f t="shared" si="150"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1154">
+        <f t="shared" si="143"/>
+        <v>1.0610000292460124</v>
+      </c>
+      <c r="Q1154">
+        <f t="shared" si="132"/>
+        <v>1.0728571528480166</v>
+      </c>
+      <c r="R1154">
+        <f t="shared" si="133"/>
+        <v>-1.1857123602004194E-2</v>
+      </c>
+      <c r="S1154">
+        <f t="shared" si="134"/>
+        <v>1.1496604705343432E-2</v>
+      </c>
+      <c r="T1154">
+        <f t="shared" si="135"/>
+        <v>1.7244907058015148E-4</v>
+      </c>
+      <c r="U1154">
+        <f t="shared" si="136"/>
+        <v>-68.757248514674941</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1154"/>
+  <dimension ref="A1:U1155"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4203,7 +4203,7 @@
         <v>22.746331236897912</v>
       </c>
     </row>
-    <row r="60" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A60" s="1">
         <v>44454</v>
       </c>
@@ -4233,6 +4233,12 @@
         <f>SUM($F$3:F60)/H60</f>
         <v>18222928.293103449</v>
       </c>
+      <c r="K60" s="2">
+        <v>46142</v>
+      </c>
+      <c r="L60" s="2">
+        <v>46113</v>
+      </c>
       <c r="N60">
         <f t="shared" si="11"/>
         <v>0.98799999999999999</v>
@@ -65797,23 +65803,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1154" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1155" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1154" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1155" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1154" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1155" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1154" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1155" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1154" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1155" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68943,7 +68949,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1154" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1155" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69053,7 +69059,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1154" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1155" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -71896,11 +71902,11 @@
         <v>4147753.41323432</v>
       </c>
       <c r="N1134">
-        <f t="shared" ref="N1134:N1154" si="149">IF(A1134&lt;&gt;$K$59,MAX(N1133,VLOOKUP(A1134,A:C,3)),)</f>
+        <f t="shared" ref="N1134:N1155" si="149">IF(A1134&lt;&gt;$K$59,MAX(N1133,VLOOKUP(A1134,A:C,3)),)</f>
         <v>1.0789999961853027</v>
       </c>
       <c r="O1134">
-        <f t="shared" ref="O1134:O1154" si="150">IF(A1134&lt;&gt;$K$59,MIN(O1133,VLOOKUP(A1134,A:D,4)),)</f>
+        <f t="shared" ref="O1134:O1155" si="150">IF(A1134&lt;&gt;$K$59,MIN(O1133,VLOOKUP(A1134,A:D,4)),)</f>
         <v>1.0570000410079956</v>
       </c>
       <c r="P1134">
@@ -73186,6 +73192,69 @@
       <c r="U1154">
         <f t="shared" si="136"/>
         <v>-68.757248514674941</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1155" s="1">
+        <v>46112</v>
+      </c>
+      <c r="B1155">
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="C1155">
+        <v>1.0690000057220459</v>
+      </c>
+      <c r="D1155">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="E1155">
+        <v>1.0479999780654907</v>
+      </c>
+      <c r="F1155">
+        <v>2017527</v>
+      </c>
+      <c r="G1155">
+        <v>20175.26953125</v>
+      </c>
+      <c r="H1155">
+        <f t="shared" si="144"/>
+        <v>1153</v>
+      </c>
+      <c r="I1155">
+        <f>SUM($F$3:F1155)/H1155</f>
+        <v>4111894.0858900696</v>
+      </c>
+      <c r="N1155">
+        <f t="shared" si="149"/>
+        <v>0</v>
+      </c>
+      <c r="O1155">
+        <f t="shared" si="150"/>
+        <v>0</v>
+      </c>
+      <c r="P1155">
+        <f t="shared" si="143"/>
+        <v>1.0546666781107585</v>
+      </c>
+      <c r="Q1155">
+        <f t="shared" si="132"/>
+        <v>1.0705714367684862</v>
+      </c>
+      <c r="R1155">
+        <f t="shared" si="133"/>
+        <v>-1.5904758657727669E-2</v>
+      </c>
+      <c r="S1155">
+        <f t="shared" si="134"/>
+        <v>1.1809527873992904E-2</v>
+      </c>
+      <c r="T1155">
+        <f t="shared" si="135"/>
+        <v>1.7714291810989356E-4</v>
+      </c>
+      <c r="U1155">
+        <f t="shared" si="136"/>
+        <v>-89.784897005371036</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1155"/>
+  <dimension ref="A1:U1175"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -65803,23 +65803,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1155" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1175" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1155" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1175" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1155" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1175" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1155" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1175" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1155" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1175" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68949,7 +68949,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1155" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1175" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69059,7 +69059,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1155" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1175" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -71902,11 +71902,11 @@
         <v>4147753.41323432</v>
       </c>
       <c r="N1134">
-        <f t="shared" ref="N1134:N1155" si="149">IF(A1134&lt;&gt;$K$59,MAX(N1133,VLOOKUP(A1134,A:C,3)),)</f>
+        <f t="shared" ref="N1134:N1154" si="149">IF(A1134&lt;&gt;$K$59,MAX(N1133,VLOOKUP(A1134,A:C,3)),)</f>
         <v>1.0789999961853027</v>
       </c>
       <c r="O1134">
-        <f t="shared" ref="O1134:O1155" si="150">IF(A1134&lt;&gt;$K$59,MIN(O1133,VLOOKUP(A1134,A:D,4)),)</f>
+        <f t="shared" ref="O1134:O1154" si="150">IF(A1134&lt;&gt;$K$59,MIN(O1133,VLOOKUP(A1134,A:D,4)),)</f>
         <v>1.0570000410079956</v>
       </c>
       <c r="P1134">
@@ -73225,12 +73225,12 @@
         <v>4111894.0858900696</v>
       </c>
       <c r="N1155">
-        <f t="shared" si="149"/>
-        <v>0</v>
+        <f>VLOOKUP(L60,A:C,3)</f>
+        <v>1.0640000104904175</v>
       </c>
       <c r="O1155">
-        <f t="shared" si="150"/>
-        <v>0</v>
+        <f>VLOOKUP(L60,A:D,4)</f>
+        <v>1.0460000038146973</v>
       </c>
       <c r="P1155">
         <f t="shared" si="143"/>
@@ -73255,6 +73255,1266 @@
       <c r="U1155">
         <f t="shared" si="136"/>
         <v>-89.784897005371036</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1156" s="1">
+        <v>46113</v>
+      </c>
+      <c r="B1156">
+        <v>1.0570000410079956</v>
+      </c>
+      <c r="C1156">
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="D1156">
+        <v>1.0460000038146973</v>
+      </c>
+      <c r="E1156">
+        <v>1.062000036239624</v>
+      </c>
+      <c r="F1156">
+        <v>1203514</v>
+      </c>
+      <c r="G1156">
+        <v>12035.1396484375</v>
+      </c>
+      <c r="H1156">
+        <f t="shared" si="144"/>
+        <v>1154</v>
+      </c>
+      <c r="I1156">
+        <f>SUM($F$3:F1156)/H1156</f>
+        <v>4109373.8258503033</v>
+      </c>
+      <c r="N1156">
+        <f t="shared" ref="N1156:N1175" si="151">IF(A1156&lt;&gt;$K$60,MAX(N1155,VLOOKUP(A1156,A:C,3)),)</f>
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="O1156">
+        <f t="shared" ref="O1156:O1175" si="152">IF(A1156&lt;&gt;$K$60,MIN(O1155,VLOOKUP(A1156,A:D,4)),)</f>
+        <v>1.0460000038146973</v>
+      </c>
+      <c r="P1156">
+        <f t="shared" si="143"/>
+        <v>1.0573333501815796</v>
+      </c>
+      <c r="Q1156">
+        <f t="shared" si="132"/>
+        <v>1.0687619135493323</v>
+      </c>
+      <c r="R1156">
+        <f t="shared" si="133"/>
+        <v>-1.1428563367752664E-2</v>
+      </c>
+      <c r="S1156">
+        <f t="shared" si="134"/>
+        <v>1.1632656564517856E-2</v>
+      </c>
+      <c r="T1156">
+        <f t="shared" si="135"/>
+        <v>1.7448984846776784E-4</v>
+      </c>
+      <c r="U1156">
+        <f t="shared" si="136"/>
+        <v>-65.497010101786955</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1157" s="1">
+        <v>46114</v>
+      </c>
+      <c r="B1157">
+        <v>1.0559999942779541</v>
+      </c>
+      <c r="C1157">
+        <v>1.0579999685287476</v>
+      </c>
+      <c r="D1157">
+        <v>1.0440000295639038</v>
+      </c>
+      <c r="E1157">
+        <v>1.0470000505447388</v>
+      </c>
+      <c r="F1157">
+        <v>1625206</v>
+      </c>
+      <c r="G1157">
+        <v>16252.0595703125</v>
+      </c>
+      <c r="H1157">
+        <f t="shared" si="144"/>
+        <v>1155</v>
+      </c>
+      <c r="I1157">
+        <f>SUM($F$3:F1157)/H1157</f>
+        <v>4107223.0311958874</v>
+      </c>
+      <c r="N1157">
+        <f t="shared" si="151"/>
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="O1157">
+        <f t="shared" si="152"/>
+        <v>1.0440000295639038</v>
+      </c>
+      <c r="P1157">
+        <f t="shared" si="143"/>
+        <v>1.0496666828791301</v>
+      </c>
+      <c r="Q1157">
+        <f t="shared" si="132"/>
+        <v>1.0663571528026035</v>
+      </c>
+      <c r="R1157">
+        <f t="shared" si="133"/>
+        <v>-1.6690469923473339E-2</v>
+      </c>
+      <c r="S1157">
+        <f t="shared" si="134"/>
+        <v>1.1598640558670928E-2</v>
+      </c>
+      <c r="T1157">
+        <f t="shared" si="135"/>
+        <v>1.7397960838006391E-4</v>
+      </c>
+      <c r="U1157">
+        <f t="shared" si="136"/>
+        <v>-95.933483693172164</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1158" s="1">
+        <v>46115</v>
+      </c>
+      <c r="B1158">
+        <v>1.0540000200271606</v>
+      </c>
+      <c r="C1158">
+        <v>1.0540000200271606</v>
+      </c>
+      <c r="D1158">
+        <v>1.0349999666213989</v>
+      </c>
+      <c r="E1158">
+        <v>1.0390000343322754</v>
+      </c>
+      <c r="F1158">
+        <v>1729633</v>
+      </c>
+      <c r="G1158">
+        <v>17296.330078125</v>
+      </c>
+      <c r="H1158">
+        <f t="shared" si="144"/>
+        <v>1156</v>
+      </c>
+      <c r="I1158">
+        <f>SUM($F$3:F1158)/H1158</f>
+        <v>4105166.2924145763</v>
+      </c>
+      <c r="N1158">
+        <f t="shared" si="151"/>
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="O1158">
+        <f t="shared" si="152"/>
+        <v>1.0349999666213989</v>
+      </c>
+      <c r="P1158">
+        <f t="shared" si="143"/>
+        <v>1.0426666736602783</v>
+      </c>
+      <c r="Q1158">
+        <f t="shared" si="132"/>
+        <v>1.0633095332554408</v>
+      </c>
+      <c r="R1158">
+        <f t="shared" si="133"/>
+        <v>-2.0642859595162433E-2</v>
+      </c>
+      <c r="S1158">
+        <f t="shared" si="134"/>
+        <v>1.1115650741421401E-2</v>
+      </c>
+      <c r="T1158">
+        <f t="shared" si="135"/>
+        <v>1.66734761121321E-4</v>
+      </c>
+      <c r="U1158">
+        <f t="shared" si="136"/>
+        <v>-123.8065743240073</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1159" s="1">
+        <v>46119</v>
+      </c>
+      <c r="B1159">
+        <v>1.0379999876022339</v>
+      </c>
+      <c r="C1159">
+        <v>1.0429999828338623</v>
+      </c>
+      <c r="D1159">
+        <v>1.031000018119812</v>
+      </c>
+      <c r="E1159">
+        <v>1.0379999876022339</v>
+      </c>
+      <c r="F1159">
+        <v>1343500</v>
+      </c>
+      <c r="G1159">
+        <v>13435</v>
+      </c>
+      <c r="H1159">
+        <f t="shared" si="144"/>
+        <v>1157</v>
+      </c>
+      <c r="I1159">
+        <f>SUM($F$3:F1159)/H1159</f>
+        <v>4102779.372542135</v>
+      </c>
+      <c r="N1159">
+        <f t="shared" si="151"/>
+        <v>1.0640000104904175</v>
+      </c>
+      <c r="O1159">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1159">
+        <f t="shared" si="143"/>
+        <v>1.037333329518636</v>
+      </c>
+      <c r="Q1159">
+        <f t="shared" si="132"/>
+        <v>1.0599047711917331</v>
+      </c>
+      <c r="R1159">
+        <f t="shared" si="133"/>
+        <v>-2.2571441673097103E-2</v>
+      </c>
+      <c r="S1159">
+        <f t="shared" si="134"/>
+        <v>1.095239037559145E-2</v>
+      </c>
+      <c r="T1159">
+        <f t="shared" si="135"/>
+        <v>1.6428585563387174E-4</v>
+      </c>
+      <c r="U1159">
+        <f t="shared" si="136"/>
+        <v>-137.39126588840324</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1160" s="1">
+        <v>46120</v>
+      </c>
+      <c r="B1160">
+        <v>1.0449999570846558</v>
+      </c>
+      <c r="C1160">
+        <v>1.0829999446868896</v>
+      </c>
+      <c r="D1160">
+        <v>1.0449999570846558</v>
+      </c>
+      <c r="E1160">
+        <v>1.0829999446868896</v>
+      </c>
+      <c r="F1160">
+        <v>1582716</v>
+      </c>
+      <c r="G1160">
+        <v>15827.16015625</v>
+      </c>
+      <c r="H1160">
+        <f t="shared" si="144"/>
+        <v>1158</v>
+      </c>
+      <c r="I1160">
+        <f>SUM($F$3:F1160)/H1160</f>
+        <v>4100603.1520131691</v>
+      </c>
+      <c r="N1160">
+        <f t="shared" si="151"/>
+        <v>1.0829999446868896</v>
+      </c>
+      <c r="O1160">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1160">
+        <f t="shared" si="143"/>
+        <v>1.0703332821528118</v>
+      </c>
+      <c r="Q1160">
+        <f t="shared" si="132"/>
+        <v>1.0590952407746086</v>
+      </c>
+      <c r="R1160">
+        <f t="shared" si="133"/>
+        <v>1.1238041378203167E-2</v>
+      </c>
+      <c r="S1160">
+        <f t="shared" si="134"/>
+        <v>1.0142859958467023E-2</v>
+      </c>
+      <c r="T1160">
+        <f t="shared" si="135"/>
+        <v>1.5214289937700535E-4</v>
+      </c>
+      <c r="U1160">
+        <f t="shared" si="136"/>
+        <v>73.865040197213887</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1161" s="1">
+        <v>46121</v>
+      </c>
+      <c r="B1161">
+        <v>1.0729999542236328</v>
+      </c>
+      <c r="C1161">
+        <v>1.0820000171661377</v>
+      </c>
+      <c r="D1161">
+        <v>1.0729999542236328</v>
+      </c>
+      <c r="E1161">
+        <v>1.0779999494552612</v>
+      </c>
+      <c r="F1161">
+        <v>1711200</v>
+      </c>
+      <c r="G1161">
+        <v>17112</v>
+      </c>
+      <c r="H1161">
+        <f t="shared" si="144"/>
+        <v>1159</v>
+      </c>
+      <c r="I1161">
+        <f>SUM($F$3:F1161)/H1161</f>
+        <v>4098541.5444618207</v>
+      </c>
+      <c r="N1161">
+        <f t="shared" si="151"/>
+        <v>1.0829999446868896</v>
+      </c>
+      <c r="O1161">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1161">
+        <f t="shared" si="143"/>
+        <v>1.0776666402816772</v>
+      </c>
+      <c r="Q1161">
+        <f t="shared" si="132"/>
+        <v>1.0591428563708349</v>
+      </c>
+      <c r="R1161">
+        <f t="shared" si="133"/>
+        <v>1.8523783910842306E-2</v>
+      </c>
+      <c r="S1161">
+        <f t="shared" si="134"/>
+        <v>1.0190475554693308E-2</v>
+      </c>
+      <c r="T1161">
+        <f t="shared" si="135"/>
+        <v>1.5285713332039962E-4</v>
+      </c>
+      <c r="U1161">
+        <f t="shared" si="136"/>
+        <v>121.1836406222215</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1162" s="1">
+        <v>46122</v>
+      </c>
+      <c r="B1162">
+        <v>1.0880000591278076</v>
+      </c>
+      <c r="C1162">
+        <v>1.1150000095367432</v>
+      </c>
+      <c r="D1162">
+        <v>1.0859999656677246</v>
+      </c>
+      <c r="E1162">
+        <v>1.1080000400543213</v>
+      </c>
+      <c r="F1162">
+        <v>3152132</v>
+      </c>
+      <c r="G1162">
+        <v>31521.3203125</v>
+      </c>
+      <c r="H1162">
+        <f t="shared" si="144"/>
+        <v>1160</v>
+      </c>
+      <c r="I1162">
+        <f>SUM($F$3:F1162)/H1162</f>
+        <v>4097725.6741648708</v>
+      </c>
+      <c r="N1162">
+        <f t="shared" si="151"/>
+        <v>1.1150000095367432</v>
+      </c>
+      <c r="O1162">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1162">
+        <f t="shared" si="143"/>
+        <v>1.1030000050862629</v>
+      </c>
+      <c r="Q1162">
+        <f t="shared" si="132"/>
+        <v>1.0606666661444166</v>
+      </c>
+      <c r="R1162">
+        <f t="shared" si="133"/>
+        <v>4.2333338941846321E-2</v>
+      </c>
+      <c r="S1162">
+        <f t="shared" si="134"/>
+        <v>1.1714285328274676E-2</v>
+      </c>
+      <c r="T1162">
+        <f t="shared" si="135"/>
+        <v>1.7571427992412014E-4</v>
+      </c>
+      <c r="U1162">
+        <f t="shared" si="136"/>
+        <v>240.9214490713413</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1163" s="1">
+        <v>46125</v>
+      </c>
+      <c r="B1163">
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="C1163">
+        <v>1.1200000047683716</v>
+      </c>
+      <c r="D1163">
+        <v>1.1000000238418579</v>
+      </c>
+      <c r="E1163">
+        <v>1.1180000305175781</v>
+      </c>
+      <c r="F1163">
+        <v>2531061</v>
+      </c>
+      <c r="G1163">
+        <v>25310.609375</v>
+      </c>
+      <c r="H1163">
+        <f t="shared" si="144"/>
+        <v>1161</v>
+      </c>
+      <c r="I1163">
+        <f>SUM($F$3:F1163)/H1163</f>
+        <v>4096376.2644541343</v>
+      </c>
+      <c r="N1163">
+        <f t="shared" si="151"/>
+        <v>1.1200000047683716</v>
+      </c>
+      <c r="O1163">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1163">
+        <f t="shared" si="143"/>
+        <v>1.1126666863759358</v>
+      </c>
+      <c r="Q1163">
+        <f t="shared" si="132"/>
+        <v>1.0649047635850453</v>
+      </c>
+      <c r="R1163">
+        <f t="shared" si="133"/>
+        <v>4.7761922790890532E-2</v>
+      </c>
+      <c r="S1163">
+        <f t="shared" si="134"/>
+        <v>1.5401350397641964E-2</v>
+      </c>
+      <c r="T1163">
+        <f t="shared" si="135"/>
+        <v>2.3102025596462945E-4</v>
+      </c>
+      <c r="U1163">
+        <f t="shared" si="136"/>
+        <v>206.74344157164799</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1164" s="1">
+        <v>46126</v>
+      </c>
+      <c r="B1164">
+        <v>1.1210000514984131</v>
+      </c>
+      <c r="C1164">
+        <v>1.1349999904632568</v>
+      </c>
+      <c r="D1164">
+        <v>1.1200000047683716</v>
+      </c>
+      <c r="E1164">
+        <v>1.1349999904632568</v>
+      </c>
+      <c r="F1164">
+        <v>4068838</v>
+      </c>
+      <c r="G1164">
+        <v>40688.37890625</v>
+      </c>
+      <c r="H1164">
+        <f t="shared" si="144"/>
+        <v>1162</v>
+      </c>
+      <c r="I1164">
+        <f>SUM($F$3:F1164)/H1164</f>
+        <v>4096352.5654313685</v>
+      </c>
+      <c r="N1164">
+        <f t="shared" si="151"/>
+        <v>1.1349999904632568</v>
+      </c>
+      <c r="O1164">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1164">
+        <f t="shared" si="143"/>
+        <v>1.1299999952316284</v>
+      </c>
+      <c r="Q1164">
+        <f t="shared" si="132"/>
+        <v>1.0707857183047704</v>
+      </c>
+      <c r="R1164">
+        <f t="shared" si="133"/>
+        <v>5.9214276926857989E-2</v>
+      </c>
+      <c r="S1164">
+        <f t="shared" si="134"/>
+        <v>2.002720767948905E-2</v>
+      </c>
+      <c r="T1164">
+        <f t="shared" si="135"/>
+        <v>3.0040811519233576E-4</v>
+      </c>
+      <c r="U1164">
+        <f t="shared" si="136"/>
+        <v>197.11277403057557</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1165" s="1">
+        <v>46127</v>
+      </c>
+      <c r="B1165">
+        <v>1.1399999856948853</v>
+      </c>
+      <c r="C1165">
+        <v>1.1399999856948853</v>
+      </c>
+      <c r="D1165">
+        <v>1.1189999580383301</v>
+      </c>
+      <c r="E1165">
+        <v>1.1230000257492065</v>
+      </c>
+      <c r="F1165">
+        <v>1070707</v>
+      </c>
+      <c r="G1165">
+        <v>10707.0703125</v>
+      </c>
+      <c r="H1165">
+        <f t="shared" si="144"/>
+        <v>1163</v>
+      </c>
+      <c r="I1165">
+        <f>SUM($F$3:F1165)/H1165</f>
+        <v>4093750.9785307394</v>
+      </c>
+      <c r="N1165">
+        <f t="shared" si="151"/>
+        <v>1.1399999856948853</v>
+      </c>
+      <c r="O1165">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1165">
+        <f t="shared" si="143"/>
+        <v>1.1273333231608074</v>
+      </c>
+      <c r="Q1165">
+        <f t="shared" si="132"/>
+        <v>1.07497619447254</v>
+      </c>
+      <c r="R1165">
+        <f t="shared" si="133"/>
+        <v>5.2357128688267363E-2</v>
+      </c>
+      <c r="S1165">
+        <f t="shared" si="134"/>
+        <v>2.5112239681944537E-2</v>
+      </c>
+      <c r="T1165">
+        <f t="shared" si="135"/>
+        <v>3.7668359522916804E-4</v>
+      </c>
+      <c r="U1165">
+        <f t="shared" si="136"/>
+        <v>138.99497974265154</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1166" s="1">
+        <v>46128</v>
+      </c>
+      <c r="B1166">
+        <v>1.1289999485015869</v>
+      </c>
+      <c r="C1166">
+        <v>1.1499999761581421</v>
+      </c>
+      <c r="D1166">
+        <v>1.1289999485015869</v>
+      </c>
+      <c r="E1166">
+        <v>1.1499999761581421</v>
+      </c>
+      <c r="F1166">
+        <v>7802622</v>
+      </c>
+      <c r="G1166">
+        <v>78026.21875</v>
+      </c>
+      <c r="H1166">
+        <f t="shared" si="144"/>
+        <v>1164</v>
+      </c>
+      <c r="I1166">
+        <f>SUM($F$3:F1166)/H1166</f>
+        <v>4096937.29384128</v>
+      </c>
+      <c r="N1166">
+        <f t="shared" si="151"/>
+        <v>1.1499999761581421</v>
+      </c>
+      <c r="O1166">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1166">
+        <f t="shared" si="143"/>
+        <v>1.1429999669392903</v>
+      </c>
+      <c r="Q1166">
+        <f t="shared" si="132"/>
+        <v>1.0806428563027155</v>
+      </c>
+      <c r="R1166">
+        <f t="shared" si="133"/>
+        <v>6.2357110636574786E-2</v>
+      </c>
+      <c r="S1166">
+        <f t="shared" si="134"/>
+        <v>3.0397956468621059E-2</v>
+      </c>
+      <c r="T1166">
+        <f t="shared" si="135"/>
+        <v>4.5596934702931584E-4</v>
+      </c>
+      <c r="U1166">
+        <f t="shared" si="136"/>
+        <v>136.75724265860711</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1167" s="1">
+        <v>46129</v>
+      </c>
+      <c r="B1167">
+        <v>1.1519999504089355</v>
+      </c>
+      <c r="C1167">
+        <v>1.159000039100647</v>
+      </c>
+      <c r="D1167">
+        <v>1.1449999809265137</v>
+      </c>
+      <c r="E1167">
+        <v>1.156000018119812</v>
+      </c>
+      <c r="F1167">
+        <v>2073127</v>
+      </c>
+      <c r="G1167">
+        <v>20731.26953125</v>
+      </c>
+      <c r="H1167">
+        <f t="shared" si="144"/>
+        <v>1165</v>
+      </c>
+      <c r="I1167">
+        <f>SUM($F$3:F1167)/H1167</f>
+        <v>4095200.1176233906</v>
+      </c>
+      <c r="N1167">
+        <f t="shared" si="151"/>
+        <v>1.159000039100647</v>
+      </c>
+      <c r="O1167">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1167">
+        <f t="shared" si="143"/>
+        <v>1.153333346048991</v>
+      </c>
+      <c r="Q1167">
+        <f t="shared" si="132"/>
+        <v>1.0871428563481287</v>
+      </c>
+      <c r="R1167">
+        <f t="shared" si="133"/>
+        <v>6.6190489700862276E-2</v>
+      </c>
+      <c r="S1167">
+        <f t="shared" si="134"/>
+        <v>3.5210883536306366E-2</v>
+      </c>
+      <c r="T1167">
+        <f t="shared" si="135"/>
+        <v>5.2816325304459548E-4</v>
+      </c>
+      <c r="U1167">
+        <f t="shared" si="136"/>
+        <v>125.32202745894834</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1168" s="1">
+        <v>46132</v>
+      </c>
+      <c r="B1168">
+        <v>1.156999945640564</v>
+      </c>
+      <c r="C1168">
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="D1168">
+        <v>1.1529999971389771</v>
+      </c>
+      <c r="E1168">
+        <v>1.1610000133514404</v>
+      </c>
+      <c r="F1168">
+        <v>1331406</v>
+      </c>
+      <c r="G1168">
+        <v>13314.0595703125</v>
+      </c>
+      <c r="H1168">
+        <f t="shared" si="144"/>
+        <v>1166</v>
+      </c>
+      <c r="I1168">
+        <f>SUM($F$3:F1168)/H1168</f>
+        <v>4092829.7967677959</v>
+      </c>
+      <c r="N1168">
+        <f t="shared" si="151"/>
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="O1168">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1168">
+        <f t="shared" si="143"/>
+        <v>1.1596666574478149</v>
+      </c>
+      <c r="Q1168">
+        <f t="shared" si="132"/>
+        <v>1.0941904726482574</v>
+      </c>
+      <c r="R1168">
+        <f t="shared" si="133"/>
+        <v>6.5476184799557524E-2</v>
+      </c>
+      <c r="S1168">
+        <f t="shared" si="134"/>
+        <v>3.8523810250418511E-2</v>
+      </c>
+      <c r="T1168">
+        <f t="shared" si="135"/>
+        <v>5.7785715375627766E-4</v>
+      </c>
+      <c r="U1168">
+        <f t="shared" si="136"/>
+        <v>113.30859949373122</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1169" s="1">
+        <v>46133</v>
+      </c>
+      <c r="B1169">
+        <v>1.156000018119812</v>
+      </c>
+      <c r="C1169">
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="D1169">
+        <v>1.1480000019073486</v>
+      </c>
+      <c r="E1169">
+        <v>1.1640000343322754</v>
+      </c>
+      <c r="F1169">
+        <v>787504</v>
+      </c>
+      <c r="G1169">
+        <v>7875.0400390625</v>
+      </c>
+      <c r="H1169">
+        <f t="shared" si="144"/>
+        <v>1167</v>
+      </c>
+      <c r="I1169">
+        <f>SUM($F$3:F1169)/H1169</f>
+        <v>4089997.4696068983</v>
+      </c>
+      <c r="N1169">
+        <f t="shared" si="151"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="O1169">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1169">
+        <f t="shared" si="143"/>
+        <v>1.159333348274231</v>
+      </c>
+      <c r="Q1169">
+        <f t="shared" si="132"/>
+        <v>1.1016666633742196</v>
+      </c>
+      <c r="R1169">
+        <f t="shared" si="133"/>
+        <v>5.7666684900011367E-2</v>
+      </c>
+      <c r="S1169">
+        <f t="shared" si="134"/>
+        <v>3.9285717367314961E-2</v>
+      </c>
+      <c r="T1169">
+        <f t="shared" si="135"/>
+        <v>5.8928576050972436E-4</v>
+      </c>
+      <c r="U1169">
+        <f t="shared" si="136"/>
+        <v>97.858609123917148</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1170" s="1">
+        <v>46134</v>
+      </c>
+      <c r="B1170">
+        <v>1.1629999876022339</v>
+      </c>
+      <c r="C1170">
+        <v>1.1829999685287476</v>
+      </c>
+      <c r="D1170">
+        <v>1.1599999666213989</v>
+      </c>
+      <c r="E1170">
+        <v>1.1829999685287476</v>
+      </c>
+      <c r="F1170">
+        <v>1108120</v>
+      </c>
+      <c r="G1170">
+        <v>11081.2001953125</v>
+      </c>
+      <c r="H1170">
+        <f t="shared" si="144"/>
+        <v>1168</v>
+      </c>
+      <c r="I1170">
+        <f>SUM($F$3:F1170)/H1170</f>
+        <v>4087444.4923212756</v>
+      </c>
+      <c r="N1170">
+        <f t="shared" si="151"/>
+        <v>1.1829999685287476</v>
+      </c>
+      <c r="O1170">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1170">
+        <f t="shared" si="143"/>
+        <v>1.1753333012262981</v>
+      </c>
+      <c r="Q1170">
+        <f t="shared" si="132"/>
+        <v>1.1100952313059851</v>
+      </c>
+      <c r="R1170">
+        <f t="shared" si="133"/>
+        <v>6.5238069920313002E-2</v>
+      </c>
+      <c r="S1170">
+        <f t="shared" si="134"/>
+        <v>3.9986396322445016E-2</v>
+      </c>
+      <c r="T1170">
+        <f t="shared" si="135"/>
+        <v>5.9979594483667523E-4</v>
+      </c>
+      <c r="U1170">
+        <f t="shared" si="136"/>
+        <v>108.76710735027955</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1171" s="1">
+        <v>46135</v>
+      </c>
+      <c r="B1171">
+        <v>1.187999963760376</v>
+      </c>
+      <c r="C1171">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="D1171">
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="E1171">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="F1171">
+        <v>2312708</v>
+      </c>
+      <c r="G1171">
+        <v>23127.080078125</v>
+      </c>
+      <c r="H1171">
+        <f t="shared" si="144"/>
+        <v>1169</v>
+      </c>
+      <c r="I1171">
+        <f>SUM($F$3:F1171)/H1171</f>
+        <v>4085926.3259463217</v>
+      </c>
+      <c r="N1171">
+        <f t="shared" si="151"/>
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="O1171">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1171">
+        <f t="shared" si="143"/>
+        <v>1.1776666641235352</v>
+      </c>
+      <c r="Q1171">
+        <f t="shared" si="132"/>
+        <v>1.119238087109157</v>
+      </c>
+      <c r="R1171">
+        <f t="shared" si="133"/>
+        <v>5.8428577014378202E-2</v>
+      </c>
+      <c r="S1171">
+        <f t="shared" si="134"/>
+        <v>3.8823129368477156E-2</v>
+      </c>
+      <c r="T1171">
+        <f t="shared" si="135"/>
+        <v>5.8234694052715732E-4</v>
+      </c>
+      <c r="U1171">
+        <f t="shared" si="136"/>
+        <v>100.3329337688062</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1172" s="1">
+        <v>46136</v>
+      </c>
+      <c r="B1172">
+        <v>1.1720000505447388</v>
+      </c>
+      <c r="C1172">
+        <v>1.1729999780654907</v>
+      </c>
+      <c r="D1172">
+        <v>1.156999945640564</v>
+      </c>
+      <c r="E1172">
+        <v>1.1670000553131104</v>
+      </c>
+      <c r="F1172">
+        <v>2117903</v>
+      </c>
+      <c r="G1172">
+        <v>21179.029296875</v>
+      </c>
+      <c r="H1172">
+        <f t="shared" si="144"/>
+        <v>1170</v>
+      </c>
+      <c r="I1172">
+        <f>SUM($F$3:F1172)/H1172</f>
+        <v>4084244.2547275643</v>
+      </c>
+      <c r="N1172">
+        <f t="shared" si="151"/>
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="O1172">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1172">
+        <f t="shared" si="143"/>
+        <v>1.1656666596730549</v>
+      </c>
+      <c r="Q1172">
+        <f t="shared" si="132"/>
+        <v>1.1280238003957839</v>
+      </c>
+      <c r="R1172">
+        <f t="shared" si="133"/>
+        <v>3.7642859277271068E-2</v>
+      </c>
+      <c r="S1172">
+        <f t="shared" si="134"/>
+        <v>3.425850511408178E-2</v>
+      </c>
+      <c r="T1172">
+        <f t="shared" si="135"/>
+        <v>5.1387757671122667E-4</v>
+      </c>
+      <c r="U1172">
+        <f t="shared" si="136"/>
+        <v>73.25258190517323</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1173" s="1">
+        <v>46139</v>
+      </c>
+      <c r="B1173">
+        <v>1.1670000553131104</v>
+      </c>
+      <c r="C1173">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="D1173">
+        <v>1.1670000553131104</v>
+      </c>
+      <c r="E1173">
+        <v>1.1690000295639038</v>
+      </c>
+      <c r="F1173">
+        <v>1376903</v>
+      </c>
+      <c r="G1173">
+        <v>13769.0302734375</v>
+      </c>
+      <c r="H1173">
+        <f t="shared" si="144"/>
+        <v>1171</v>
+      </c>
+      <c r="I1173">
+        <f>SUM($F$3:F1173)/H1173</f>
+        <v>4081932.2639037147</v>
+      </c>
+      <c r="N1173">
+        <f t="shared" si="151"/>
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="O1173">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1173">
+        <f t="shared" si="143"/>
+        <v>1.1710000435511272</v>
+      </c>
+      <c r="Q1173">
+        <f t="shared" si="132"/>
+        <v>1.137571422826676</v>
+      </c>
+      <c r="R1173">
+        <f t="shared" si="133"/>
+        <v>3.3428620724451186E-2</v>
+      </c>
+      <c r="S1173">
+        <f t="shared" si="134"/>
+        <v>2.9204086381561929E-2</v>
+      </c>
+      <c r="T1173">
+        <f t="shared" si="135"/>
+        <v>4.3806129572342893E-4</v>
+      </c>
+      <c r="U1173">
+        <f t="shared" si="136"/>
+        <v>76.310372659712044</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1174" s="1">
+        <v>46140</v>
+      </c>
+      <c r="B1174">
+        <v>1.159000039100647</v>
+      </c>
+      <c r="C1174">
+        <v>1.1649999618530273</v>
+      </c>
+      <c r="D1174">
+        <v>1.1549999713897705</v>
+      </c>
+      <c r="E1174">
+        <v>1.156999945640564</v>
+      </c>
+      <c r="F1174">
+        <v>1329318</v>
+      </c>
+      <c r="G1174">
+        <v>13293.1796875</v>
+      </c>
+      <c r="H1174">
+        <f t="shared" si="144"/>
+        <v>1172</v>
+      </c>
+      <c r="I1174">
+        <f>SUM($F$3:F1174)/H1174</f>
+        <v>4079583.6169208619</v>
+      </c>
+      <c r="N1174">
+        <f t="shared" si="151"/>
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="O1174">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1174">
+        <f t="shared" si="143"/>
+        <v>1.1589999596277873</v>
+      </c>
+      <c r="Q1174">
+        <f t="shared" si="132"/>
+        <v>1.1439047569320313</v>
+      </c>
+      <c r="R1174">
+        <f t="shared" si="133"/>
+        <v>1.5095202695756038E-2</v>
+      </c>
+      <c r="S1174">
+        <f t="shared" si="134"/>
+        <v>2.4251703502369635E-2</v>
+      </c>
+      <c r="T1174">
+        <f t="shared" si="135"/>
+        <v>3.6377555253554449E-4</v>
+      </c>
+      <c r="U1174">
+        <f t="shared" si="136"/>
+        <v>41.495924040363008</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1175" s="1">
+        <v>46141</v>
+      </c>
+      <c r="B1175">
+        <v>1.1529999971389771</v>
+      </c>
+      <c r="C1175">
+        <v>1.1790000200271606</v>
+      </c>
+      <c r="D1175">
+        <v>1.1529999971389771</v>
+      </c>
+      <c r="E1175">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="F1175">
+        <v>526604</v>
+      </c>
+      <c r="G1175">
+        <v>5266.0400390625</v>
+      </c>
+      <c r="H1175">
+        <f t="shared" si="144"/>
+        <v>1173</v>
+      </c>
+      <c r="I1175">
+        <f>SUM($F$3:F1175)/H1175</f>
+        <v>4076554.6487904945</v>
+      </c>
+      <c r="N1175">
+        <f t="shared" si="151"/>
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="O1175">
+        <f t="shared" si="152"/>
+        <v>1.031000018119812</v>
+      </c>
+      <c r="P1175">
+        <f t="shared" si="143"/>
+        <v>1.1696666876475017</v>
+      </c>
+      <c r="Q1175">
+        <f t="shared" si="132"/>
+        <v>1.1504761888867332</v>
+      </c>
+      <c r="R1175">
+        <f t="shared" si="133"/>
+        <v>1.9190498760768504E-2</v>
+      </c>
+      <c r="S1175">
+        <f t="shared" si="134"/>
+        <v>1.9482995377105978E-2</v>
+      </c>
+      <c r="T1175">
+        <f t="shared" si="135"/>
+        <v>2.9224493065658965E-4</v>
+      </c>
+      <c r="U1175">
+        <f t="shared" si="136"/>
+        <v>65.665805451793517</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1175"/>
+  <dimension ref="A1:U1176"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4272,7 +4272,7 @@
         <v>-43.32500693866178</v>
       </c>
     </row>
-    <row r="61" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A61" s="1">
         <v>44455</v>
       </c>
@@ -4302,6 +4302,12 @@
         <f>SUM($F$3:F61)/H61</f>
         <v>18027865.474576272</v>
       </c>
+      <c r="K61" s="2">
+        <v>46171</v>
+      </c>
+      <c r="L61" s="2">
+        <v>46148</v>
+      </c>
       <c r="N61">
         <f t="shared" si="11"/>
         <v>0.98799999999999999</v>
@@ -65803,23 +65809,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1175" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1176" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1175" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1176" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1175" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1176" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1175" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1176" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1175" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1176" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68949,7 +68955,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1175" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1176" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69059,7 +69065,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1175" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1176" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -73288,11 +73294,11 @@
         <v>4109373.8258503033</v>
       </c>
       <c r="N1156">
-        <f t="shared" ref="N1156:N1175" si="151">IF(A1156&lt;&gt;$K$60,MAX(N1155,VLOOKUP(A1156,A:C,3)),)</f>
+        <f t="shared" ref="N1156:N1176" si="151">IF(A1156&lt;&gt;$K$60,MAX(N1155,VLOOKUP(A1156,A:C,3)),)</f>
         <v>1.0640000104904175</v>
       </c>
       <c r="O1156">
-        <f t="shared" ref="O1156:O1175" si="152">IF(A1156&lt;&gt;$K$60,MIN(O1155,VLOOKUP(A1156,A:D,4)),)</f>
+        <f t="shared" ref="O1156:O1176" si="152">IF(A1156&lt;&gt;$K$60,MIN(O1155,VLOOKUP(A1156,A:D,4)),)</f>
         <v>1.0460000038146973</v>
       </c>
       <c r="P1156">
@@ -74515,6 +74521,69 @@
       <c r="U1175">
         <f t="shared" si="136"/>
         <v>65.665805451793517</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1176" s="1">
+        <v>46142</v>
+      </c>
+      <c r="B1176">
+        <v>1.1809999942779541</v>
+      </c>
+      <c r="C1176">
+        <v>1.1859999895095825</v>
+      </c>
+      <c r="D1176">
+        <v>1.1740000247955322</v>
+      </c>
+      <c r="E1176">
+        <v>1.1770000457763672</v>
+      </c>
+      <c r="F1176">
+        <v>1531906</v>
+      </c>
+      <c r="G1176">
+        <v>15319.0595703125</v>
+      </c>
+      <c r="H1176">
+        <f t="shared" si="144"/>
+        <v>1174</v>
+      </c>
+      <c r="I1176">
+        <f>SUM($F$3:F1176)/H1176</f>
+        <v>4074387.1456824956</v>
+      </c>
+      <c r="N1176">
+        <f t="shared" si="151"/>
+        <v>0</v>
+      </c>
+      <c r="O1176">
+        <f t="shared" si="152"/>
+        <v>0</v>
+      </c>
+      <c r="P1176">
+        <f t="shared" si="143"/>
+        <v>1.1790000200271606</v>
+      </c>
+      <c r="Q1176">
+        <f t="shared" si="132"/>
+        <v>1.1559047613825117</v>
+      </c>
+      <c r="R1176">
+        <f t="shared" si="133"/>
+        <v>2.3095258644648897E-2</v>
+      </c>
+      <c r="S1176">
+        <f t="shared" si="134"/>
+        <v>1.6170069879415081E-2</v>
+      </c>
+      <c r="T1176">
+        <f t="shared" si="135"/>
+        <v>2.4255104819122621E-4</v>
+      </c>
+      <c r="U1176">
+        <f t="shared" si="136"/>
+        <v>95.218135798121537</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1176"/>
+  <dimension ref="A1:U1193"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -65809,23 +65809,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1176" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1193" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1176" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1193" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1176" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1193" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1176" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1193" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1176" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1193" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68955,7 +68955,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1176" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1193" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69065,7 +69065,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1176" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1193" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -73294,11 +73294,11 @@
         <v>4109373.8258503033</v>
       </c>
       <c r="N1156">
-        <f t="shared" ref="N1156:N1176" si="151">IF(A1156&lt;&gt;$K$60,MAX(N1155,VLOOKUP(A1156,A:C,3)),)</f>
+        <f t="shared" ref="N1156:N1175" si="151">IF(A1156&lt;&gt;$K$60,MAX(N1155,VLOOKUP(A1156,A:C,3)),)</f>
         <v>1.0640000104904175</v>
       </c>
       <c r="O1156">
-        <f t="shared" ref="O1156:O1176" si="152">IF(A1156&lt;&gt;$K$60,MIN(O1155,VLOOKUP(A1156,A:D,4)),)</f>
+        <f t="shared" ref="O1156:O1175" si="152">IF(A1156&lt;&gt;$K$60,MIN(O1155,VLOOKUP(A1156,A:D,4)),)</f>
         <v>1.0460000038146973</v>
       </c>
       <c r="P1156">
@@ -74554,12 +74554,12 @@
         <v>4074387.1456824956</v>
       </c>
       <c r="N1176">
-        <f t="shared" si="151"/>
-        <v>0</v>
+        <f>VLOOKUP(L61,A:C,3)</f>
+        <v>1.2000000476837158</v>
       </c>
       <c r="O1176">
-        <f t="shared" si="152"/>
-        <v>0</v>
+        <f>VLOOKUP(L61,A:D,4)</f>
+        <v>1.1660000085830688</v>
       </c>
       <c r="P1176">
         <f t="shared" si="143"/>
@@ -74584,6 +74584,1077 @@
       <c r="U1176">
         <f t="shared" si="136"/>
         <v>95.218135798121537</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1177" s="1">
+        <v>46148</v>
+      </c>
+      <c r="B1177">
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="C1177">
+        <v>1.2000000476837158</v>
+      </c>
+      <c r="D1177">
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="E1177">
+        <v>1.1929999589920044</v>
+      </c>
+      <c r="F1177">
+        <v>2577800</v>
+      </c>
+      <c r="G1177">
+        <v>25778</v>
+      </c>
+      <c r="H1177">
+        <f t="shared" si="144"/>
+        <v>1175</v>
+      </c>
+      <c r="I1177">
+        <f>SUM($F$3:F1177)/H1177</f>
+        <v>4073113.4544946807</v>
+      </c>
+      <c r="N1177">
+        <f t="shared" ref="N1177:N1193" si="153">IF(A1177&lt;&gt;$K$61,MAX(N1176,VLOOKUP(A1177,A:C,3)),)</f>
+        <v>1.2000000476837158</v>
+      </c>
+      <c r="O1177">
+        <f t="shared" ref="O1177:O1193" si="154">IF(A1177&lt;&gt;$K$61,MIN(O1176,VLOOKUP(A1177,A:D,4)),)</f>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1177">
+        <f t="shared" si="143"/>
+        <v>1.1863333384195964</v>
+      </c>
+      <c r="Q1177">
+        <f t="shared" si="132"/>
+        <v>1.161166665099916</v>
+      </c>
+      <c r="R1177">
+        <f t="shared" si="133"/>
+        <v>2.5166673319680477E-2</v>
+      </c>
+      <c r="S1177">
+        <f t="shared" si="134"/>
+        <v>1.378572270983742E-2</v>
+      </c>
+      <c r="T1177">
+        <f t="shared" si="135"/>
+        <v>2.0678584064756129E-4</v>
+      </c>
+      <c r="U1177">
+        <f t="shared" si="136"/>
+        <v>121.7040453102091</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1178" s="1">
+        <v>46149</v>
+      </c>
+      <c r="B1178">
+        <v>1.1929999589920044</v>
+      </c>
+      <c r="C1178">
+        <v>1.2059999704360962</v>
+      </c>
+      <c r="D1178">
+        <v>1.1890000104904175</v>
+      </c>
+      <c r="E1178">
+        <v>1.2050000429153442</v>
+      </c>
+      <c r="F1178">
+        <v>2515003</v>
+      </c>
+      <c r="G1178">
+        <v>25150.029296875</v>
+      </c>
+      <c r="H1178">
+        <f t="shared" si="144"/>
+        <v>1176</v>
+      </c>
+      <c r="I1178">
+        <f>SUM($F$3:F1178)/H1178</f>
+        <v>4071788.5306388182</v>
+      </c>
+      <c r="N1178">
+        <f t="shared" si="153"/>
+        <v>1.2059999704360962</v>
+      </c>
+      <c r="O1178">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1178">
+        <f t="shared" si="143"/>
+        <v>1.2000000079472859</v>
+      </c>
+      <c r="Q1178">
+        <f t="shared" si="132"/>
+        <v>1.1661666660081771</v>
+      </c>
+      <c r="R1178">
+        <f t="shared" si="133"/>
+        <v>3.3833341939108807E-2</v>
+      </c>
+      <c r="S1178">
+        <f t="shared" si="134"/>
+        <v>1.3690485840752022E-2</v>
+      </c>
+      <c r="T1178">
+        <f t="shared" si="135"/>
+        <v>2.0535728761128034E-4</v>
+      </c>
+      <c r="U1178">
+        <f t="shared" si="136"/>
+        <v>164.75354896170887</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1179" s="1">
+        <v>46150</v>
+      </c>
+      <c r="B1179">
+        <v>1.1970000267028809</v>
+      </c>
+      <c r="C1179">
+        <v>1.2050000429153442</v>
+      </c>
+      <c r="D1179">
+        <v>1.1950000524520874</v>
+      </c>
+      <c r="E1179">
+        <v>1.1959999799728394</v>
+      </c>
+      <c r="F1179">
+        <v>585700</v>
+      </c>
+      <c r="G1179">
+        <v>5857</v>
+      </c>
+      <c r="H1179">
+        <f t="shared" si="144"/>
+        <v>1177</v>
+      </c>
+      <c r="I1179">
+        <f>SUM($F$3:F1179)/H1179</f>
+        <v>4068826.6882168651</v>
+      </c>
+      <c r="N1179">
+        <f t="shared" si="153"/>
+        <v>1.2059999704360962</v>
+      </c>
+      <c r="O1179">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1179">
+        <f t="shared" si="143"/>
+        <v>1.1986666917800903</v>
+      </c>
+      <c r="Q1179">
+        <f t="shared" si="132"/>
+        <v>1.1712619066238403</v>
+      </c>
+      <c r="R1179">
+        <f t="shared" si="133"/>
+        <v>2.740478515625E-2</v>
+      </c>
+      <c r="S1179">
+        <f t="shared" si="134"/>
+        <v>1.2775511968703492E-2</v>
+      </c>
+      <c r="T1179">
+        <f t="shared" si="135"/>
+        <v>1.9163267953055236E-4</v>
+      </c>
+      <c r="U1179">
+        <f t="shared" si="136"/>
+        <v>143.00684634470605</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1180" s="1">
+        <v>46153</v>
+      </c>
+      <c r="B1180">
+        <v>1.2070000171661377</v>
+      </c>
+      <c r="C1180">
+        <v>1.2259999513626099</v>
+      </c>
+      <c r="D1180">
+        <v>1.2039999961853027</v>
+      </c>
+      <c r="E1180">
+        <v>1.2239999771118164</v>
+      </c>
+      <c r="F1180">
+        <v>1827702.875</v>
+      </c>
+      <c r="G1180">
+        <v>18277.029296875</v>
+      </c>
+      <c r="H1180">
+        <f t="shared" si="144"/>
+        <v>1178</v>
+      </c>
+      <c r="I1180">
+        <f>SUM($F$3:F1180)/H1180</f>
+        <v>4066924.2062022495</v>
+      </c>
+      <c r="N1180">
+        <f t="shared" si="153"/>
+        <v>1.2259999513626099</v>
+      </c>
+      <c r="O1180">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1180">
+        <f t="shared" si="143"/>
+        <v>1.2179999748865764</v>
+      </c>
+      <c r="Q1180">
+        <f t="shared" si="132"/>
+        <v>1.1766190500486464</v>
+      </c>
+      <c r="R1180">
+        <f t="shared" si="133"/>
+        <v>4.1380924837929989E-2</v>
+      </c>
+      <c r="S1180">
+        <f t="shared" si="134"/>
+        <v>1.4278913841766541E-2</v>
+      </c>
+      <c r="T1180">
+        <f t="shared" si="135"/>
+        <v>2.1418370762649809E-4</v>
+      </c>
+      <c r="U1180">
+        <f t="shared" si="136"/>
+        <v>193.2029531867646</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1181" s="1">
+        <v>46154</v>
+      </c>
+      <c r="B1181">
+        <v>1.2300000190734863</v>
+      </c>
+      <c r="C1181">
+        <v>1.2300000190734863</v>
+      </c>
+      <c r="D1181">
+        <v>1.2100000381469727</v>
+      </c>
+      <c r="E1181">
+        <v>1.2220000028610229</v>
+      </c>
+      <c r="F1181">
+        <v>2837503</v>
+      </c>
+      <c r="G1181">
+        <v>28375.029296875</v>
+      </c>
+      <c r="H1181">
+        <f t="shared" si="144"/>
+        <v>1179</v>
+      </c>
+      <c r="I1181">
+        <f>SUM($F$3:F1181)/H1181</f>
+        <v>4065881.4401240456</v>
+      </c>
+      <c r="N1181">
+        <f t="shared" si="153"/>
+        <v>1.2300000190734863</v>
+      </c>
+      <c r="O1181">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1181">
+        <f t="shared" si="143"/>
+        <v>1.2206666866938274</v>
+      </c>
+      <c r="Q1181">
+        <f t="shared" si="132"/>
+        <v>1.1814285743804205</v>
+      </c>
+      <c r="R1181">
+        <f t="shared" si="133"/>
+        <v>3.9238112313406903E-2</v>
+      </c>
+      <c r="S1181">
+        <f t="shared" si="134"/>
+        <v>1.6646261117896244E-2</v>
+      </c>
+      <c r="T1181">
+        <f t="shared" si="135"/>
+        <v>2.4969391676844365E-4</v>
+      </c>
+      <c r="U1181">
+        <f t="shared" si="136"/>
+        <v>157.14484686382966</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1182" s="1">
+        <v>46155</v>
+      </c>
+      <c r="B1182">
+        <v>1.2220000028610229</v>
+      </c>
+      <c r="C1182">
+        <v>1.2430000305175781</v>
+      </c>
+      <c r="D1182">
+        <v>1.2150000333786011</v>
+      </c>
+      <c r="E1182">
+        <v>1.2430000305175781</v>
+      </c>
+      <c r="F1182">
+        <v>3813105.75</v>
+      </c>
+      <c r="G1182">
+        <v>38131.05859375</v>
+      </c>
+      <c r="H1182">
+        <f t="shared" si="144"/>
+        <v>1180</v>
+      </c>
+      <c r="I1182">
+        <f>SUM($F$3:F1182)/H1182</f>
+        <v>4065667.2234375002</v>
+      </c>
+      <c r="N1182">
+        <f t="shared" si="153"/>
+        <v>1.2430000305175781</v>
+      </c>
+      <c r="O1182">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1182">
+        <f t="shared" si="143"/>
+        <v>1.2336666981379192</v>
+      </c>
+      <c r="Q1182">
+        <f t="shared" si="132"/>
+        <v>1.1867142915725708</v>
+      </c>
+      <c r="R1182">
+        <f t="shared" si="133"/>
+        <v>4.6952406565348381E-2</v>
+      </c>
+      <c r="S1182">
+        <f t="shared" si="134"/>
+        <v>1.9632657368977853E-2</v>
+      </c>
+      <c r="T1182">
+        <f t="shared" si="135"/>
+        <v>2.9448986053466777E-4</v>
+      </c>
+      <c r="U1182">
+        <f t="shared" si="136"/>
+        <v>159.43641142721475</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1183" s="1">
+        <v>46156</v>
+      </c>
+      <c r="B1183">
+        <v>1.2389999628067017</v>
+      </c>
+      <c r="C1183">
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="D1183">
+        <v>1.2150000333786011</v>
+      </c>
+      <c r="E1183">
+        <v>1.2239999771118164</v>
+      </c>
+      <c r="F1183">
+        <v>1523502</v>
+      </c>
+      <c r="G1183">
+        <v>15235.01953125</v>
+      </c>
+      <c r="H1183">
+        <f t="shared" si="144"/>
+        <v>1181</v>
+      </c>
+      <c r="I1183">
+        <f>SUM($F$3:F1183)/H1183</f>
+        <v>4063514.6703270534</v>
+      </c>
+      <c r="N1183">
+        <f t="shared" si="153"/>
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="O1183">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1183">
+        <f t="shared" si="143"/>
+        <v>1.2316666841506958</v>
+      </c>
+      <c r="Q1183">
+        <f t="shared" si="132"/>
+        <v>1.1918809584208898</v>
+      </c>
+      <c r="R1183">
+        <f t="shared" si="133"/>
+        <v>3.9785725729805987E-2</v>
+      </c>
+      <c r="S1183">
+        <f t="shared" si="134"/>
+        <v>2.1625856153008081E-2</v>
+      </c>
+      <c r="T1183">
+        <f t="shared" si="135"/>
+        <v>3.2438784229512122E-4</v>
+      </c>
+      <c r="U1183">
+        <f t="shared" si="136"/>
+        <v>122.64863395715605</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1184" s="1">
+        <v>46157</v>
+      </c>
+      <c r="B1184">
+        <v>1.218999981880188</v>
+      </c>
+      <c r="C1184">
+        <v>1.2319999933242798</v>
+      </c>
+      <c r="D1184">
+        <v>1.2000000476837158</v>
+      </c>
+      <c r="E1184">
+        <v>1.2100000381469727</v>
+      </c>
+      <c r="F1184">
+        <v>2310300</v>
+      </c>
+      <c r="G1184">
+        <v>23103</v>
+      </c>
+      <c r="H1184">
+        <f t="shared" si="144"/>
+        <v>1182</v>
+      </c>
+      <c r="I1184">
+        <f>SUM($F$3:F1184)/H1184</f>
+        <v>4062031.4091846445</v>
+      </c>
+      <c r="N1184">
+        <f t="shared" si="153"/>
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="O1184">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1184">
+        <f t="shared" si="143"/>
+        <v>1.2140000263849895</v>
+      </c>
+      <c r="Q1184">
+        <f t="shared" si="132"/>
+        <v>1.1946428673607963</v>
+      </c>
+      <c r="R1184">
+        <f t="shared" si="133"/>
+        <v>1.9357159024193216E-2</v>
+      </c>
+      <c r="S1184">
+        <f t="shared" si="134"/>
+        <v>2.2023814065115794E-2</v>
+      </c>
+      <c r="T1184">
+        <f t="shared" si="135"/>
+        <v>3.3035721097673688E-4</v>
+      </c>
+      <c r="U1184">
+        <f t="shared" si="136"/>
+        <v>58.594631450488635</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1185" s="1">
+        <v>46160</v>
+      </c>
+      <c r="B1185">
+        <v>1.2009999752044678</v>
+      </c>
+      <c r="C1185">
+        <v>1.2150000333786011</v>
+      </c>
+      <c r="D1185">
+        <v>1.1959999799728394</v>
+      </c>
+      <c r="E1185">
+        <v>1.2029999494552612</v>
+      </c>
+      <c r="F1185">
+        <v>1285802</v>
+      </c>
+      <c r="G1185">
+        <v>12858.01953125</v>
+      </c>
+      <c r="H1185">
+        <f t="shared" si="144"/>
+        <v>1183</v>
+      </c>
+      <c r="I1185">
+        <f>SUM($F$3:F1185)/H1185</f>
+        <v>4059684.6387626794</v>
+      </c>
+      <c r="N1185">
+        <f t="shared" si="153"/>
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="O1185">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1185">
+        <f t="shared" si="143"/>
+        <v>1.2046666542689006</v>
+      </c>
+      <c r="Q1185">
+        <f t="shared" si="132"/>
+        <v>1.1965714380854651</v>
+      </c>
+      <c r="R1185">
+        <f t="shared" si="133"/>
+        <v>8.0952161834355607E-3</v>
+      </c>
+      <c r="S1185">
+        <f t="shared" si="134"/>
+        <v>2.1251702795223339E-2</v>
+      </c>
+      <c r="T1185">
+        <f t="shared" si="135"/>
+        <v>3.1877554192835011E-4</v>
+      </c>
+      <c r="U1185">
+        <f t="shared" si="136"/>
+        <v>25.39472173575691</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1186" s="1">
+        <v>46161</v>
+      </c>
+      <c r="B1186">
+        <v>1.1929999589920044</v>
+      </c>
+      <c r="C1186">
+        <v>1.2029999494552612</v>
+      </c>
+      <c r="D1186">
+        <v>1.1779999732971191</v>
+      </c>
+      <c r="E1186">
+        <v>1.2029999494552612</v>
+      </c>
+      <c r="F1186">
+        <v>1353000</v>
+      </c>
+      <c r="G1186">
+        <v>13530</v>
+      </c>
+      <c r="H1186">
+        <f t="shared" si="144"/>
+        <v>1184</v>
+      </c>
+      <c r="I1186">
+        <f>SUM($F$3:F1186)/H1186</f>
+        <v>4057398.5875475085</v>
+      </c>
+      <c r="N1186">
+        <f t="shared" si="153"/>
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="O1186">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1186">
+        <f t="shared" si="143"/>
+        <v>1.1946666240692139</v>
+      </c>
+      <c r="Q1186">
+        <f t="shared" si="132"/>
+        <v>1.1986428641137619</v>
+      </c>
+      <c r="R1186">
+        <f t="shared" si="133"/>
+        <v>-3.9762400445479962E-3</v>
+      </c>
+      <c r="S1186">
+        <f t="shared" si="134"/>
+        <v>1.8884358762883875E-2</v>
+      </c>
+      <c r="T1186">
+        <f t="shared" si="135"/>
+        <v>2.832653814432581E-4</v>
+      </c>
+      <c r="U1186">
+        <f t="shared" si="136"/>
+        <v>-14.037154926199449</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1187" s="1">
+        <v>46162</v>
+      </c>
+      <c r="B1187">
+        <v>1.1940000057220459</v>
+      </c>
+      <c r="C1187">
+        <v>1.2050000429153442</v>
+      </c>
+      <c r="D1187">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="E1187">
+        <v>1.1990000009536743</v>
+      </c>
+      <c r="F1187">
+        <v>1973003.875</v>
+      </c>
+      <c r="G1187">
+        <v>19730.0390625</v>
+      </c>
+      <c r="H1187">
+        <f t="shared" si="144"/>
+        <v>1185</v>
+      </c>
+      <c r="I1187">
+        <f>SUM($F$3:F1187)/H1187</f>
+        <v>4055639.6046677213</v>
+      </c>
+      <c r="N1187">
+        <f t="shared" si="153"/>
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="O1187">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1187">
+        <f t="shared" si="143"/>
+        <v>1.1983333428700764</v>
+      </c>
+      <c r="Q1187">
+        <f t="shared" si="132"/>
+        <v>1.200595242636544</v>
+      </c>
+      <c r="R1187">
+        <f t="shared" si="133"/>
+        <v>-2.2618997664676233E-3</v>
+      </c>
+      <c r="S1187">
+        <f t="shared" si="134"/>
+        <v>1.7013609814806024E-2</v>
+      </c>
+      <c r="T1187">
+        <f t="shared" si="135"/>
+        <v>2.5520414722209034E-4</v>
+      </c>
+      <c r="U1187">
+        <f t="shared" si="136"/>
+        <v>-8.8630995659299163</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1188" s="1">
+        <v>46163</v>
+      </c>
+      <c r="B1188">
+        <v>1.2109999656677246</v>
+      </c>
+      <c r="C1188">
+        <v>1.2319999933242798</v>
+      </c>
+      <c r="D1188">
+        <v>1.1859999895095825</v>
+      </c>
+      <c r="E1188">
+        <v>1.1859999895095825</v>
+      </c>
+      <c r="F1188">
+        <v>4589602</v>
+      </c>
+      <c r="G1188">
+        <v>45896.01953125</v>
+      </c>
+      <c r="H1188">
+        <f t="shared" si="144"/>
+        <v>1186</v>
+      </c>
+      <c r="I1188">
+        <f>SUM($F$3:F1188)/H1188</f>
+        <v>4056089.8259116779</v>
+      </c>
+      <c r="N1188">
+        <f t="shared" si="153"/>
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="O1188">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1188">
+        <f t="shared" si="143"/>
+        <v>1.2013333241144817</v>
+      </c>
+      <c r="Q1188">
+        <f t="shared" si="132"/>
+        <v>1.203619054385594</v>
+      </c>
+      <c r="R1188">
+        <f t="shared" si="133"/>
+        <v>-2.2857302711123406E-3</v>
+      </c>
+      <c r="S1188">
+        <f t="shared" si="134"/>
+        <v>1.4421771172763569E-2</v>
+      </c>
+      <c r="T1188">
+        <f t="shared" si="135"/>
+        <v>2.1632656759145352E-4</v>
+      </c>
+      <c r="U1188">
+        <f t="shared" si="136"/>
+        <v>-10.56610982442567</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1189" s="1">
+        <v>46164</v>
+      </c>
+      <c r="B1189">
+        <v>1.190000057220459</v>
+      </c>
+      <c r="C1189">
+        <v>1.2150000333786011</v>
+      </c>
+      <c r="D1189">
+        <v>1.190000057220459</v>
+      </c>
+      <c r="E1189">
+        <v>1.2150000333786011</v>
+      </c>
+      <c r="F1189">
+        <v>3018704</v>
+      </c>
+      <c r="G1189">
+        <v>30187.0390625</v>
+      </c>
+      <c r="H1189">
+        <f t="shared" si="144"/>
+        <v>1187</v>
+      </c>
+      <c r="I1189">
+        <f>SUM($F$3:F1189)/H1189</f>
+        <v>4055215.8698662594</v>
+      </c>
+      <c r="N1189">
+        <f t="shared" si="153"/>
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="O1189">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1189">
+        <f t="shared" si="143"/>
+        <v>1.2066667079925537</v>
+      </c>
+      <c r="Q1189">
+        <f t="shared" si="132"/>
+        <v>1.206261912981669</v>
+      </c>
+      <c r="R1189">
+        <f t="shared" si="133"/>
+        <v>4.0479501088475089E-4</v>
+      </c>
+      <c r="S1189">
+        <f t="shared" si="134"/>
+        <v>1.2442185765221001E-2</v>
+      </c>
+      <c r="T1189">
+        <f t="shared" si="135"/>
+        <v>1.8663278647831501E-4</v>
+      </c>
+      <c r="U1189">
+        <f t="shared" si="136"/>
+        <v>2.1689383656701944</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1190" s="1">
+        <v>46167</v>
+      </c>
+      <c r="B1190">
+        <v>1.2239999771118164</v>
+      </c>
+      <c r="C1190">
+        <v>1.2380000352859497</v>
+      </c>
+      <c r="D1190">
+        <v>1.2109999656677246</v>
+      </c>
+      <c r="E1190">
+        <v>1.2359999418258667</v>
+      </c>
+      <c r="F1190">
+        <v>1636907</v>
+      </c>
+      <c r="G1190">
+        <v>16369.0703125</v>
+      </c>
+      <c r="H1190">
+        <f t="shared" si="144"/>
+        <v>1188</v>
+      </c>
+      <c r="I1190">
+        <f>SUM($F$3:F1190)/H1190</f>
+        <v>4053180.2563394359</v>
+      </c>
+      <c r="N1190">
+        <f t="shared" si="153"/>
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="O1190">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1190">
+        <f t="shared" si="143"/>
+        <v>1.2283333142598469</v>
+      </c>
+      <c r="Q1190">
+        <f t="shared" si="132"/>
+        <v>1.2097857197125752</v>
+      </c>
+      <c r="R1190">
+        <f t="shared" si="133"/>
+        <v>1.8547594547271729E-2</v>
+      </c>
+      <c r="S1190">
+        <f t="shared" si="134"/>
+        <v>1.2517009462629045E-2</v>
+      </c>
+      <c r="T1190">
+        <f t="shared" si="135"/>
+        <v>1.8775514193943566E-4</v>
+      </c>
+      <c r="U1190">
+        <f t="shared" si="136"/>
+        <v>98.786080400688263</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1191" s="1">
+        <v>46168</v>
+      </c>
+      <c r="B1191">
+        <v>1.2630000114440918</v>
+      </c>
+      <c r="C1191">
+        <v>1.2630000114440918</v>
+      </c>
+      <c r="D1191">
+        <v>1.2130000591278076</v>
+      </c>
+      <c r="E1191">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="F1191">
+        <v>2589104</v>
+      </c>
+      <c r="G1191">
+        <v>25891.0390625</v>
+      </c>
+      <c r="H1191">
+        <f t="shared" si="144"/>
+        <v>1189</v>
+      </c>
+      <c r="I1191">
+        <f>SUM($F$3:F1191)/H1191</f>
+        <v>4051948.905408957</v>
+      </c>
+      <c r="N1191">
+        <f t="shared" si="153"/>
+        <v>1.2630000114440918</v>
+      </c>
+      <c r="O1191">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1191">
+        <f t="shared" si="143"/>
+        <v>1.2403333584467571</v>
+      </c>
+      <c r="Q1191">
+        <f t="shared" si="132"/>
+        <v>1.2136428640002297</v>
+      </c>
+      <c r="R1191">
+        <f t="shared" si="133"/>
+        <v>2.669049444652738E-2</v>
+      </c>
+      <c r="S1191">
+        <f t="shared" si="134"/>
+        <v>1.3023813565572124E-2</v>
+      </c>
+      <c r="T1191">
+        <f t="shared" si="135"/>
+        <v>1.9535720348358185E-4</v>
+      </c>
+      <c r="U1191">
+        <f t="shared" si="136"/>
+        <v>136.62406080035075</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1192" s="1">
+        <v>46169</v>
+      </c>
+      <c r="B1192">
+        <v>1.2439999580383301</v>
+      </c>
+      <c r="C1192">
+        <v>1.2640000581741333</v>
+      </c>
+      <c r="D1192">
+        <v>1.2350000143051147</v>
+      </c>
+      <c r="E1192">
+        <v>1.2389999628067017</v>
+      </c>
+      <c r="F1192">
+        <v>1705300</v>
+      </c>
+      <c r="G1192">
+        <v>17053</v>
+      </c>
+      <c r="H1192">
+        <f t="shared" si="144"/>
+        <v>1190</v>
+      </c>
+      <c r="I1192">
+        <f>SUM($F$3:F1192)/H1192</f>
+        <v>4049976.9315388654</v>
+      </c>
+      <c r="N1192">
+        <f t="shared" si="153"/>
+        <v>1.2640000581741333</v>
+      </c>
+      <c r="O1192">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1192">
+        <f t="shared" si="143"/>
+        <v>1.2460000117619832</v>
+      </c>
+      <c r="Q1192">
+        <f t="shared" si="132"/>
+        <v>1.2169285785584223</v>
+      </c>
+      <c r="R1192">
+        <f t="shared" si="133"/>
+        <v>2.907143320356087E-2</v>
+      </c>
+      <c r="S1192">
+        <f t="shared" si="134"/>
+        <v>1.4309525489807129E-2</v>
+      </c>
+      <c r="T1192">
+        <f t="shared" si="135"/>
+        <v>2.1464288234710691E-4</v>
+      </c>
+      <c r="U1192">
+        <f t="shared" si="136"/>
+        <v>135.44093745698208</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1193" s="1">
+        <v>46170</v>
+      </c>
+      <c r="B1193">
+        <v>1.25</v>
+      </c>
+      <c r="C1193">
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="D1193">
+        <v>1.2209999561309814</v>
+      </c>
+      <c r="E1193">
+        <v>1.2519999742507935</v>
+      </c>
+      <c r="F1193">
+        <v>2592805</v>
+      </c>
+      <c r="G1193">
+        <v>25928.05078125</v>
+      </c>
+      <c r="H1193">
+        <f t="shared" si="144"/>
+        <v>1191</v>
+      </c>
+      <c r="I1193">
+        <f>SUM($F$3:F1193)/H1193</f>
+        <v>4048753.4454502519</v>
+      </c>
+      <c r="N1193">
+        <f t="shared" si="153"/>
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="O1193">
+        <f t="shared" si="154"/>
+        <v>1.1660000085830688</v>
+      </c>
+      <c r="P1193">
+        <f t="shared" si="143"/>
+        <v>1.246999979019165</v>
+      </c>
+      <c r="Q1193">
+        <f t="shared" si="132"/>
+        <v>1.2203809562183563</v>
+      </c>
+      <c r="R1193">
+        <f t="shared" si="133"/>
+        <v>2.6619022800808745E-2</v>
+      </c>
+      <c r="S1193">
+        <f t="shared" si="134"/>
+        <v>1.5000005563100169E-2</v>
+      </c>
+      <c r="T1193">
+        <f t="shared" si="135"/>
+        <v>2.2500008344650252E-4</v>
+      </c>
+      <c r="U1193">
+        <f t="shared" si="136"/>
+        <v>118.30672412678396</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1193"/>
+  <dimension ref="A1:U1194"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4341,7 +4341,7 @@
         <v>-117.56885090218483</v>
       </c>
     </row>
-    <row r="62" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A62" s="1">
         <v>44456</v>
       </c>
@@ -4371,6 +4371,12 @@
         <f>SUM($F$3:F62)/H62</f>
         <v>17833232.983333334</v>
       </c>
+      <c r="K62" s="2">
+        <v>46171</v>
+      </c>
+      <c r="L62" s="2">
+        <v>46148</v>
+      </c>
       <c r="N62">
         <f t="shared" si="11"/>
         <v>0.98799999999999999</v>
@@ -65809,23 +65815,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1193" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1194" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1193" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1194" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1193" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1194" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1193" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1194" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1193" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1194" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68955,7 +68961,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1193" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1194" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69065,7 +69071,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1193" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1194" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -74617,11 +74623,11 @@
         <v>4073113.4544946807</v>
       </c>
       <c r="N1177">
-        <f t="shared" ref="N1177:N1193" si="153">IF(A1177&lt;&gt;$K$61,MAX(N1176,VLOOKUP(A1177,A:C,3)),)</f>
+        <f t="shared" ref="N1177:N1194" si="153">IF(A1177&lt;&gt;$K$61,MAX(N1176,VLOOKUP(A1177,A:C,3)),)</f>
         <v>1.2000000476837158</v>
       </c>
       <c r="O1177">
-        <f t="shared" ref="O1177:O1193" si="154">IF(A1177&lt;&gt;$K$61,MIN(O1176,VLOOKUP(A1177,A:D,4)),)</f>
+        <f t="shared" ref="O1177:O1194" si="154">IF(A1177&lt;&gt;$K$61,MIN(O1176,VLOOKUP(A1177,A:D,4)),)</f>
         <v>1.1660000085830688</v>
       </c>
       <c r="P1177">
@@ -75655,6 +75661,69 @@
       <c r="U1193">
         <f t="shared" si="136"/>
         <v>118.30672412678396</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1194" s="1">
+        <v>46171</v>
+      </c>
+      <c r="B1194">
+        <v>1.2519999742507935</v>
+      </c>
+      <c r="C1194">
+        <v>1.2680000066757202</v>
+      </c>
+      <c r="D1194">
+        <v>1.2369999885559082</v>
+      </c>
+      <c r="E1194">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="F1194">
+        <v>2806705</v>
+      </c>
+      <c r="G1194">
+        <v>28067.05078125</v>
+      </c>
+      <c r="H1194">
+        <f t="shared" si="144"/>
+        <v>1192</v>
+      </c>
+      <c r="I1194">
+        <f>SUM($F$3:F1194)/H1194</f>
+        <v>4047711.4584993706</v>
+      </c>
+      <c r="N1194">
+        <f t="shared" si="153"/>
+        <v>0</v>
+      </c>
+      <c r="O1194">
+        <f t="shared" si="154"/>
+        <v>0</v>
+      </c>
+      <c r="P1194">
+        <f t="shared" si="143"/>
+        <v>1.25</v>
+      </c>
+      <c r="Q1194">
+        <f t="shared" si="132"/>
+        <v>1.2226666722978865</v>
+      </c>
+      <c r="R1194">
+        <f t="shared" si="133"/>
+        <v>2.7333327702113497E-2</v>
+      </c>
+      <c r="S1194">
+        <f t="shared" si="134"/>
+        <v>1.6904762813023142E-2</v>
+      </c>
+      <c r="T1194">
+        <f t="shared" si="135"/>
+        <v>2.5357144219534714E-4</v>
+      </c>
+      <c r="U1194">
+        <f t="shared" si="136"/>
+        <v>107.7933992308817</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1194"/>
+  <dimension ref="A1:U1214"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4372,10 +4372,10 @@
         <v>17833232.983333334</v>
       </c>
       <c r="K62" s="2">
-        <v>46171</v>
+        <v>46203</v>
       </c>
       <c r="L62" s="2">
-        <v>46148</v>
+        <v>46174</v>
       </c>
       <c r="N62">
         <f t="shared" si="11"/>
@@ -65815,23 +65815,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1194" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1214" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1194" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1214" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1194" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1214" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1194" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1214" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1194" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1214" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68961,7 +68961,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1194" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1214" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69071,7 +69071,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1194" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1214" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -74623,11 +74623,11 @@
         <v>4073113.4544946807</v>
       </c>
       <c r="N1177">
-        <f t="shared" ref="N1177:N1194" si="153">IF(A1177&lt;&gt;$K$61,MAX(N1176,VLOOKUP(A1177,A:C,3)),)</f>
+        <f t="shared" ref="N1177:N1193" si="153">IF(A1177&lt;&gt;$K$61,MAX(N1176,VLOOKUP(A1177,A:C,3)),)</f>
         <v>1.2000000476837158</v>
       </c>
       <c r="O1177">
-        <f t="shared" ref="O1177:O1194" si="154">IF(A1177&lt;&gt;$K$61,MIN(O1176,VLOOKUP(A1177,A:D,4)),)</f>
+        <f t="shared" ref="O1177:O1193" si="154">IF(A1177&lt;&gt;$K$61,MIN(O1176,VLOOKUP(A1177,A:D,4)),)</f>
         <v>1.1660000085830688</v>
       </c>
       <c r="P1177">
@@ -75694,12 +75694,12 @@
         <v>4047711.4584993706</v>
       </c>
       <c r="N1194">
-        <f t="shared" si="153"/>
-        <v>0</v>
+        <f>VLOOKUP(L62,A:C,3)</f>
+        <v>1.2489999532699585</v>
       </c>
       <c r="O1194">
-        <f t="shared" si="154"/>
-        <v>0</v>
+        <f>VLOOKUP(L62,A:D,4)</f>
+        <v>1.218000054359436</v>
       </c>
       <c r="P1194">
         <f t="shared" si="143"/>
@@ -75724,6 +75724,1266 @@
       <c r="U1194">
         <f t="shared" si="136"/>
         <v>107.7933992308817</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1195" s="1">
+        <v>46174</v>
+      </c>
+      <c r="B1195">
+        <v>1.2410000562667847</v>
+      </c>
+      <c r="C1195">
+        <v>1.2489999532699585</v>
+      </c>
+      <c r="D1195">
+        <v>1.218000054359436</v>
+      </c>
+      <c r="E1195">
+        <v>1.2209999561309814</v>
+      </c>
+      <c r="F1195">
+        <v>2885709</v>
+      </c>
+      <c r="G1195">
+        <v>28857.08984375</v>
+      </c>
+      <c r="H1195">
+        <f t="shared" si="144"/>
+        <v>1193</v>
+      </c>
+      <c r="I1195">
+        <f>SUM($F$3:F1195)/H1195</f>
+        <v>4046737.4413505867</v>
+      </c>
+      <c r="N1195">
+        <f t="shared" ref="N1195:N1214" si="155">IF(A1195&lt;&gt;$K$62,MAX(N1194,VLOOKUP(A1195,A:C,3)),)</f>
+        <v>1.2489999532699585</v>
+      </c>
+      <c r="O1195">
+        <f t="shared" ref="O1195:O1214" si="156">IF(A1195&lt;&gt;$K$62,MIN(O1194,VLOOKUP(A1195,A:D,4)),)</f>
+        <v>1.218000054359436</v>
+      </c>
+      <c r="P1195">
+        <f t="shared" si="143"/>
+        <v>1.2293333212534587</v>
+      </c>
+      <c r="Q1195">
+        <f t="shared" si="132"/>
+        <v>1.2232857176235743</v>
+      </c>
+      <c r="R1195">
+        <f t="shared" si="133"/>
+        <v>6.0476036298844349E-3</v>
+      </c>
+      <c r="S1195">
+        <f t="shared" si="134"/>
+        <v>1.7149660863032965E-2</v>
+      </c>
+      <c r="T1195">
+        <f t="shared" si="135"/>
+        <v>2.5724491294549449E-4</v>
+      </c>
+      <c r="U1195">
+        <f t="shared" si="136"/>
+        <v>23.509128171431758</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1196" s="1">
+        <v>46175</v>
+      </c>
+      <c r="B1196">
+        <v>1.2350000143051147</v>
+      </c>
+      <c r="C1196">
+        <v>1.2519999742507935</v>
+      </c>
+      <c r="D1196">
+        <v>1.2170000076293945</v>
+      </c>
+      <c r="E1196">
+        <v>1.2489999532699585</v>
+      </c>
+      <c r="F1196">
+        <v>4139100</v>
+      </c>
+      <c r="G1196">
+        <v>41391</v>
+      </c>
+      <c r="H1196">
+        <f t="shared" si="144"/>
+        <v>1194</v>
+      </c>
+      <c r="I1196">
+        <f>SUM($F$3:F1196)/H1196</f>
+        <v>4046814.796927345</v>
+      </c>
+      <c r="N1196">
+        <f t="shared" si="155"/>
+        <v>1.2519999742507935</v>
+      </c>
+      <c r="O1196">
+        <f t="shared" si="156"/>
+        <v>1.2170000076293945</v>
+      </c>
+      <c r="P1196">
+        <f t="shared" si="143"/>
+        <v>1.2393333117167156</v>
+      </c>
+      <c r="Q1196">
+        <f t="shared" si="132"/>
+        <v>1.2236904757363456</v>
+      </c>
+      <c r="R1196">
+        <f t="shared" si="133"/>
+        <v>1.5642835980369973E-2</v>
+      </c>
+      <c r="S1196">
+        <f t="shared" si="134"/>
+        <v>1.7496596388265378E-2</v>
+      </c>
+      <c r="T1196">
+        <f t="shared" si="135"/>
+        <v>2.6244894582398064E-4</v>
+      </c>
+      <c r="U1196">
+        <f t="shared" si="136"/>
+        <v>59.6033484960588</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1197" s="1">
+        <v>46176</v>
+      </c>
+      <c r="B1197">
+        <v>1.2539999485015869</v>
+      </c>
+      <c r="C1197">
+        <v>1.281000018119812</v>
+      </c>
+      <c r="D1197">
+        <v>1.2480000257492065</v>
+      </c>
+      <c r="E1197">
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="F1197">
+        <v>4913218</v>
+      </c>
+      <c r="G1197">
+        <v>49132.1796875</v>
+      </c>
+      <c r="H1197">
+        <f t="shared" si="144"/>
+        <v>1195</v>
+      </c>
+      <c r="I1197">
+        <f>SUM($F$3:F1197)/H1197</f>
+        <v>4047539.8205282427</v>
+      </c>
+      <c r="N1197">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1197">
+        <f t="shared" si="156"/>
+        <v>1.2170000076293945</v>
+      </c>
+      <c r="P1197">
+        <f t="shared" si="143"/>
+        <v>1.2616666952768962</v>
+      </c>
+      <c r="Q1197">
+        <f t="shared" si="132"/>
+        <v>1.2258333336739313</v>
+      </c>
+      <c r="R1197">
+        <f t="shared" si="133"/>
+        <v>3.5833361602964908E-2</v>
+      </c>
+      <c r="S1197">
+        <f t="shared" si="134"/>
+        <v>1.9333331763338877E-2</v>
+      </c>
+      <c r="T1197">
+        <f t="shared" si="135"/>
+        <v>2.8999997645008316E-4</v>
+      </c>
+      <c r="U1197">
+        <f t="shared" si="136"/>
+        <v>123.56332590645158</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1198" s="1">
+        <v>46177</v>
+      </c>
+      <c r="B1198">
+        <v>1.2699999809265137</v>
+      </c>
+      <c r="C1198">
+        <v>1.2699999809265137</v>
+      </c>
+      <c r="D1198">
+        <v>1.25</v>
+      </c>
+      <c r="E1198">
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="F1198">
+        <v>2417115</v>
+      </c>
+      <c r="G1198">
+        <v>24171.150390625</v>
+      </c>
+      <c r="H1198">
+        <f t="shared" si="144"/>
+        <v>1196</v>
+      </c>
+      <c r="I1198">
+        <f>SUM($F$3:F1198)/H1198</f>
+        <v>4046176.5890729516</v>
+      </c>
+      <c r="N1198">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1198">
+        <f t="shared" si="156"/>
+        <v>1.2170000076293945</v>
+      </c>
+      <c r="P1198">
+        <f t="shared" si="143"/>
+        <v>1.2586666742960613</v>
+      </c>
+      <c r="Q1198">
+        <f t="shared" si="132"/>
+        <v>1.229023808524722</v>
+      </c>
+      <c r="R1198">
+        <f t="shared" si="133"/>
+        <v>2.9642865771339233E-2</v>
+      </c>
+      <c r="S1198">
+        <f t="shared" si="134"/>
+        <v>2.0020411939037124E-2</v>
+      </c>
+      <c r="T1198">
+        <f t="shared" si="135"/>
+        <v>3.0030617908555684E-4</v>
+      </c>
+      <c r="U1198">
+        <f t="shared" si="136"/>
+        <v>98.708810659849988</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1199" s="1">
+        <v>46178</v>
+      </c>
+      <c r="B1199">
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="C1199">
+        <v>1.2599999904632568</v>
+      </c>
+      <c r="D1199">
+        <v>1.218000054359436</v>
+      </c>
+      <c r="E1199">
+        <v>1.2239999771118164</v>
+      </c>
+      <c r="F1199">
+        <v>2687302</v>
+      </c>
+      <c r="G1199">
+        <v>26873.01953125</v>
+      </c>
+      <c r="H1199">
+        <f t="shared" si="144"/>
+        <v>1197</v>
+      </c>
+      <c r="I1199">
+        <f>SUM($F$3:F1199)/H1199</f>
+        <v>4045041.3554981202</v>
+      </c>
+      <c r="N1199">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1199">
+        <f t="shared" si="156"/>
+        <v>1.2170000076293945</v>
+      </c>
+      <c r="P1199">
+        <f t="shared" si="143"/>
+        <v>1.2340000073115032</v>
+      </c>
+      <c r="Q1199">
+        <f t="shared" si="132"/>
+        <v>1.2311190480277652</v>
+      </c>
+      <c r="R1199">
+        <f t="shared" si="133"/>
+        <v>2.8809592837379938E-3</v>
+      </c>
+      <c r="S1199">
+        <f t="shared" si="134"/>
+        <v>1.8292521943851416E-2</v>
+      </c>
+      <c r="T1199">
+        <f t="shared" si="135"/>
+        <v>2.7438782915777121E-4</v>
+      </c>
+      <c r="U1199">
+        <f t="shared" si="136"/>
+        <v>10.49958845689712</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1200" s="1">
+        <v>46181</v>
+      </c>
+      <c r="B1200">
+        <v>1.2120000123977661</v>
+      </c>
+      <c r="C1200">
+        <v>1.2120000123977661</v>
+      </c>
+      <c r="D1200">
+        <v>1.1829999685287476</v>
+      </c>
+      <c r="E1200">
+        <v>1.1890000104904175</v>
+      </c>
+      <c r="F1200">
+        <v>2282700</v>
+      </c>
+      <c r="G1200">
+        <v>22827</v>
+      </c>
+      <c r="H1200">
+        <f t="shared" si="144"/>
+        <v>1198</v>
+      </c>
+      <c r="I1200">
+        <f>SUM($F$3:F1200)/H1200</f>
+        <v>4043570.2859192402</v>
+      </c>
+      <c r="N1200">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1200">
+        <f t="shared" si="156"/>
+        <v>1.1829999685287476</v>
+      </c>
+      <c r="P1200">
+        <f t="shared" si="143"/>
+        <v>1.1946666638056438</v>
+      </c>
+      <c r="Q1200">
+        <f t="shared" si="132"/>
+        <v>1.2311190508660814</v>
+      </c>
+      <c r="R1200">
+        <f t="shared" si="133"/>
+        <v>-3.645238706043763E-2</v>
+      </c>
+      <c r="S1200">
+        <f t="shared" si="134"/>
+        <v>1.8292518700061242E-2</v>
+      </c>
+      <c r="T1200">
+        <f t="shared" si="135"/>
+        <v>2.7438778050091863E-4</v>
+      </c>
+      <c r="U1200">
+        <f t="shared" si="136"/>
+        <v>-132.84989219961125</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1201" s="1">
+        <v>46182</v>
+      </c>
+      <c r="B1201">
+        <v>1.2000000476837158</v>
+      </c>
+      <c r="C1201">
+        <v>1.2300000190734863</v>
+      </c>
+      <c r="D1201">
+        <v>1.1929999589920044</v>
+      </c>
+      <c r="E1201">
+        <v>1.2230000495910645</v>
+      </c>
+      <c r="F1201">
+        <v>3061100</v>
+      </c>
+      <c r="G1201">
+        <v>30611</v>
+      </c>
+      <c r="H1201">
+        <f t="shared" si="144"/>
+        <v>1199</v>
+      </c>
+      <c r="I1201">
+        <f>SUM($F$3:F1201)/H1201</f>
+        <v>4042750.8778409092</v>
+      </c>
+      <c r="N1201">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1201">
+        <f t="shared" si="156"/>
+        <v>1.1829999685287476</v>
+      </c>
+      <c r="P1201">
+        <f t="shared" si="143"/>
+        <v>1.2153333425521851</v>
+      </c>
+      <c r="Q1201">
+        <f t="shared" si="132"/>
+        <v>1.2323333365576605</v>
+      </c>
+      <c r="R1201">
+        <f t="shared" si="133"/>
+        <v>-1.6999994005475472E-2</v>
+      </c>
+      <c r="S1201">
+        <f t="shared" si="134"/>
+        <v>1.6904763623970753E-2</v>
+      </c>
+      <c r="T1201">
+        <f t="shared" si="135"/>
+        <v>2.5357145435956128E-4</v>
+      </c>
+      <c r="U1201">
+        <f t="shared" si="136"/>
+        <v>-67.042223062575829</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1202" s="1">
+        <v>46183</v>
+      </c>
+      <c r="B1202">
+        <v>1.2109999656677246</v>
+      </c>
+      <c r="C1202">
+        <v>1.2289999723434448</v>
+      </c>
+      <c r="D1202">
+        <v>1.190000057220459</v>
+      </c>
+      <c r="E1202">
+        <v>1.1970000267028809</v>
+      </c>
+      <c r="F1202">
+        <v>2207300</v>
+      </c>
+      <c r="G1202">
+        <v>22073</v>
+      </c>
+      <c r="H1202">
+        <f t="shared" si="144"/>
+        <v>1200</v>
+      </c>
+      <c r="I1202">
+        <f>SUM($F$3:F1202)/H1202</f>
+        <v>4041221.3354427083</v>
+      </c>
+      <c r="N1202">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1202">
+        <f t="shared" si="156"/>
+        <v>1.1829999685287476</v>
+      </c>
+      <c r="P1202">
+        <f t="shared" si="143"/>
+        <v>1.2053333520889282</v>
+      </c>
+      <c r="Q1202">
+        <f t="shared" si="132"/>
+        <v>1.2326190528415495</v>
+      </c>
+      <c r="R1202">
+        <f t="shared" si="133"/>
+        <v>-2.7285700752621267E-2</v>
+      </c>
+      <c r="S1202">
+        <f t="shared" si="134"/>
+        <v>1.6578230728097578E-2</v>
+      </c>
+      <c r="T1202">
+        <f t="shared" si="135"/>
+        <v>2.4867346092146368E-4</v>
+      </c>
+      <c r="U1202">
+        <f t="shared" si="136"/>
+        <v>-109.72502112414266</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1203" s="1">
+        <v>46184</v>
+      </c>
+      <c r="B1203">
+        <v>1.1940000057220459</v>
+      </c>
+      <c r="C1203">
+        <v>1.2059999704360962</v>
+      </c>
+      <c r="D1203">
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="E1203">
+        <v>1.1809999942779541</v>
+      </c>
+      <c r="F1203">
+        <v>2693002</v>
+      </c>
+      <c r="G1203">
+        <v>26930.01953125</v>
+      </c>
+      <c r="H1203">
+        <f t="shared" si="144"/>
+        <v>1201</v>
+      </c>
+      <c r="I1203">
+        <f>SUM($F$3:F1203)/H1203</f>
+        <v>4040098.7548136967</v>
+      </c>
+      <c r="N1203">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1203">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1203">
+        <f t="shared" si="143"/>
+        <v>1.1859999895095825</v>
+      </c>
+      <c r="Q1203">
+        <f t="shared" si="132"/>
+        <v>1.2311428586641944</v>
+      </c>
+      <c r="R1203">
+        <f t="shared" si="133"/>
+        <v>-4.5142869154611853E-2</v>
+      </c>
+      <c r="S1203">
+        <f t="shared" si="134"/>
+        <v>1.8265309787931967E-2</v>
+      </c>
+      <c r="T1203">
+        <f t="shared" si="135"/>
+        <v>2.7397964681897949E-4</v>
+      </c>
+      <c r="U1203">
+        <f t="shared" si="136"/>
+        <v>-164.76723610216968</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1204" s="1">
+        <v>46185</v>
+      </c>
+      <c r="B1204">
+        <v>1.1990000009536743</v>
+      </c>
+      <c r="C1204">
+        <v>1.2070000171661377</v>
+      </c>
+      <c r="D1204">
+        <v>1.1909999847412109</v>
+      </c>
+      <c r="E1204">
+        <v>1.1940000057220459</v>
+      </c>
+      <c r="F1204">
+        <v>3299102</v>
+      </c>
+      <c r="G1204">
+        <v>32991.01953125</v>
+      </c>
+      <c r="H1204">
+        <f t="shared" si="144"/>
+        <v>1202</v>
+      </c>
+      <c r="I1204">
+        <f>SUM($F$3:F1204)/H1204</f>
+        <v>4039482.284967762</v>
+      </c>
+      <c r="N1204">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1204">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1204">
+        <f t="shared" si="143"/>
+        <v>1.1973333358764648</v>
+      </c>
+      <c r="Q1204">
+        <f t="shared" si="132"/>
+        <v>1.2289285744939531</v>
+      </c>
+      <c r="R1204">
+        <f t="shared" si="133"/>
+        <v>-3.1595238617488253E-2</v>
+      </c>
+      <c r="S1204">
+        <f t="shared" si="134"/>
+        <v>2.0853741233851673E-2</v>
+      </c>
+      <c r="T1204">
+        <f t="shared" si="135"/>
+        <v>3.128061185077751E-4</v>
+      </c>
+      <c r="U1204">
+        <f t="shared" si="136"/>
+        <v>-101.00582037273328</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1205" s="1">
+        <v>46188</v>
+      </c>
+      <c r="B1205">
+        <v>1.2070000171661377</v>
+      </c>
+      <c r="C1205">
+        <v>1.2339999675750732</v>
+      </c>
+      <c r="D1205">
+        <v>1.2070000171661377</v>
+      </c>
+      <c r="E1205">
+        <v>1.2330000400543213</v>
+      </c>
+      <c r="F1205">
+        <v>3050800</v>
+      </c>
+      <c r="G1205">
+        <v>30508</v>
+      </c>
+      <c r="H1205">
+        <f t="shared" si="144"/>
+        <v>1203</v>
+      </c>
+      <c r="I1205">
+        <f>SUM($F$3:F1205)/H1205</f>
+        <v>4038660.437681837</v>
+      </c>
+      <c r="N1205">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1205">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1205">
+        <f t="shared" si="143"/>
+        <v>1.224666674931844</v>
+      </c>
+      <c r="Q1205">
+        <f t="shared" si="132"/>
+        <v>1.2278095256714592</v>
+      </c>
+      <c r="R1205">
+        <f t="shared" si="133"/>
+        <v>-3.1428507396151772E-3</v>
+      </c>
+      <c r="S1205">
+        <f t="shared" si="134"/>
+        <v>2.0503399323444027E-2</v>
+      </c>
+      <c r="T1205">
+        <f t="shared" si="135"/>
+        <v>3.075509898516604E-4</v>
+      </c>
+      <c r="U1205">
+        <f t="shared" si="136"/>
+        <v>-10.218958297390145</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1206" s="1">
+        <v>46189</v>
+      </c>
+      <c r="B1206">
+        <v>1.2400000095367432</v>
+      </c>
+      <c r="C1206">
+        <v>1.2460000514984131</v>
+      </c>
+      <c r="D1206">
+        <v>1.2350000143051147</v>
+      </c>
+      <c r="E1206">
+        <v>1.2410000562667847</v>
+      </c>
+      <c r="F1206">
+        <v>618100</v>
+      </c>
+      <c r="G1206">
+        <v>6181</v>
+      </c>
+      <c r="H1206">
+        <f t="shared" si="144"/>
+        <v>1204</v>
+      </c>
+      <c r="I1206">
+        <f>SUM($F$3:F1206)/H1206</f>
+        <v>4035819.4406405729</v>
+      </c>
+      <c r="N1206">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1206">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1206">
+        <f t="shared" si="143"/>
+        <v>1.2406667073567708</v>
+      </c>
+      <c r="Q1206">
+        <f t="shared" si="132"/>
+        <v>1.2274285753568015</v>
+      </c>
+      <c r="R1206">
+        <f t="shared" si="133"/>
+        <v>1.323813199996926E-2</v>
+      </c>
+      <c r="S1206">
+        <f t="shared" si="134"/>
+        <v>2.0176870482308523E-2</v>
+      </c>
+      <c r="T1206">
+        <f t="shared" si="135"/>
+        <v>3.0265305723462785E-4</v>
+      </c>
+      <c r="U1206">
+        <f t="shared" si="136"/>
+        <v>43.740288371534838</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1207" s="1">
+        <v>46190</v>
+      </c>
+      <c r="B1207">
+        <v>1.2339999675750732</v>
+      </c>
+      <c r="C1207">
+        <v>1.2569999694824219</v>
+      </c>
+      <c r="D1207">
+        <v>1.2330000400543213</v>
+      </c>
+      <c r="E1207">
+        <v>1.2560000419616699</v>
+      </c>
+      <c r="F1207">
+        <v>1950400</v>
+      </c>
+      <c r="G1207">
+        <v>19504</v>
+      </c>
+      <c r="H1207">
+        <f t="shared" si="144"/>
+        <v>1205</v>
+      </c>
+      <c r="I1207">
+        <f>SUM($F$3:F1207)/H1207</f>
+        <v>4034088.8021006226</v>
+      </c>
+      <c r="N1207">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1207">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1207">
+        <f t="shared" si="143"/>
+        <v>1.2486666838328044</v>
+      </c>
+      <c r="Q1207">
+        <f t="shared" si="132"/>
+        <v>1.2275476257006328</v>
+      </c>
+      <c r="R1207">
+        <f t="shared" si="133"/>
+        <v>2.1119058132171631E-2</v>
+      </c>
+      <c r="S1207">
+        <f t="shared" si="134"/>
+        <v>2.0278913634164009E-2</v>
+      </c>
+      <c r="T1207">
+        <f t="shared" si="135"/>
+        <v>3.0418370451246011E-4</v>
+      </c>
+      <c r="U1207">
+        <f t="shared" si="136"/>
+        <v>69.42863085325645</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1208" s="1">
+        <v>46191</v>
+      </c>
+      <c r="B1208">
+        <v>1.2649999856948853</v>
+      </c>
+      <c r="C1208">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="D1208">
+        <v>1.2619999647140503</v>
+      </c>
+      <c r="E1208">
+        <v>1.2719999551773071</v>
+      </c>
+      <c r="F1208">
+        <v>1272900</v>
+      </c>
+      <c r="G1208">
+        <v>12729</v>
+      </c>
+      <c r="H1208">
+        <f t="shared" si="144"/>
+        <v>1206</v>
+      </c>
+      <c r="I1208">
+        <f>SUM($F$3:F1208)/H1208</f>
+        <v>4031799.2591469735</v>
+      </c>
+      <c r="N1208">
+        <f t="shared" si="155"/>
+        <v>1.281000018119812</v>
+      </c>
+      <c r="O1208">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1208">
+        <f t="shared" si="143"/>
+        <v>1.2699999809265137</v>
+      </c>
+      <c r="Q1208">
+        <f t="shared" si="132"/>
+        <v>1.2289761957668124</v>
+      </c>
+      <c r="R1208">
+        <f t="shared" si="133"/>
+        <v>4.1023785159701287E-2</v>
+      </c>
+      <c r="S1208">
+        <f t="shared" si="134"/>
+        <v>2.1503402262317901E-2</v>
+      </c>
+      <c r="T1208">
+        <f t="shared" si="135"/>
+        <v>3.2255103393476848E-4</v>
+      </c>
+      <c r="U1208">
+        <f t="shared" si="136"/>
+        <v>127.18540895453395</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1209" s="1">
+        <v>46195</v>
+      </c>
+      <c r="B1209">
+        <v>1.2669999599456787</v>
+      </c>
+      <c r="C1209">
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="D1209">
+        <v>1.2619999647140503</v>
+      </c>
+      <c r="E1209">
+        <v>1.2960000038146973</v>
+      </c>
+      <c r="F1209">
+        <v>3210112</v>
+      </c>
+      <c r="G1209">
+        <v>32101.119140625</v>
+      </c>
+      <c r="H1209">
+        <f t="shared" si="144"/>
+        <v>1207</v>
+      </c>
+      <c r="I1209">
+        <f>SUM($F$3:F1209)/H1209</f>
+        <v>4031118.4909123862</v>
+      </c>
+      <c r="N1209">
+        <f t="shared" si="155"/>
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="O1209">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1209">
+        <f t="shared" si="143"/>
+        <v>1.2850000063578289</v>
+      </c>
+      <c r="Q1209">
+        <f t="shared" si="132"/>
+        <v>1.2329523875599817</v>
+      </c>
+      <c r="R1209">
+        <f t="shared" si="133"/>
+        <v>5.2047618797847139E-2</v>
+      </c>
+      <c r="S1209">
+        <f t="shared" si="134"/>
+        <v>2.4911566656463009E-2</v>
+      </c>
+      <c r="T1209">
+        <f t="shared" si="135"/>
+        <v>3.7367349984694512E-4</v>
+      </c>
+      <c r="U1209">
+        <f t="shared" si="136"/>
+        <v>139.28635244181243</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1210" s="1">
+        <v>46196</v>
+      </c>
+      <c r="B1210">
+        <v>1.2910000085830688</v>
+      </c>
+      <c r="C1210">
+        <v>1.2910000085830688</v>
+      </c>
+      <c r="D1210">
+        <v>1.246999979019165</v>
+      </c>
+      <c r="E1210">
+        <v>1.2549999952316284</v>
+      </c>
+      <c r="F1210">
+        <v>3099306</v>
+      </c>
+      <c r="G1210">
+        <v>30993.060546875</v>
+      </c>
+      <c r="H1210">
+        <f t="shared" si="144"/>
+        <v>1208</v>
+      </c>
+      <c r="I1210">
+        <f>SUM($F$3:F1210)/H1210</f>
+        <v>4030347.1229563328</v>
+      </c>
+      <c r="N1210">
+        <f t="shared" si="155"/>
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="O1210">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1210">
+        <f t="shared" si="143"/>
+        <v>1.2643333276112874</v>
+      </c>
+      <c r="Q1210">
+        <f t="shared" si="132"/>
+        <v>1.2347381029810225</v>
+      </c>
+      <c r="R1210">
+        <f t="shared" si="133"/>
+        <v>2.9595224630264871E-2</v>
+      </c>
+      <c r="S1210">
+        <f t="shared" si="134"/>
+        <v>2.6547622113000786E-2</v>
+      </c>
+      <c r="T1210">
+        <f t="shared" si="135"/>
+        <v>3.9821433169501177E-4</v>
+      </c>
+      <c r="U1210">
+        <f t="shared" si="136"/>
+        <v>74.319838023638852</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1211" s="1">
+        <v>46197</v>
+      </c>
+      <c r="B1211">
+        <v>1.2539999485015869</v>
+      </c>
+      <c r="C1211">
+        <v>1.2630000114440918</v>
+      </c>
+      <c r="D1211">
+        <v>1.2419999837875366</v>
+      </c>
+      <c r="E1211">
+        <v>1.2610000371932983</v>
+      </c>
+      <c r="F1211">
+        <v>3049700</v>
+      </c>
+      <c r="G1211">
+        <v>30497</v>
+      </c>
+      <c r="H1211">
+        <f t="shared" si="144"/>
+        <v>1209</v>
+      </c>
+      <c r="I1211">
+        <f>SUM($F$3:F1211)/H1211</f>
+        <v>4029536.0004394129</v>
+      </c>
+      <c r="N1211">
+        <f t="shared" si="155"/>
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="O1211">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1211">
+        <f t="shared" si="143"/>
+        <v>1.2553333441416423</v>
+      </c>
+      <c r="Q1211">
+        <f t="shared" si="132"/>
+        <v>1.2342857207570757</v>
+      </c>
+      <c r="R1211">
+        <f t="shared" si="133"/>
+        <v>2.1047623384566672E-2</v>
+      </c>
+      <c r="S1211">
+        <f t="shared" si="134"/>
+        <v>2.6095239889054076E-2</v>
+      </c>
+      <c r="T1211">
+        <f t="shared" si="135"/>
+        <v>3.9142859833581111E-4</v>
+      </c>
+      <c r="U1211">
+        <f t="shared" si="136"/>
+        <v>53.771296921206748</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1212" s="1">
+        <v>46198</v>
+      </c>
+      <c r="B1212">
+        <v>1.2619999647140503</v>
+      </c>
+      <c r="C1212">
+        <v>1.2920000553131104</v>
+      </c>
+      <c r="D1212">
+        <v>1.2619999647140503</v>
+      </c>
+      <c r="E1212">
+        <v>1.2920000553131104</v>
+      </c>
+      <c r="F1212">
+        <v>2589909</v>
+      </c>
+      <c r="G1212">
+        <v>25899.08984375</v>
+      </c>
+      <c r="H1212">
+        <f t="shared" si="144"/>
+        <v>1210</v>
+      </c>
+      <c r="I1212">
+        <f>SUM($F$3:F1212)/H1212</f>
+        <v>4028346.2260588845</v>
+      </c>
+      <c r="N1212">
+        <f t="shared" si="155"/>
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="O1212">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1212">
+        <f t="shared" si="143"/>
+        <v>1.2820000251134236</v>
+      </c>
+      <c r="Q1212">
+        <f t="shared" si="132"/>
+        <v>1.2359523886726016</v>
+      </c>
+      <c r="R1212">
+        <f t="shared" si="133"/>
+        <v>4.6047636440821993E-2</v>
+      </c>
+      <c r="S1212">
+        <f t="shared" si="134"/>
+        <v>2.7761907804579957E-2</v>
+      </c>
+      <c r="T1212">
+        <f t="shared" si="135"/>
+        <v>4.1642861706869935E-4</v>
+      </c>
+      <c r="U1212">
+        <f t="shared" si="136"/>
+        <v>110.57750249000152</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1213" s="1">
+        <v>46199</v>
+      </c>
+      <c r="B1213">
+        <v>1.2790000438690186</v>
+      </c>
+      <c r="C1213">
+        <v>1.2790000438690186</v>
+      </c>
+      <c r="D1213">
+        <v>1.2359999418258667</v>
+      </c>
+      <c r="E1213">
+        <v>1.2400000095367432</v>
+      </c>
+      <c r="F1213">
+        <v>2505511</v>
+      </c>
+      <c r="G1213">
+        <v>25055.109375</v>
+      </c>
+      <c r="H1213">
+        <f t="shared" si="144"/>
+        <v>1211</v>
+      </c>
+      <c r="I1213">
+        <f>SUM($F$3:F1213)/H1213</f>
+        <v>4027088.7238078034</v>
+      </c>
+      <c r="N1213">
+        <f t="shared" si="155"/>
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="O1213">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1213">
+        <f t="shared" si="143"/>
+        <v>1.2516666650772095</v>
+      </c>
+      <c r="Q1213">
+        <f t="shared" si="132"/>
+        <v>1.2372142927987235</v>
+      </c>
+      <c r="R1213">
+        <f t="shared" si="133"/>
+        <v>1.4452372278485948E-2</v>
+      </c>
+      <c r="S1213">
+        <f t="shared" si="134"/>
+        <v>2.8564628289670355E-2</v>
+      </c>
+      <c r="T1213">
+        <f t="shared" si="135"/>
+        <v>4.284694243450553E-4</v>
+      </c>
+      <c r="U1213">
+        <f t="shared" si="136"/>
+        <v>33.730230110532119</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1214" s="1">
+        <v>46202</v>
+      </c>
+      <c r="B1214">
+        <v>1.2369999885559082</v>
+      </c>
+      <c r="C1214">
+        <v>1.2489999532699585</v>
+      </c>
+      <c r="D1214">
+        <v>1.2209999561309814</v>
+      </c>
+      <c r="E1214">
+        <v>1.2450000047683716</v>
+      </c>
+      <c r="F1214">
+        <v>4012905</v>
+      </c>
+      <c r="G1214">
+        <v>40129.05078125</v>
+      </c>
+      <c r="H1214">
+        <f t="shared" si="144"/>
+        <v>1212</v>
+      </c>
+      <c r="I1214">
+        <f>SUM($F$3:F1214)/H1214</f>
+        <v>4027077.0210653879</v>
+      </c>
+      <c r="N1214">
+        <f t="shared" si="155"/>
+        <v>1.2970000505447388</v>
+      </c>
+      <c r="O1214">
+        <f t="shared" si="156"/>
+        <v>1.1710000038146973</v>
+      </c>
+      <c r="P1214">
+        <f t="shared" si="143"/>
+        <v>1.2383333047231038</v>
+      </c>
+      <c r="Q1214">
+        <f t="shared" si="132"/>
+        <v>1.240333338578542</v>
+      </c>
+      <c r="R1214">
+        <f t="shared" si="133"/>
+        <v>-2.0000338554382324E-3</v>
+      </c>
+      <c r="S1214">
+        <f t="shared" si="134"/>
+        <v>2.5000004541306291E-2</v>
+      </c>
+      <c r="T1214">
+        <f t="shared" si="135"/>
+        <v>3.7500006811959434E-4</v>
+      </c>
+      <c r="U1214">
+        <f t="shared" si="136"/>
+        <v>-5.3334226456737213</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
+++ b/lai/valuationquan/HwabaoWPszseinnovation100ETF.xlsx
@@ -461,7 +461,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:U1214"/>
+  <dimension ref="A1:U1215"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="7" max="7" width="10.125" customWidth="1"/>
@@ -4410,7 +4410,7 @@
         <v>-129.2003593890397</v>
       </c>
     </row>
-    <row r="63" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
       <c r="A63" s="1">
         <v>44461</v>
       </c>
@@ -4440,6 +4440,12 @@
         <f>SUM($F$3:F63)/H63</f>
         <v>17585909.836065575</v>
       </c>
+      <c r="K63" s="2">
+        <v>46234</v>
+      </c>
+      <c r="L63" s="2">
+        <v>46204</v>
+      </c>
       <c r="N63">
         <f t="shared" si="11"/>
         <v>0.98799999999999999</v>
@@ -65815,23 +65821,23 @@
         <v>1.0699999729792278</v>
       </c>
       <c r="Q1037">
-        <f t="shared" ref="Q1037:Q1214" si="132">SUM(P1024:P1037)/14</f>
+        <f t="shared" ref="Q1037:Q1215" si="132">SUM(P1024:P1037)/14</f>
         <v>1.0372619047051386</v>
       </c>
       <c r="R1037">
-        <f t="shared" ref="R1037:R1214" si="133">P1037-Q1037</f>
+        <f t="shared" ref="R1037:R1215" si="133">P1037-Q1037</f>
         <v>3.2738068274089205E-2</v>
       </c>
       <c r="S1037">
-        <f t="shared" ref="S1037:S1214" si="134">AVEDEV(P1024:P1037)</f>
+        <f t="shared" ref="S1037:S1215" si="134">AVEDEV(P1024:P1037)</f>
         <v>2.2748304062149134E-2</v>
       </c>
       <c r="T1037">
-        <f t="shared" ref="T1037:T1214" si="135">0.015*S1037</f>
+        <f t="shared" ref="T1037:T1215" si="135">0.015*S1037</f>
         <v>3.4122456093223696E-4</v>
       </c>
       <c r="U1037">
-        <f t="shared" ref="U1037:U1214" si="136">R1037/T1037</f>
+        <f t="shared" ref="U1037:U1215" si="136">R1037/T1037</f>
         <v>95.942883433266658</v>
       </c>
     </row>
@@ -68961,7 +68967,7 @@
         <v>1.0379999876022339</v>
       </c>
       <c r="P1087">
-        <f t="shared" ref="P1087:P1214" si="143">(C1087+D1087+E1087)/3</f>
+        <f t="shared" ref="P1087:P1215" si="143">(C1087+D1087+E1087)/3</f>
         <v>1.0546666781107585</v>
       </c>
       <c r="Q1087">
@@ -69071,7 +69077,7 @@
         <v>16744.029296875</v>
       </c>
       <c r="H1089">
-        <f t="shared" ref="H1089:H1214" si="144">H1088+1</f>
+        <f t="shared" ref="H1089:H1215" si="144">H1088+1</f>
         <v>1087</v>
       </c>
       <c r="I1089">
@@ -75757,11 +75763,11 @@
         <v>4046737.4413505867</v>
       </c>
       <c r="N1195">
-        <f t="shared" ref="N1195:N1214" si="155">IF(A1195&lt;&gt;$K$62,MAX(N1194,VLOOKUP(A1195,A:C,3)),)</f>
+        <f t="shared" ref="N1195:N1215" si="155">IF(A1195&lt;&gt;$K$62,MAX(N1194,VLOOKUP(A1195,A:C,3)),)</f>
         <v>1.2489999532699585</v>
       </c>
       <c r="O1195">
-        <f t="shared" ref="O1195:O1214" si="156">IF(A1195&lt;&gt;$K$62,MIN(O1194,VLOOKUP(A1195,A:D,4)),)</f>
+        <f t="shared" ref="O1195:O1215" si="156">IF(A1195&lt;&gt;$K$62,MIN(O1194,VLOOKUP(A1195,A:D,4)),)</f>
         <v>1.218000054359436</v>
       </c>
       <c r="P1195">
@@ -76984,6 +76990,69 @@
       <c r="U1214">
         <f t="shared" si="136"/>
         <v>-5.3334226456737213</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:21" x14ac:dyDescent="0.15">
+      <c r="A1215" s="1">
+        <v>46203</v>
+      </c>
+      <c r="B1215">
+        <v>1.2549999952316284</v>
+      </c>
+      <c r="C1215">
+        <v>1.2790000438690186</v>
+      </c>
+      <c r="D1215">
+        <v>1.2510000467300415</v>
+      </c>
+      <c r="E1215">
+        <v>1.2760000228881836</v>
+      </c>
+      <c r="F1215">
+        <v>3094800</v>
+      </c>
+      <c r="G1215">
+        <v>30948</v>
+      </c>
+      <c r="H1215">
+        <f t="shared" si="144"/>
+        <v>1213</v>
+      </c>
+      <c r="I1215">
+        <f>SUM($F$3:F1215)/H1215</f>
+        <v>4026308.4497372219</v>
+      </c>
+      <c r="N1215">
+        <f t="shared" si="155"/>
+        <v>0</v>
+      </c>
+      <c r="O1215">
+        <f t="shared" si="156"/>
+        <v>0</v>
+      </c>
+      <c r="P1215">
+        <f t="shared" si="143"/>
+        <v>1.2686667044957478</v>
+      </c>
+      <c r="Q1215">
+        <f t="shared" si="132"/>
+        <v>1.2441428644316535</v>
+      </c>
+      <c r="R1215">
+        <f t="shared" si="133"/>
+        <v>2.452384006409436E-2</v>
+      </c>
+      <c r="S1215">
+        <f t="shared" si="134"/>
+        <v>2.464626030046118E-2</v>
+      </c>
+      <c r="T1215">
+        <f t="shared" si="135"/>
+        <v>3.696939045069177E-4</v>
+      </c>
+      <c r="U1215">
+        <f t="shared" si="136"/>
+        <v>66.335527216233743</v>
       </c>
     </row>
   </sheetData>
